--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>97578</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>17.1599998474121</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>15.8599996566772</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>15.6599998474121</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="D2719" t="n">
-        <v>15.8599996566772</v>
+        <v>15.6599998474121</v>
       </c>
       <c r="E2719" t="n">
         <v>17</v>
@@ -62906,6 +62906,29 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>101490</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>15.4200000762939</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>57023</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>15.8599996566772</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>15.5600004196167</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>48323</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>16.1399993896484</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>15.7799997329712</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>15.960000038147</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>27658</v>
+        <v>18116</v>
       </c>
       <c r="C2715" t="n">
-        <v>17.2600002288818</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="D2715" t="n">
         <v>16.7800006866455</v>
       </c>
       <c r="E2715" t="n">
-        <v>17.1000003814697</v>
+        <v>16.8999996185303</v>
       </c>
       <c r="F2715" t="n">
-        <v>16.9200000762939</v>
+        <v>16.9799995422363</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>31473</v>
+        <v>27658</v>
       </c>
       <c r="C2716" t="n">
-        <v>17.3400001525879</v>
+        <v>17.2600002288818</v>
       </c>
       <c r="D2716" t="n">
+        <v>16.7800006866455</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F2716" t="n">
         <v>16.9200000762939</v>
-      </c>
-      <c r="E2716" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>17.2199993133545</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>64815</v>
+        <v>31473</v>
       </c>
       <c r="C2717" t="n">
-        <v>17.7000007629395</v>
+        <v>17.3400001525879</v>
       </c>
       <c r="D2717" t="n">
-        <v>17.1000003814697</v>
+        <v>16.9200000762939</v>
       </c>
       <c r="E2717" t="n">
-        <v>17.1200008392334</v>
+        <v>17</v>
       </c>
       <c r="F2717" t="n">
-        <v>17.1000003814697</v>
+        <v>17.2199993133545</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>168609</v>
+        <v>64815</v>
       </c>
       <c r="C2718" t="n">
-        <v>17.2399997711182</v>
+        <v>17.7000007629395</v>
       </c>
       <c r="D2718" t="n">
-        <v>16.1399993896484</v>
+        <v>17.1000003814697</v>
       </c>
       <c r="E2718" t="n">
-        <v>16.6800003051758</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="F2718" t="n">
-        <v>16.9599990844727</v>
+        <v>17.1000003814697</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>97578</v>
+        <v>168609</v>
       </c>
       <c r="C2719" t="n">
-        <v>17.1599998474121</v>
+        <v>17.2399997711182</v>
       </c>
       <c r="D2719" t="n">
-        <v>15.6599998474121</v>
+        <v>16.1399993896484</v>
       </c>
       <c r="E2719" t="n">
-        <v>17</v>
+        <v>16.6800003051758</v>
       </c>
       <c r="F2719" t="n">
-        <v>15.6599998474121</v>
+        <v>16.9599990844727</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>101490</v>
+        <v>97578</v>
       </c>
       <c r="C2720" t="n">
-        <v>15.8000001907349</v>
+        <v>17.1599998474121</v>
       </c>
       <c r="D2720" t="n">
-        <v>14.7799997329712</v>
+        <v>15.6599998474121</v>
       </c>
       <c r="E2720" t="n">
-        <v>15.8000001907349</v>
+        <v>17</v>
       </c>
       <c r="F2720" t="n">
-        <v>15.4200000762939</v>
+        <v>15.6599998474121</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>57023</v>
+        <v>101490</v>
       </c>
       <c r="C2721" t="n">
-        <v>15.8599996566772</v>
+        <v>15.8000001907349</v>
       </c>
       <c r="D2721" t="n">
-        <v>15.3000001907349</v>
+        <v>14.7799997329712</v>
       </c>
       <c r="E2721" t="n">
-        <v>15.5600004196167</v>
+        <v>15.8000001907349</v>
       </c>
       <c r="F2721" t="n">
-        <v>15.7600002288818</v>
+        <v>15.4200000762939</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>48323</v>
+        <v>57023</v>
       </c>
       <c r="C2722" t="n">
-        <v>16.1399993896484</v>
+        <v>15.8599996566772</v>
       </c>
       <c r="D2722" t="n">
-        <v>15.7799997329712</v>
+        <v>15.3000001907349</v>
       </c>
       <c r="E2722" t="n">
-        <v>15.960000038147</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="F2722" t="n">
-        <v>16.1000003814697</v>
+        <v>15.7600002288818</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>30461</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>16.2600002288818</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>15.8199996948242</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>16.2399997711182</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>15.9799995422363</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>14.7200002670288</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>15.1400003433228</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>20792</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>15.2600002288818</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>14.9399995803833</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>14.9399995803833</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>14.9399995803833</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>15.0799999237061</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>27278</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>15.0799999237061</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>15.0799999237061</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>15.0200004577637</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>12594</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>15</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>14.8400001525879</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>13898</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>15.1800003051758</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>28332</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>15.3199996948242</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>15.3199996948242</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.740159034729</v>
       </c>
       <c r="G2" t="n">
-        <v>7.79471635818481</v>
+        <v>7.79471731185913</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G14" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G15" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G16" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G20" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G21" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G22" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G24" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G25" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G27" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.55951404571533</v>
       </c>
       <c r="G34" t="n">
-        <v>7.6501522064209</v>
+        <v>7.65015125274658</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G35" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G36" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G37" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G38" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G39" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G40" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G41" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G42" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G44" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G45" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G46" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G47" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G48" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G49" t="n">
-        <v>7.7986216545105</v>
+        <v>7.79862260818481</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.81339263916016</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85332298278809</v>
+        <v>7.85332202911377</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G52" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G53" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G54" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G55" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G56" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G57" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G58" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G59" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G60" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.27634239196777</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42353820800781</v>
+        <v>7.42353916168213</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.40328121185303</v>
       </c>
       <c r="G62" t="n">
-        <v>7.52512407302856</v>
+        <v>7.52512311935425</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G64" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G65" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G66" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G67" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.55951404571533</v>
       </c>
       <c r="G70" t="n">
-        <v>7.6501522064209</v>
+        <v>7.65015125274658</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G71" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G72" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G73" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G74" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G75" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G79" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G80" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G82" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G83" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.38863372802734</v>
       </c>
       <c r="G84" t="n">
-        <v>7.5134015083313</v>
+        <v>7.51340198516846</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.38863372802734</v>
       </c>
       <c r="G85" t="n">
-        <v>7.5134015083313</v>
+        <v>7.51340198516846</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G87" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G94" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G95" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G96" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G97" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G98" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G99" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G100" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>10.0575084686279</v>
       </c>
       <c r="G101" t="n">
-        <v>8.04867935180664</v>
+        <v>8.04868030548096</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G102" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G105" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G106" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G107" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G111" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G112" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G124" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G125" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G126" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G139" t="n">
-        <v>7.56419515609741</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G140" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.50092697143555</v>
       </c>
       <c r="G143" t="n">
-        <v>7.6032657623291</v>
+        <v>7.60326671600342</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.50092697143555</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6032657623291</v>
+        <v>7.60326671600342</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G145" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.52045631408691</v>
       </c>
       <c r="G146" t="n">
-        <v>7.61889600753784</v>
+        <v>7.61889505386353</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G153" t="n">
-        <v>7.56419515609741</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G154" t="n">
-        <v>7.56419515609741</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G155" t="n">
-        <v>7.56419515609741</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G156" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G158" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G159" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G160" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G161" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G162" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G163" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.4716329574585</v>
       </c>
       <c r="G164" t="n">
-        <v>7.57982492446899</v>
+        <v>7.57982397079468</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G172" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G182" t="n">
-        <v>7.73220109939575</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G183" t="n">
-        <v>7.73220109939575</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G184" t="n">
-        <v>7.63452291488647</v>
+        <v>7.63452386856079</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G185" t="n">
-        <v>7.63452291488647</v>
+        <v>7.63452386856079</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G186" t="n">
-        <v>7.63452291488647</v>
+        <v>7.63452386856079</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G187" t="n">
-        <v>7.63452291488647</v>
+        <v>7.63452386856079</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G189" t="n">
-        <v>7.73220109939575</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G190" t="n">
-        <v>7.73220109939575</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G192" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G201" t="n">
-        <v>7.81034421920776</v>
+        <v>7.81034326553345</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G202" t="n">
-        <v>7.81034421920776</v>
+        <v>7.81034326553345</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G209" t="n">
-        <v>7.7986216545105</v>
+        <v>7.79862260818481</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G210" t="n">
-        <v>7.7986216545105</v>
+        <v>7.79862260818481</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G211" t="n">
-        <v>7.81034421920776</v>
+        <v>7.81034326553345</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.88174533843994</v>
       </c>
       <c r="G226" t="n">
-        <v>7.90802240371704</v>
+        <v>7.90802145004272</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.88174533843994</v>
       </c>
       <c r="G227" t="n">
-        <v>7.90802240371704</v>
+        <v>7.90802145004272</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.73039436340332</v>
       </c>
       <c r="G232" t="n">
-        <v>7.78690147399902</v>
+        <v>7.78690052032471</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.67668914794922</v>
       </c>
       <c r="G233" t="n">
-        <v>7.74392318725586</v>
+        <v>7.74392223358154</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65796661376953</v>
+        <v>7.6579647064209</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.85245227813721</v>
       </c>
       <c r="G237" t="n">
-        <v>7.88458108901978</v>
+        <v>7.88458013534546</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.70598316192627</v>
       </c>
       <c r="G241" t="n">
-        <v>7.7673659324646</v>
+        <v>7.76736688613892</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.70598316192627</v>
       </c>
       <c r="G242" t="n">
-        <v>7.7673659324646</v>
+        <v>7.76736688613892</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.85245227813721</v>
       </c>
       <c r="G249" t="n">
-        <v>7.88458108901978</v>
+        <v>7.88458013534546</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.0575084686279</v>
       </c>
       <c r="G251" t="n">
-        <v>8.04867935180664</v>
+        <v>8.04868030548096</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.1453886032104</v>
       </c>
       <c r="G252" t="n">
-        <v>8.11900615692139</v>
+        <v>8.11900806427002</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.1551532745361</v>
       </c>
       <c r="G255" t="n">
-        <v>8.12682247161865</v>
+        <v>8.12682151794434</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G257" t="n">
-        <v>8.15644550323486</v>
+        <v>8.15644264221191</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.3783721923828</v>
       </c>
       <c r="G262" t="n">
-        <v>8.30545616149902</v>
+        <v>8.30545711517334</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G264" t="n">
-        <v>8.15644550323486</v>
+        <v>8.15644264221191</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G265" t="n">
-        <v>8.15644550323486</v>
+        <v>8.15644264221191</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3783721923828</v>
       </c>
       <c r="G266" t="n">
-        <v>8.30545616149902</v>
+        <v>8.30545711517334</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6821765899658</v>
       </c>
       <c r="G271" t="n">
-        <v>8.54858016967773</v>
+        <v>8.54858112335205</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7801790237427</v>
       </c>
       <c r="G272" t="n">
-        <v>8.62700748443604</v>
+        <v>8.62700843811035</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.770378112793</v>
       </c>
       <c r="G274" t="n">
-        <v>8.61916542053223</v>
+        <v>8.61916446685791</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.6821765899658</v>
       </c>
       <c r="G275" t="n">
-        <v>8.54858016967773</v>
+        <v>8.54858112335205</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.535174369812</v>
       </c>
       <c r="G277" t="n">
-        <v>8.43093872070312</v>
+        <v>8.43093967437744</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.7409782409668</v>
       </c>
       <c r="G278" t="n">
-        <v>8.59563636779785</v>
+        <v>8.59563732147217</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.9859819412231</v>
       </c>
       <c r="G283" t="n">
-        <v>8.79170513153076</v>
+        <v>8.79170417785645</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>11.0055818557739</v>
       </c>
       <c r="G284" t="n">
-        <v>8.8073902130127</v>
+        <v>8.80738925933838</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.025182723999</v>
       </c>
       <c r="G285" t="n">
-        <v>8.82307720184326</v>
+        <v>8.82307624816895</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.0349826812744</v>
       </c>
       <c r="G286" t="n">
-        <v>8.83091831207275</v>
+        <v>8.83091735839844</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.025182723999</v>
       </c>
       <c r="G287" t="n">
-        <v>8.82307720184326</v>
+        <v>8.82307624816895</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.4567728042603</v>
       </c>
       <c r="G290" t="n">
-        <v>8.36819744110107</v>
+        <v>8.36819648742676</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.6723766326904</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54073715209961</v>
+        <v>8.54073619842529</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.5155744552612</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41525268554688</v>
+        <v>8.41525459289551</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.4861736297607</v>
       </c>
       <c r="G293" t="n">
-        <v>8.39172649383545</v>
+        <v>8.39172554016113</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.4371728897095</v>
       </c>
       <c r="G294" t="n">
-        <v>8.35251235961914</v>
+        <v>8.35251140594482</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.3881721496582</v>
       </c>
       <c r="G296" t="n">
-        <v>8.31329917907715</v>
+        <v>8.31329822540283</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.535174369812</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43093872070312</v>
+        <v>8.43093967437744</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.2999706268311</v>
       </c>
       <c r="G304" t="n">
-        <v>8.24271488189697</v>
+        <v>8.24271297454834</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.2901697158813</v>
       </c>
       <c r="G305" t="n">
-        <v>8.23487091064453</v>
+        <v>8.23486995697021</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2019691467285</v>
       </c>
       <c r="G308" t="n">
-        <v>8.16428565979004</v>
+        <v>8.16428661346436</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G309" t="n">
-        <v>8.21134376525879</v>
+        <v>8.21134281158447</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.2901697158813</v>
       </c>
       <c r="G310" t="n">
-        <v>8.23487091064453</v>
+        <v>8.23486995697021</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3881721496582</v>
       </c>
       <c r="G311" t="n">
-        <v>8.31329917907715</v>
+        <v>8.31329822540283</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.2411699295044</v>
       </c>
       <c r="G312" t="n">
-        <v>8.19565677642822</v>
+        <v>8.19565773010254</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.2411699295044</v>
       </c>
       <c r="G313" t="n">
-        <v>8.19565677642822</v>
+        <v>8.19565773010254</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2019691467285</v>
       </c>
       <c r="G314" t="n">
-        <v>8.16428565979004</v>
+        <v>8.16428661346436</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.3979721069336</v>
       </c>
       <c r="G316" t="n">
-        <v>8.32114219665527</v>
+        <v>8.32114028930664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.6135759353638</v>
       </c>
       <c r="G317" t="n">
-        <v>8.49368286132812</v>
+        <v>8.49368190765381</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.7605781555176</v>
       </c>
       <c r="G319" t="n">
-        <v>8.61132144927979</v>
+        <v>8.6113224029541</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.7997789382935</v>
       </c>
       <c r="G320" t="n">
-        <v>8.64269351959229</v>
+        <v>8.64269161224365</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.9075813293457</v>
       </c>
       <c r="G322" t="n">
-        <v>8.72896385192871</v>
+        <v>8.72896480560303</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.2113857269287</v>
       </c>
       <c r="G323" t="n">
-        <v>8.97208690643311</v>
+        <v>8.97208786010742</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.9663820266724</v>
       </c>
       <c r="G324" t="n">
-        <v>8.77602005004883</v>
+        <v>8.77602100372314</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>11.0741834640503</v>
       </c>
       <c r="G325" t="n">
-        <v>8.86228847503662</v>
+        <v>8.86228942871094</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.5053911209106</v>
       </c>
       <c r="G328" t="n">
-        <v>9.20737075805664</v>
+        <v>9.20737171173096</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.5543909072876</v>
       </c>
       <c r="G329" t="n">
-        <v>9.24658298492432</v>
+        <v>9.24658393859863</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.6425933837891</v>
       </c>
       <c r="G330" t="n">
-        <v>9.31716823577881</v>
+        <v>9.31716918945312</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>12.3384037017822</v>
       </c>
       <c r="G334" t="n">
-        <v>9.87400245666504</v>
+        <v>9.87400341033936</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>12.4560060501099</v>
       </c>
       <c r="G336" t="n">
-        <v>9.96811580657959</v>
+        <v>9.96811485290527</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.5638084411621</v>
       </c>
       <c r="G339" t="n">
-        <v>10.0543870925903</v>
+        <v>10.0543851852417</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.5344076156616</v>
       </c>
       <c r="G340" t="n">
-        <v>10.0308570861816</v>
+        <v>10.030858039856</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.6814098358154</v>
       </c>
       <c r="G341" t="n">
-        <v>10.1484975814819</v>
+        <v>10.1484985351562</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>12.7304105758667</v>
       </c>
       <c r="G343" t="n">
-        <v>10.1877107620239</v>
+        <v>10.1877117156982</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.8382129669189</v>
       </c>
       <c r="G348" t="n">
-        <v>10.273983001709</v>
+        <v>10.2739820480347</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.8382129669189</v>
       </c>
       <c r="G351" t="n">
-        <v>10.273983001709</v>
+        <v>10.2739820480347</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>12.67160987854</v>
       </c>
       <c r="G353" t="n">
-        <v>10.1406564712524</v>
+        <v>10.1406555175781</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>12.8382129669189</v>
       </c>
       <c r="G354" t="n">
-        <v>10.273983001709</v>
+        <v>10.2739820480347</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>12.7010097503662</v>
       </c>
       <c r="G355" t="n">
-        <v>10.1641836166382</v>
+        <v>10.1641845703125</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>12.6618099212646</v>
       </c>
       <c r="G357" t="n">
-        <v>10.1328134536743</v>
+        <v>10.1328125</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.034215927124</v>
       </c>
       <c r="G360" t="n">
-        <v>10.430835723877</v>
+        <v>10.4308366775513</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.965615272522</v>
       </c>
       <c r="G362" t="n">
-        <v>10.3759365081787</v>
+        <v>10.375937461853</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.8284130096436</v>
       </c>
       <c r="G363" t="n">
-        <v>10.2661399841309</v>
+        <v>10.2661390304565</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.1126165390015</v>
       </c>
       <c r="G365" t="n">
-        <v>10.4935779571533</v>
+        <v>10.4935789108276</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.8578128814697</v>
       </c>
       <c r="G366" t="n">
-        <v>10.2896671295166</v>
+        <v>10.2896661758423</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G369" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>13.1126165390015</v>
       </c>
       <c r="G370" t="n">
-        <v>10.4935779571533</v>
+        <v>10.4935789108276</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>13.2596197128296</v>
       </c>
       <c r="G371" t="n">
-        <v>10.6112194061279</v>
+        <v>10.6112203598022</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.2792196273804</v>
       </c>
       <c r="G372" t="n">
-        <v>10.6269035339355</v>
+        <v>10.6269054412842</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>13.4752225875854</v>
       </c>
       <c r="G373" t="n">
-        <v>10.7837591171265</v>
+        <v>10.7837600708008</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.6614255905151</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9327726364136</v>
+        <v>10.9327716827393</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.6516256332397</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9249296188354</v>
+        <v>10.9249277114868</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.3478212356567</v>
       </c>
       <c r="G380" t="n">
-        <v>10.6818037033081</v>
+        <v>10.6818046569824</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.7794122695923</v>
       </c>
       <c r="G383" t="n">
-        <v>10.2269248962402</v>
+        <v>10.2269258499146</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.5638084411621</v>
       </c>
       <c r="G387" t="n">
-        <v>10.0543870925903</v>
+        <v>10.0543851852417</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.544207572937</v>
       </c>
       <c r="G388" t="n">
-        <v>10.0387001037598</v>
+        <v>10.0386991500854</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.3776054382324</v>
       </c>
       <c r="G391" t="n">
-        <v>9.90537357330322</v>
+        <v>9.90537261962891</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.3286037445068</v>
       </c>
       <c r="G392" t="n">
-        <v>9.86615943908691</v>
+        <v>9.86616039276123</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.4364061355591</v>
       </c>
       <c r="G393" t="n">
-        <v>9.95243072509766</v>
+        <v>9.95242977142334</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G396" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G397" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G398" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.4168062210083</v>
       </c>
       <c r="G399" t="n">
-        <v>9.93674373626709</v>
+        <v>9.93674468994141</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>12.3580045700073</v>
       </c>
       <c r="G400" t="n">
-        <v>9.88968849182129</v>
+        <v>9.88968944549561</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G401" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.2698030471802</v>
       </c>
       <c r="G403" t="n">
-        <v>9.8191032409668</v>
+        <v>9.81910419464111</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.6324090957642</v>
       </c>
       <c r="G405" t="n">
-        <v>10.1092844009399</v>
+        <v>10.1092853546143</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.4560060501099</v>
       </c>
       <c r="G407" t="n">
-        <v>9.96811580657959</v>
+        <v>9.96811485290527</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.4364061355591</v>
       </c>
       <c r="G408" t="n">
-        <v>9.95243072509766</v>
+        <v>9.95242977142334</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G409" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4168062210083</v>
       </c>
       <c r="G410" t="n">
-        <v>9.93674373626709</v>
+        <v>9.93674468994141</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>12.4854068756104</v>
       </c>
       <c r="G413" t="n">
-        <v>9.99164485931396</v>
+        <v>9.99164295196533</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.5834093093872</v>
       </c>
       <c r="G414" t="n">
-        <v>10.0700712203979</v>
+        <v>10.0700702667236</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>12.8382129669189</v>
       </c>
       <c r="G415" t="n">
-        <v>10.273983001709</v>
+        <v>10.2739820480347</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G416" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G418" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G419" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.2596197128296</v>
       </c>
       <c r="G421" t="n">
-        <v>10.6112194061279</v>
+        <v>10.6112203598022</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.2596197128296</v>
       </c>
       <c r="G422" t="n">
-        <v>10.6112194061279</v>
+        <v>10.6112203598022</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G424" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G425" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13.328221321106</v>
       </c>
       <c r="G426" t="n">
-        <v>10.6661195755005</v>
+        <v>10.6661205291748</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.4262218475342</v>
       </c>
       <c r="G428" t="n">
-        <v>10.7445449829102</v>
+        <v>10.7445459365845</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G429" t="n">
-        <v>10.775915145874</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.4164218902588</v>
       </c>
       <c r="G430" t="n">
-        <v>10.736701965332</v>
+        <v>10.7367029190063</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.396821975708</v>
       </c>
       <c r="G432" t="n">
-        <v>10.7210168838501</v>
+        <v>10.7210178375244</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.4262218475342</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7445449829102</v>
+        <v>10.7445459365845</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G435" t="n">
-        <v>10.775915145874</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G436" t="n">
-        <v>10.775915145874</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.396821975708</v>
       </c>
       <c r="G438" t="n">
-        <v>10.7210168838501</v>
+        <v>10.7210178375244</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.2596197128296</v>
       </c>
       <c r="G440" t="n">
-        <v>10.6112194061279</v>
+        <v>10.6112203598022</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G441" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092649459839</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.5834093093872</v>
       </c>
       <c r="G444" t="n">
-        <v>10.0700712203979</v>
+        <v>10.0700702667236</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12.2110023498535</v>
       </c>
       <c r="G445" t="n">
-        <v>9.77204704284668</v>
+        <v>9.77204608917236</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10.2999706268311</v>
       </c>
       <c r="G446" t="n">
-        <v>8.24271488189697</v>
+        <v>8.24271297454834</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>10.0745668411255</v>
       </c>
       <c r="G447" t="n">
-        <v>8.062331199646</v>
+        <v>8.06233024597168</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.1137666702271</v>
       </c>
       <c r="G450" t="n">
-        <v>8.09370231628418</v>
+        <v>8.09370136260986</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G451" t="n">
-        <v>7.92116117477417</v>
+        <v>7.9211630821228</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G455" t="n">
-        <v>8.15644550323486</v>
+        <v>8.15644264221191</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.2901697158813</v>
       </c>
       <c r="G456" t="n">
-        <v>8.23487091064453</v>
+        <v>8.23486995697021</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.92756366729736</v>
       </c>
       <c r="G458" t="n">
-        <v>7.94468879699707</v>
+        <v>7.94468975067139</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G460" t="n">
-        <v>8.21134376525879</v>
+        <v>8.21134281158447</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G462" t="n">
-        <v>8.15644550323486</v>
+        <v>8.15644264221191</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.535174369812</v>
       </c>
       <c r="G465" t="n">
-        <v>8.43093872070312</v>
+        <v>8.43093967437744</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.4861736297607</v>
       </c>
       <c r="G467" t="n">
-        <v>8.39172649383545</v>
+        <v>8.39172554016113</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.3489713668823</v>
       </c>
       <c r="G468" t="n">
-        <v>8.28192806243896</v>
+        <v>8.28192710876465</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.2901697158813</v>
       </c>
       <c r="G470" t="n">
-        <v>8.23487091064453</v>
+        <v>8.23486995697021</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G471" t="n">
-        <v>8.21134376525879</v>
+        <v>8.21134281158447</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>10.3881721496582</v>
       </c>
       <c r="G472" t="n">
-        <v>8.31329917907715</v>
+        <v>8.31329822540283</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>10.4371728897095</v>
       </c>
       <c r="G473" t="n">
-        <v>8.35251235961914</v>
+        <v>8.35251140594482</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>10.535174369812</v>
       </c>
       <c r="G474" t="n">
-        <v>8.43093872070312</v>
+        <v>8.43093967437744</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.2901697158813</v>
       </c>
       <c r="G476" t="n">
-        <v>8.23487091064453</v>
+        <v>8.23486995697021</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.1137666702271</v>
       </c>
       <c r="G477" t="n">
-        <v>8.09370231628418</v>
+        <v>8.09370136260986</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.99616622924805</v>
       </c>
       <c r="G479" t="n">
-        <v>7.99958896636963</v>
+        <v>7.99958801269531</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.0745668411255</v>
       </c>
       <c r="G480" t="n">
-        <v>8.062331199646</v>
+        <v>8.06233024597168</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G481" t="n">
-        <v>7.92116117477417</v>
+        <v>7.9211630821228</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G483" t="n">
-        <v>7.92116117477417</v>
+        <v>7.9211630821228</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G484" t="n">
-        <v>7.8819465637207</v>
+        <v>7.88194751739502</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G485" t="n">
-        <v>7.8819465637207</v>
+        <v>7.88194751739502</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G486" t="n">
-        <v>7.8819465637207</v>
+        <v>7.88194751739502</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>9.8687629699707</v>
       </c>
       <c r="G487" t="n">
-        <v>7.89763212203979</v>
+        <v>7.89763307571411</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G488" t="n">
-        <v>7.92116117477417</v>
+        <v>7.9211630821228</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.91776371002197</v>
       </c>
       <c r="G489" t="n">
-        <v>7.93684673309326</v>
+        <v>7.93684768676758</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.97656536102295</v>
       </c>
       <c r="G490" t="n">
-        <v>7.98390245437622</v>
+        <v>7.98390340805054</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G491" t="n">
-        <v>7.92116117477417</v>
+        <v>7.9211630821228</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.83936309814453</v>
       </c>
       <c r="G494" t="n">
-        <v>7.87410497665405</v>
+        <v>7.87410593032837</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.78546237945557</v>
       </c>
       <c r="G495" t="n">
-        <v>7.830970287323</v>
+        <v>7.83097124099731</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.70216083526611</v>
       </c>
       <c r="G496" t="n">
-        <v>7.76430559158325</v>
+        <v>7.76430749893188</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.51595783233643</v>
       </c>
       <c r="G497" t="n">
-        <v>7.61529445648193</v>
+        <v>7.61529588699341</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.46695709228516</v>
       </c>
       <c r="G498" t="n">
-        <v>7.57608127593994</v>
+        <v>7.57608222961426</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.55515766143799</v>
       </c>
       <c r="G499" t="n">
-        <v>7.64666509628296</v>
+        <v>7.64666700363159</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>9.52575778961182</v>
       </c>
       <c r="G500" t="n">
-        <v>7.62313747406006</v>
+        <v>7.62313842773438</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.4081563949585</v>
       </c>
       <c r="G503" t="n">
-        <v>7.52902555465698</v>
+        <v>7.52902412414551</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.12395095825195</v>
       </c>
       <c r="G505" t="n">
-        <v>7.30158519744873</v>
+        <v>7.30158615112305</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.01614856719971</v>
       </c>
       <c r="G506" t="n">
-        <v>7.21531391143799</v>
+        <v>7.21531534194946</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.23665332794189</v>
       </c>
       <c r="G507" t="n">
-        <v>7.39177703857422</v>
+        <v>7.39177751541138</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G508" t="n">
-        <v>7.3329553604126</v>
+        <v>7.33295679092407</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G509" t="n">
-        <v>7.3329553604126</v>
+        <v>7.33295679092407</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.06515026092529</v>
       </c>
       <c r="G511" t="n">
-        <v>7.25452947616577</v>
+        <v>7.25452899932861</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.01124858856201</v>
       </c>
       <c r="G512" t="n">
-        <v>7.21139478683472</v>
+        <v>7.21139287948608</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.06515026092529</v>
       </c>
       <c r="G513" t="n">
-        <v>7.25452947616577</v>
+        <v>7.25452899932861</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G514" t="n">
-        <v>7.3329553604126</v>
+        <v>7.33295679092407</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.17295169830322</v>
       </c>
       <c r="G515" t="n">
-        <v>7.34079885482788</v>
+        <v>7.34079933166504</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.09455108642578</v>
       </c>
       <c r="G516" t="n">
-        <v>7.2780590057373</v>
+        <v>7.27805852890015</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.04555034637451</v>
       </c>
       <c r="G518" t="n">
-        <v>7.23884439468384</v>
+        <v>7.23884344100952</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.0259485244751</v>
       </c>
       <c r="G520" t="n">
-        <v>7.22315740585327</v>
+        <v>7.22315692901611</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.03575038909912</v>
       </c>
       <c r="G522" t="n">
-        <v>7.23100090026855</v>
+        <v>7.23100185394287</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G524" t="n">
-        <v>7.01924657821655</v>
+        <v>7.01924753189087</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>8.888747215271</v>
       </c>
       <c r="G525" t="n">
-        <v>7.11336040496826</v>
+        <v>7.1133599281311</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>8.89854717254639</v>
       </c>
       <c r="G526" t="n">
-        <v>7.12120294570923</v>
+        <v>7.12120246887207</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>8.87894725799561</v>
       </c>
       <c r="G527" t="n">
-        <v>7.10551738739014</v>
+        <v>7.10551834106445</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G529" t="n">
-        <v>7.08198833465576</v>
+        <v>7.08198881149292</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G530" t="n">
-        <v>7.01924657821655</v>
+        <v>7.01924753189087</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G531" t="n">
-        <v>7.02709054946899</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>8.90834712982178</v>
       </c>
       <c r="G534" t="n">
-        <v>7.12904596328735</v>
+        <v>7.12904405593872</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.94754791259766</v>
       </c>
       <c r="G535" t="n">
-        <v>7.16041612625122</v>
+        <v>7.1604151725769</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.94754791259766</v>
       </c>
       <c r="G536" t="n">
-        <v>7.16041612625122</v>
+        <v>7.1604151725769</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G538" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G540" t="n">
-        <v>7.01924657821655</v>
+        <v>7.01924753189087</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.68294429779053</v>
       </c>
       <c r="G541" t="n">
-        <v>6.94866228103638</v>
+        <v>6.94866275787354</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.87894725799561</v>
       </c>
       <c r="G543" t="n">
-        <v>7.10551738739014</v>
+        <v>7.10551834106445</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G544" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.888747215271</v>
       </c>
       <c r="G545" t="n">
-        <v>7.11336040496826</v>
+        <v>7.1133599281311</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.08198833465576</v>
+        <v>7.08198881149292</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.83974647521973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.07414531707764</v>
+        <v>7.07414674758911</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G550" t="n">
-        <v>7.06630373001099</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G551" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G553" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G556" t="n">
-        <v>7.02709054946899</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.7319450378418</v>
       </c>
       <c r="G558" t="n">
-        <v>6.98787689208984</v>
+        <v>6.987877368927</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.83974647521973</v>
       </c>
       <c r="G561" t="n">
-        <v>7.07414531707764</v>
+        <v>7.07414674758911</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.96714782714844</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17610216140747</v>
+        <v>7.17610168457031</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G565" t="n">
-        <v>7.02709054946899</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G566" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G571" t="n">
-        <v>7.06630373001099</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G573" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G574" t="n">
-        <v>7.06630373001099</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G575" t="n">
-        <v>7.08198833465576</v>
+        <v>7.08198881149292</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G576" t="n">
-        <v>7.01924657821655</v>
+        <v>7.01924753189087</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>8.74174499511719</v>
       </c>
       <c r="G577" t="n">
-        <v>6.99571943283081</v>
+        <v>6.99571895599365</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G580" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G582" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G583" t="n">
-        <v>7.01924657821655</v>
+        <v>7.01924753189087</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G584" t="n">
-        <v>7.02709054946899</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G586" t="n">
-        <v>7.05846071243286</v>
+        <v>7.05846118927002</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.60454177856445</v>
       </c>
       <c r="G591" t="n">
-        <v>6.88592004776001</v>
+        <v>6.88591909408569</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.49674129486084</v>
       </c>
       <c r="G592" t="n">
-        <v>6.79965019226074</v>
+        <v>6.79965114593506</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.47714042663574</v>
       </c>
       <c r="G594" t="n">
-        <v>6.78396463394165</v>
+        <v>6.78396511077881</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.45753955841064</v>
       </c>
       <c r="G595" t="n">
-        <v>6.7682785987854</v>
+        <v>6.76827955245972</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.28113746643066</v>
       </c>
       <c r="G596" t="n">
-        <v>6.62711095809937</v>
+        <v>6.62711000442505</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.13413524627686</v>
       </c>
       <c r="G598" t="n">
-        <v>6.60602617263794</v>
+        <v>6.60602569580078</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G600" t="n">
-        <v>7.00397777557373</v>
+        <v>7.00397872924805</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.48694038391113</v>
       </c>
       <c r="G601" t="n">
-        <v>6.89255237579346</v>
+        <v>6.8925518989563</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.42813873291016</v>
       </c>
       <c r="G602" t="n">
-        <v>6.8447961807251</v>
+        <v>6.84479665756226</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G603" t="n">
-        <v>7.00397777557373</v>
+        <v>7.00397872924805</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.47714042663574</v>
       </c>
       <c r="G606" t="n">
-        <v>6.88459253311157</v>
+        <v>6.88459205627441</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.47714042663574</v>
       </c>
       <c r="G608" t="n">
-        <v>6.88459253311157</v>
+        <v>6.88459205627441</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.56534194946289</v>
       </c>
       <c r="G609" t="n">
-        <v>6.95622444152832</v>
+        <v>6.956223487854</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>8.47714042663574</v>
       </c>
       <c r="G612" t="n">
-        <v>6.88459253311157</v>
+        <v>6.88459205627441</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G615" t="n">
-        <v>6.36725282669067</v>
+        <v>6.36725330352783</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G616" t="n">
-        <v>6.36725282669067</v>
+        <v>6.36725330352783</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.77152919769287</v>
       </c>
       <c r="G620" t="n">
-        <v>6.3115406036377</v>
+        <v>6.31153964996338</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.77152919769287</v>
       </c>
       <c r="G621" t="n">
-        <v>6.3115406036377</v>
+        <v>6.31153964996338</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.50692415237427</v>
       </c>
       <c r="G623" t="n">
-        <v>6.09664487838745</v>
+        <v>6.09664535522461</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.57552480697632</v>
       </c>
       <c r="G625" t="n">
-        <v>6.15235710144043</v>
+        <v>6.15235757827759</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.50692415237427</v>
       </c>
       <c r="G626" t="n">
-        <v>6.09664487838745</v>
+        <v>6.09664535522461</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.59512615203857</v>
       </c>
       <c r="G627" t="n">
-        <v>6.1682767868042</v>
+        <v>6.16827726364136</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.68332719802856</v>
       </c>
       <c r="G628" t="n">
-        <v>6.23990774154663</v>
+        <v>6.23990869522095</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>7.57552480697632</v>
       </c>
       <c r="G629" t="n">
-        <v>6.15235710144043</v>
+        <v>6.15235757827759</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G630" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684852600098</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.23252010345459</v>
       </c>
       <c r="G632" t="n">
-        <v>5.87379169464111</v>
+        <v>5.87379121780396</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G634" t="n">
-        <v>5.74644613265991</v>
+        <v>5.74644565582275</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>7.23252010345459</v>
       </c>
       <c r="G635" t="n">
-        <v>5.87379169464111</v>
+        <v>5.87379121780396</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7782826423645</v>
+        <v>5.77828216552734</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G638" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G640" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G641" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G647" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7.78132915496826</v>
       </c>
       <c r="G654" t="n">
-        <v>6.31949901580811</v>
+        <v>6.31949949264526</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.73232793807983</v>
       </c>
       <c r="G655" t="n">
-        <v>6.27970266342163</v>
+        <v>6.27970314025879</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.55592489242554</v>
       </c>
       <c r="G656" t="n">
-        <v>6.13643980026245</v>
+        <v>6.13644027709961</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>7.59512615203857</v>
       </c>
       <c r="G657" t="n">
-        <v>6.1682767868042</v>
+        <v>6.16827726364136</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>7.57552480697632</v>
       </c>
       <c r="G658" t="n">
-        <v>6.15235710144043</v>
+        <v>6.15235757827759</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G661" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G663" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684852600098</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G665" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684852600098</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G666" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684852600098</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>7.41872310638428</v>
       </c>
       <c r="G667" t="n">
-        <v>6.0250129699707</v>
+        <v>6.02501392364502</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>7.26191997528076</v>
       </c>
       <c r="G668" t="n">
-        <v>5.89766836166382</v>
+        <v>5.89766788482666</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>7.18351888656616</v>
       </c>
       <c r="G670" t="n">
-        <v>5.83399534225464</v>
+        <v>5.8339958190918</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G672" t="n">
-        <v>5.74644613265991</v>
+        <v>5.74644565582275</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G673" t="n">
-        <v>5.7782826423645</v>
+        <v>5.77828216552734</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>7.18351888656616</v>
       </c>
       <c r="G674" t="n">
-        <v>5.83399534225464</v>
+        <v>5.8339958190918</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>7.18351888656616</v>
       </c>
       <c r="G675" t="n">
-        <v>5.83399534225464</v>
+        <v>5.8339958190918</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G677" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G678" t="n">
-        <v>5.49175643920898</v>
+        <v>5.49175596237183</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G679" t="n">
-        <v>5.58726406097412</v>
+        <v>5.58726453781128</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G681" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G682" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G683" t="n">
-        <v>5.58726406097412</v>
+        <v>5.58726453781128</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G684" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G686" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G687" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.81111288070679</v>
       </c>
       <c r="G688" t="n">
-        <v>5.53155088424683</v>
+        <v>5.53155136108398</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G689" t="n">
-        <v>5.58726406097412</v>
+        <v>5.58726453781128</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G690" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G692" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G694" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.94831514358521</v>
       </c>
       <c r="G695" t="n">
-        <v>5.64297771453857</v>
+        <v>5.64297819137573</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>7.23252010345459</v>
       </c>
       <c r="G696" t="n">
-        <v>5.87379169464111</v>
+        <v>5.87379121780396</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>7.47752380371094</v>
       </c>
       <c r="G698" t="n">
-        <v>6.07276773452759</v>
+        <v>6.07276725769043</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.34032106399536</v>
       </c>
       <c r="G704" t="n">
-        <v>5.96134042739868</v>
+        <v>5.96133995056152</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>7.16391801834106</v>
       </c>
       <c r="G707" t="n">
-        <v>5.8180775642395</v>
+        <v>5.81807708740234</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.90911388397217</v>
       </c>
       <c r="G710" t="n">
-        <v>5.61114120483398</v>
+        <v>5.61114168167114</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G714" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G715" t="n">
-        <v>5.58726406097412</v>
+        <v>5.58726453781128</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.84051322937012</v>
       </c>
       <c r="G716" t="n">
-        <v>5.55542802810669</v>
+        <v>5.55542850494385</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G717" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.83071279525757</v>
       </c>
       <c r="G718" t="n">
-        <v>5.54746913909912</v>
+        <v>5.54746866226196</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.89931392669678</v>
       </c>
       <c r="G719" t="n">
-        <v>5.60318279266357</v>
+        <v>5.60318326950073</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.84051322937012</v>
       </c>
       <c r="G720" t="n">
-        <v>5.55542802810669</v>
+        <v>5.55542850494385</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.83071279525757</v>
       </c>
       <c r="G722" t="n">
-        <v>5.54746913909912</v>
+        <v>5.54746866226196</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.90911388397217</v>
       </c>
       <c r="G724" t="n">
-        <v>5.61114120483398</v>
+        <v>5.61114168167114</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G725" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.84051322937012</v>
       </c>
       <c r="G727" t="n">
-        <v>5.55542802810669</v>
+        <v>5.55542850494385</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G730" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G731" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G732" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.83071279525757</v>
       </c>
       <c r="G733" t="n">
-        <v>5.54746913909912</v>
+        <v>5.54746866226196</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.81111288070679</v>
       </c>
       <c r="G734" t="n">
-        <v>5.53155088424683</v>
+        <v>5.53155136108398</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>6.83071279525757</v>
       </c>
       <c r="G735" t="n">
-        <v>5.54746913909912</v>
+        <v>5.54746866226196</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>6.7817120552063</v>
       </c>
       <c r="G736" t="n">
-        <v>5.50767469406128</v>
+        <v>5.50767421722412</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.84051322937012</v>
       </c>
       <c r="G737" t="n">
-        <v>5.55542802810669</v>
+        <v>5.55542850494385</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>6.7817120552063</v>
       </c>
       <c r="G738" t="n">
-        <v>5.50767469406128</v>
+        <v>5.50767421722412</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G739" t="n">
-        <v>5.49175643920898</v>
+        <v>5.49175596237183</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G740" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G741" t="n">
-        <v>5.57134580612183</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>6.89931392669678</v>
       </c>
       <c r="G742" t="n">
-        <v>5.60318279266357</v>
+        <v>5.60318326950073</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G743" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.90911388397217</v>
       </c>
       <c r="G744" t="n">
-        <v>5.61114120483398</v>
+        <v>5.61114168167114</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>6.94831514358521</v>
       </c>
       <c r="G745" t="n">
-        <v>5.64297771453857</v>
+        <v>5.64297819137573</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G746" t="n">
-        <v>5.7782826423645</v>
+        <v>5.77828216552734</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>7.05611705780029</v>
       </c>
       <c r="G747" t="n">
-        <v>5.73052835464478</v>
+        <v>5.73052787780762</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G748" t="n">
-        <v>5.74644613265991</v>
+        <v>5.74644565582275</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>7.08551692962646</v>
       </c>
       <c r="G749" t="n">
-        <v>5.75440454483032</v>
+        <v>5.75440502166748</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G750" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G758" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G762" t="n">
-        <v>5.74644613265991</v>
+        <v>5.74644565582275</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G763" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>7.0463171005249</v>
       </c>
       <c r="G767" t="n">
-        <v>5.72256898880005</v>
+        <v>5.72256946563721</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G769" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G770" t="n">
-        <v>5.7782826423645</v>
+        <v>5.77828216552734</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G772" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G773" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>7.20311880111694</v>
       </c>
       <c r="G774" t="n">
-        <v>5.84991312026978</v>
+        <v>5.84991359710693</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G781" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G783" t="n">
-        <v>5.97725868225098</v>
+        <v>5.97725820541382</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G786" t="n">
-        <v>5.97725868225098</v>
+        <v>5.97725820541382</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7.34032106399536</v>
       </c>
       <c r="G790" t="n">
-        <v>5.96134042739868</v>
+        <v>5.96133995056152</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>7.26191997528076</v>
       </c>
       <c r="G791" t="n">
-        <v>5.89766836166382</v>
+        <v>5.89766788482666</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>7.34032106399536</v>
       </c>
       <c r="G793" t="n">
-        <v>5.96134042739868</v>
+        <v>5.96133995056152</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>7.34032106399536</v>
       </c>
       <c r="G794" t="n">
-        <v>5.96134042739868</v>
+        <v>5.96133995056152</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>7.20311880111694</v>
       </c>
       <c r="G796" t="n">
-        <v>5.84991312026978</v>
+        <v>5.84991359710693</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G799" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G807" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>7.19331884384155</v>
       </c>
       <c r="G810" t="n">
-        <v>5.84195423126221</v>
+        <v>5.84195470809937</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>7.19331884384155</v>
       </c>
       <c r="G811" t="n">
-        <v>5.84195423126221</v>
+        <v>5.84195470809937</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>7.05611705780029</v>
       </c>
       <c r="G812" t="n">
-        <v>5.73052835464478</v>
+        <v>5.73052787780762</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G813" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G814" t="n">
-        <v>5.7782826423645</v>
+        <v>5.77828216552734</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G815" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G817" t="n">
-        <v>5.77032279968262</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>7.16391801834106</v>
       </c>
       <c r="G818" t="n">
-        <v>5.8180775642395</v>
+        <v>5.81807708740234</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>7.34032106399536</v>
       </c>
       <c r="G819" t="n">
-        <v>5.96134042739868</v>
+        <v>5.96133995056152</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>7.59512615203857</v>
       </c>
       <c r="G822" t="n">
-        <v>6.1682767868042</v>
+        <v>6.16827726364136</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G824" t="n">
-        <v>5.97725868225098</v>
+        <v>5.97725820541382</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G825" t="n">
-        <v>5.97725868225098</v>
+        <v>5.97725820541382</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G826" t="n">
-        <v>5.92950534820557</v>
+        <v>5.92950487136841</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G827" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G831" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>7.33052110671997</v>
       </c>
       <c r="G832" t="n">
-        <v>5.95338153839111</v>
+        <v>5.95338201522827</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>7.33052110671997</v>
       </c>
       <c r="G834" t="n">
-        <v>5.95338153839111</v>
+        <v>5.95338201522827</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>7.33052110671997</v>
       </c>
       <c r="G838" t="n">
-        <v>5.95338153839111</v>
+        <v>5.95338201522827</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>7.33052110671997</v>
       </c>
       <c r="G840" t="n">
-        <v>5.95338153839111</v>
+        <v>5.95338201522827</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>7.29132080078125</v>
       </c>
       <c r="G842" t="n">
-        <v>5.92154598236084</v>
+        <v>5.92154550552368</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G848" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G851" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>7.31092119216919</v>
       </c>
       <c r="G852" t="n">
-        <v>6.03587484359741</v>
+        <v>6.03587532043457</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>7.31092119216919</v>
       </c>
       <c r="G853" t="n">
-        <v>6.03587484359741</v>
+        <v>6.03587532043457</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G854" t="n">
-        <v>5.98732900619507</v>
+        <v>5.98732852935791</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G855" t="n">
-        <v>5.98732900619507</v>
+        <v>5.98732852935791</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G856" t="n">
-        <v>5.87405586242676</v>
+        <v>5.8740553855896</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G857" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G860" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G861" t="n">
-        <v>5.87405586242676</v>
+        <v>5.8740553855896</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G862" t="n">
-        <v>5.84169149398804</v>
+        <v>5.84169101715088</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G864" t="n">
-        <v>5.76078128814697</v>
+        <v>5.76078081130981</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G865" t="n">
-        <v>5.76078128814697</v>
+        <v>5.76078081130981</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G866" t="n">
-        <v>5.74459934234619</v>
+        <v>5.74459886550903</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G868" t="n">
-        <v>5.87405586242676</v>
+        <v>5.8740553855896</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>7.19331884384155</v>
       </c>
       <c r="G870" t="n">
-        <v>5.93878221511841</v>
+        <v>5.93878269195557</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G871" t="n">
-        <v>5.87405586242676</v>
+        <v>5.8740553855896</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>7.23252010345459</v>
       </c>
       <c r="G875" t="n">
-        <v>5.97114753723145</v>
+        <v>5.97114706039429</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G876" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>7.50692415237427</v>
       </c>
       <c r="G877" t="n">
-        <v>6.19769430160522</v>
+        <v>6.19769477844238</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G878" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>7.76172780990601</v>
       </c>
       <c r="G879" t="n">
-        <v>6.40805864334106</v>
+        <v>6.40805912017822</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G880" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G881" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>7.76172780990601</v>
       </c>
       <c r="G882" t="n">
-        <v>6.40805864334106</v>
+        <v>6.40805912017822</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G883" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>7.91853094100952</v>
       </c>
       <c r="G884" t="n">
-        <v>6.53751516342163</v>
+        <v>6.53751564025879</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>7.91853094100952</v>
       </c>
       <c r="G885" t="n">
-        <v>6.53751516342163</v>
+        <v>6.53751564025879</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>7.8597297668457</v>
       </c>
       <c r="G886" t="n">
-        <v>6.48896980285645</v>
+        <v>6.48896932601929</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>7.76172780990601</v>
       </c>
       <c r="G887" t="n">
-        <v>6.40805864334106</v>
+        <v>6.40805912017822</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G888" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G889" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G891" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G894" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G895" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G896" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G897" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G898" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G899" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G900" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>7.82052898406982</v>
       </c>
       <c r="G901" t="n">
-        <v>6.45660543441772</v>
+        <v>6.45660591125488</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>7.80092906951904</v>
       </c>
       <c r="G902" t="n">
-        <v>6.44042348861694</v>
+        <v>6.4404239654541</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.80092906951904</v>
       </c>
       <c r="G903" t="n">
-        <v>6.44042348861694</v>
+        <v>6.4404239654541</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>7.76172780990601</v>
       </c>
       <c r="G904" t="n">
-        <v>6.40805864334106</v>
+        <v>6.40805912017822</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G908" t="n">
-        <v>6.47278785705566</v>
+        <v>6.47278833389282</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>7.68332719802856</v>
       </c>
       <c r="G909" t="n">
-        <v>6.34333229064941</v>
+        <v>6.34333276748657</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.50692415237427</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19769430160522</v>
+        <v>6.19769477844238</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G911" t="n">
-        <v>6.14914846420288</v>
+        <v>6.14914798736572</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>7.27171993255615</v>
       </c>
       <c r="G913" t="n">
-        <v>6.00351095199585</v>
+        <v>6.00351047515869</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>7.50692415237427</v>
       </c>
       <c r="G915" t="n">
-        <v>6.19769430160522</v>
+        <v>6.19769477844238</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>7.42852306365967</v>
       </c>
       <c r="G916" t="n">
-        <v>6.13296699523926</v>
+        <v>6.1329665184021</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G917" t="n">
-        <v>6.14914846420288</v>
+        <v>6.14914798736572</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G919" t="n">
-        <v>5.98732900619507</v>
+        <v>5.98732852935791</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G920" t="n">
-        <v>5.98732900619507</v>
+        <v>5.98732852935791</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.27171993255615</v>
       </c>
       <c r="G922" t="n">
-        <v>6.00351095199585</v>
+        <v>6.00351047515869</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G923" t="n">
-        <v>5.98732900619507</v>
+        <v>5.98732852935791</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G924" t="n">
-        <v>5.84169149398804</v>
+        <v>5.84169101715088</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G927" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G928" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G929" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>7.19331884384155</v>
       </c>
       <c r="G934" t="n">
-        <v>5.93878221511841</v>
+        <v>5.93878269195557</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>7.19331884384155</v>
       </c>
       <c r="G935" t="n">
-        <v>5.93878221511841</v>
+        <v>5.93878269195557</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.11491823196411</v>
       </c>
       <c r="G936" t="n">
-        <v>5.87405586242676</v>
+        <v>5.8740553855896</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G938" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>6.6249098777771</v>
       </c>
       <c r="G939" t="n">
-        <v>5.46950626373291</v>
+        <v>5.46950578689575</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>6.48770713806152</v>
       </c>
       <c r="G940" t="n">
-        <v>5.35623168945312</v>
+        <v>5.35623121261597</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>6.56610918045044</v>
       </c>
       <c r="G942" t="n">
-        <v>5.42095994949341</v>
+        <v>5.42096042633057</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G944" t="n">
-        <v>5.34005069732666</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>6.35050487518311</v>
       </c>
       <c r="G945" t="n">
-        <v>5.2429575920105</v>
+        <v>5.24295806884766</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>6.54650783538818</v>
       </c>
       <c r="G947" t="n">
-        <v>5.40477705001831</v>
+        <v>5.40477752685547</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G953" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>6.35050487518311</v>
       </c>
       <c r="G954" t="n">
-        <v>5.2429575920105</v>
+        <v>5.24295806884766</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G955" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G956" t="n">
-        <v>5.17823028564453</v>
+        <v>5.17822980880737</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G957" t="n">
-        <v>5.17823028564453</v>
+        <v>5.17822980880737</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>6.17410182952881</v>
       </c>
       <c r="G960" t="n">
-        <v>5.09732007980347</v>
+        <v>5.09731960296631</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G961" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>6.29170417785645</v>
       </c>
       <c r="G963" t="n">
-        <v>5.19441223144531</v>
+        <v>5.19441175460815</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G964" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>6.35050487518311</v>
       </c>
       <c r="G966" t="n">
-        <v>5.2429575920105</v>
+        <v>5.24295806884766</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>6.35050487518311</v>
       </c>
       <c r="G967" t="n">
-        <v>5.2429575920105</v>
+        <v>5.24295806884766</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.605309009552</v>
       </c>
       <c r="G969" t="n">
-        <v>5.45332384109497</v>
+        <v>5.45332336425781</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.72291088104248</v>
       </c>
       <c r="G971" t="n">
-        <v>5.5504150390625</v>
+        <v>5.55041551589966</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.72291088104248</v>
       </c>
       <c r="G974" t="n">
-        <v>5.5504150390625</v>
+        <v>5.55041551589966</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>6.7033109664917</v>
       </c>
       <c r="G975" t="n">
-        <v>5.53423309326172</v>
+        <v>5.53423357009888</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G976" t="n">
-        <v>5.43714237213135</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.56610918045044</v>
       </c>
       <c r="G977" t="n">
-        <v>5.42095994949341</v>
+        <v>5.42096042633057</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>6.54650783538818</v>
       </c>
       <c r="G978" t="n">
-        <v>5.40477705001831</v>
+        <v>5.40477752685547</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G980" t="n">
-        <v>5.34005069732666</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G982" t="n">
-        <v>5.34005069732666</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G983" t="n">
-        <v>5.17823028564453</v>
+        <v>5.17822980880737</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G984" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G985" t="n">
-        <v>5.00022840499878</v>
+        <v>5.00022888183594</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G986" t="n">
-        <v>5.0164098739624</v>
+        <v>5.01640939712524</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G987" t="n">
-        <v>5.00022840499878</v>
+        <v>5.00022888183594</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>6.03690004348755</v>
       </c>
       <c r="G989" t="n">
-        <v>4.984046459198</v>
+        <v>4.98404693603516</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G991" t="n">
-        <v>5.0164098739624</v>
+        <v>5.01640939712524</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G995" t="n">
-        <v>5.00022840499878</v>
+        <v>5.00022888183594</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.93889808654785</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.90313625335693</v>
+        <v>4.90313673019409</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.93889808654785</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.90313625335693</v>
+        <v>4.90313673019409</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.00022840499878</v>
+        <v>5.00022888183594</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G1012" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1013" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G1014" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.23290300369263</v>
       </c>
       <c r="G1017" t="n">
-        <v>5.14586591720581</v>
+        <v>5.14586639404297</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G1018" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.0164098739624</v>
+        <v>5.01640939712524</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.0164098739624</v>
+        <v>5.01640939712524</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.23290300369263</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.14586591720581</v>
+        <v>5.14586639404297</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G1024" t="n">
-        <v>5.00022840499878</v>
+        <v>5.00022888183594</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>6.17410182952881</v>
       </c>
       <c r="G1028" t="n">
-        <v>5.09732007980347</v>
+        <v>5.09731960296631</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>6.25250291824341</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.16204738616943</v>
+        <v>5.16204786300659</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.29170417785645</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.19441223144531</v>
+        <v>5.19441175460815</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G1036" t="n">
-        <v>5.17823028564453</v>
+        <v>5.17822980880737</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.17823028564453</v>
+        <v>5.17822980880737</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.43714237213135</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.43714237213135</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.58278036117554</v>
+        <v>5.58277988433838</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.58278036117554</v>
+        <v>5.58277988433838</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.74251079559326</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.56659698486328</v>
+        <v>5.56659650802612</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1050" t="n">
-        <v>5.43714237213135</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.0164098739624</v>
+        <v>5.01640939712524</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.60569286346436</v>
       </c>
       <c r="G1061" t="n">
-        <v>4.62804317474365</v>
+        <v>4.62804412841797</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.3704891204834</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.43385934829712</v>
+        <v>4.43385982513428</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.0960841178894</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.20731258392334</v>
+        <v>4.20731210708618</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.03728294372559</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.15876579284668</v>
+        <v>4.15876531600952</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.80207920074463</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.9645824432373</v>
+        <v>3.96458196640015</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.70407819747925</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.88367366790771</v>
+        <v>3.88367319107056</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.97267293930054</v>
+        <v>3.9726734161377</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.88048076629639</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.02931070327759</v>
+        <v>4.02931022644043</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.80207920074463</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.9645824432373</v>
+        <v>3.96458196640015</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.97267293930054</v>
+        <v>3.9726734161377</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.80207920074463</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.9645824432373</v>
+        <v>3.96458196640015</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.72367811203003</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.89985489845276</v>
+        <v>3.8998544216156</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.97267293930054</v>
+        <v>3.9726734161377</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.88048076629639</v>
       </c>
       <c r="G1090" t="n">
-        <v>4.02931070327759</v>
+        <v>4.02931022644043</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.70407819747925</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.88367366790771</v>
+        <v>3.88367319107056</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.65507698059082</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.84321761131287</v>
+        <v>3.84321784973145</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.70407819747925</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.88367366790771</v>
+        <v>3.88367319107056</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.72367811203003</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.89985489845276</v>
+        <v>3.8998544216156</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.04549264907837</v>
+        <v>4.04549217224121</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.97267293930054</v>
+        <v>3.9726734161377</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.86173391342163</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.01383304595947</v>
+        <v>4.01383256912231</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.7623119354248</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.93175053596497</v>
+        <v>3.93175101280212</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.91144514083862</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.05487442016602</v>
+        <v>4.05487489700317</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.96115589141846</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.0959153175354</v>
+        <v>4.09591579437256</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.05063486099243</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.16978883743286</v>
+        <v>4.16978931427002</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>5.05063486099243</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.16978883743286</v>
+        <v>4.16978931427002</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>5.03075122833252</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.15337371826172</v>
+        <v>4.15337324142456</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.95121288299561</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.08770656585693</v>
+        <v>4.08770704269409</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>5.05063486099243</v>
       </c>
       <c r="G1121" t="n">
-        <v>4.16978883743286</v>
+        <v>4.16978931427002</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.05063486099243</v>
       </c>
       <c r="G1122" t="n">
-        <v>4.16978883743286</v>
+        <v>4.16978931427002</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>5.03075122833252</v>
       </c>
       <c r="G1124" t="n">
-        <v>4.15337371826172</v>
+        <v>4.15337324142456</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>6.8799991607666</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.68010663986206</v>
+        <v>5.68010711669922</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>6.8799991607666</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.68010663986206</v>
+        <v>5.68010711669922</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>6.70103979110718</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.53235816955566</v>
+        <v>5.53235864639282</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>6.48231220245361</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.35177850723267</v>
+        <v>5.35177755355835</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.28611135482788</v>
+        <v>5.28611087799072</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>6.54196500778198</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.4010272026062</v>
+        <v>5.40102672576904</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>6.66127109527588</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.49952507019043</v>
+        <v>5.49952602386475</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>6.66127109527588</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.49952507019043</v>
+        <v>5.49952602386475</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>6.48231220245361</v>
       </c>
       <c r="G1147" t="n">
-        <v>5.35177850723267</v>
+        <v>5.35177755355835</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686122894287</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.10450792312622</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.03986358642578</v>
+        <v>5.03986310958862</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.8460111618042</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.82644987106323</v>
+        <v>4.82644939422607</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.77720022201538</v>
+        <v>4.77719974517822</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.76647281646729</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078271865845</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>5.70682001113892</v>
       </c>
       <c r="G1159" t="n">
-        <v>4.71153402328491</v>
+        <v>4.71153354644775</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1160" t="n">
-        <v>4.77720022201538</v>
+        <v>4.77719974517822</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.84286642074585</v>
+        <v>4.84286546707153</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.7267050743103</v>
       </c>
       <c r="G1163" t="n">
-        <v>4.72795104980469</v>
+        <v>4.72795057296753</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.76647281646729</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078271865845</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.76647281646729</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078271865845</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>5.76647281646729</v>
       </c>
       <c r="G1169" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078271865845</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1178" t="n">
-        <v>5.02344751358032</v>
+        <v>5.02344799041748</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.02344751358032</v>
+        <v>5.02344799041748</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.02497100830078</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.97419786453247</v>
+        <v>4.97419834136963</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.82612705230713</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.81003379821777</v>
+        <v>4.81003332138062</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.8460111618042</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.82644987106323</v>
+        <v>4.82644939422607</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.02344751358032</v>
+        <v>5.02344799041748</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.00703096389771</v>
+        <v>5.00703048706055</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>6.04485511779785</v>
       </c>
       <c r="G1203" t="n">
-        <v>4.99061441421509</v>
+        <v>4.99061393737793</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>6.04485511779785</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.99061441421509</v>
+        <v>4.99061393737793</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>6.10450792312622</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.03986358642578</v>
+        <v>5.03986310958862</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>6.02497100830078</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.97419786453247</v>
+        <v>4.97419834136963</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.00703096389771</v>
+        <v>5.00703048706055</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.84286642074585</v>
+        <v>4.84286546707153</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.84286642074585</v>
+        <v>4.84286546707153</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>5.82612705230713</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.81003379821777</v>
+        <v>4.81003332138062</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.77720022201538</v>
+        <v>4.77719974517822</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>5.34890079498291</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.41603660583496</v>
+        <v>4.41603708267212</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.77720022201538</v>
+        <v>4.77719974517822</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.00703096389771</v>
+        <v>5.00703048706055</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1244" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686122894287</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1247" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1248" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.54196500778198</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.4010272026062</v>
+        <v>5.40102672576904</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.38289022445679</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.26969575881958</v>
+        <v>5.26969528198242</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1258" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1259" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.13836288452148</v>
+        <v>5.13836336135864</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>6.38289022445679</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.26969575881958</v>
+        <v>5.26969528198242</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.28611135482788</v>
+        <v>5.28611087799072</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.48231220245361</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35177850723267</v>
+        <v>5.35177755355835</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1280" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686122894287</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1281" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686122894287</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.02344751358032</v>
+        <v>5.02344799041748</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.84286642074585</v>
+        <v>4.84286546707153</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.00703096389771</v>
+        <v>5.00703048706055</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1294" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>6.64138698577881</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.48310899734497</v>
+        <v>5.48310947418213</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>6.60161781311035</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.45027589797974</v>
+        <v>5.45027637481689</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.20402908325195</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.28611135482788</v>
+        <v>5.28611087799072</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.28611135482788</v>
+        <v>5.28611087799072</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.28611135482788</v>
+        <v>5.28611087799072</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.48231220245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.35177850723267</v>
+        <v>5.35177755355835</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.54196500778198</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.4010272026062</v>
+        <v>5.40102672576904</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1319" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.60161781311035</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45027589797974</v>
+        <v>5.45027637481689</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.70103979110718</v>
       </c>
       <c r="G1321" t="n">
-        <v>5.53235816955566</v>
+        <v>5.53235864639282</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.84023094177246</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.64727354049683</v>
+        <v>5.64727401733398</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>6.86011505126953</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.6636905670166</v>
+        <v>5.66369104385376</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>7.39699411392212</v>
       </c>
       <c r="G1325" t="n">
-        <v>6.10693597793579</v>
+        <v>6.10693693161011</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>7.35722494125366</v>
       </c>
       <c r="G1326" t="n">
-        <v>6.07410287857056</v>
+        <v>6.07410335540771</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>7.39699411392212</v>
       </c>
       <c r="G1327" t="n">
-        <v>6.10693597793579</v>
+        <v>6.10693693161011</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.45168256759644</v>
+        <v>6.45168209075928</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1341" t="n">
-        <v>6.45168256759644</v>
+        <v>6.45168209075928</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>7.83444976806641</v>
       </c>
       <c r="G1342" t="n">
-        <v>6.46809911727905</v>
+        <v>6.46809864044189</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1347" t="n">
-        <v>6.45168256759644</v>
+        <v>6.45168209075928</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>7.85433483123779</v>
       </c>
       <c r="G1348" t="n">
-        <v>6.48451614379883</v>
+        <v>6.48451566696167</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>7.77479696273804</v>
       </c>
       <c r="G1350" t="n">
-        <v>6.41884994506836</v>
+        <v>6.4188494682312</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>7.85433483123779</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.48451614379883</v>
+        <v>6.48451566696167</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.45168256759644</v>
+        <v>6.45168209075928</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>8.07306289672852</v>
       </c>
       <c r="G1355" t="n">
-        <v>6.66509675979614</v>
+        <v>6.6650972366333</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>14.539999961853</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>23957</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G14" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H14" t="n">
         <v>3072</v>
@@ -804,7 +804,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G15" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G16" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H16" t="n">
         <v>716</v>
@@ -891,7 +891,7 @@
         <v>9.56439685821533</v>
       </c>
       <c r="G18" t="n">
-        <v>7.65405893325806</v>
+        <v>7.65405988693237</v>
       </c>
       <c r="H18" t="n">
         <v>307</v>
@@ -920,7 +920,7 @@
         <v>9.56439685821533</v>
       </c>
       <c r="G19" t="n">
-        <v>7.65405893325806</v>
+        <v>7.65405988693237</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G21" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H21" t="n">
         <v>102</v>
@@ -1007,7 +1007,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G22" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>9.6864538192749</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75173616409302</v>
+        <v>7.75173711776733</v>
       </c>
       <c r="H23" t="n">
         <v>2048</v>
@@ -1065,7 +1065,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G24" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H24" t="n">
         <v>1228</v>
@@ -1094,7 +1094,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G25" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>9.54975032806396</v>
       </c>
       <c r="G26" t="n">
-        <v>7.64233922958374</v>
+        <v>7.64233779907227</v>
       </c>
       <c r="H26" t="n">
         <v>512</v>
@@ -1355,7 +1355,7 @@
         <v>9.55951404571533</v>
       </c>
       <c r="G34" t="n">
-        <v>7.65015125274658</v>
+        <v>7.6501522064209</v>
       </c>
       <c r="H34" t="n">
         <v>204</v>
@@ -1616,7 +1616,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G43" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H43" t="n">
         <v>1536</v>
@@ -1790,7 +1790,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G49" t="n">
-        <v>7.79862213134766</v>
+        <v>7.79862117767334</v>
       </c>
       <c r="H49" t="n">
         <v>409</v>
@@ -1819,7 +1819,7 @@
         <v>9.81339263916016</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85332250595093</v>
+        <v>7.85332155227661</v>
       </c>
       <c r="H50" t="n">
         <v>1843</v>
@@ -1877,7 +1877,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G52" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H52" t="n">
         <v>2662</v>
@@ -1993,7 +1993,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G56" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H56" t="n">
         <v>3584</v>
@@ -2022,7 +2022,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G57" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G58" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>9.27634239196777</v>
       </c>
       <c r="G61" t="n">
-        <v>7.42353820800781</v>
+        <v>7.42353868484497</v>
       </c>
       <c r="H61" t="n">
         <v>5632</v>
@@ -2196,7 +2196,7 @@
         <v>9.60833740234375</v>
       </c>
       <c r="G63" t="n">
-        <v>7.68922328948975</v>
+        <v>7.68922424316406</v>
       </c>
       <c r="H63" t="n">
         <v>11470</v>
@@ -2399,7 +2399,7 @@
         <v>9.55951404571533</v>
       </c>
       <c r="G70" t="n">
-        <v>7.65015125274658</v>
+        <v>7.6501522064209</v>
       </c>
       <c r="H70" t="n">
         <v>614</v>
@@ -2428,7 +2428,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G71" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H71" t="n">
         <v>1945</v>
@@ -2457,7 +2457,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G72" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G73" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G74" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G75" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.65227794647217</v>
       </c>
       <c r="G76" t="n">
-        <v>7.72438716888428</v>
+        <v>7.72438812255859</v>
       </c>
       <c r="H76" t="n">
         <v>28060</v>
@@ -2602,7 +2602,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G77" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H77" t="n">
         <v>9319</v>
@@ -2631,7 +2631,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G78" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>9.43257522583008</v>
       </c>
       <c r="G89" t="n">
-        <v>7.54856586456299</v>
+        <v>7.5485668182373</v>
       </c>
       <c r="H89" t="n">
         <v>9933</v>
@@ -2979,7 +2979,7 @@
         <v>9.43257522583008</v>
       </c>
       <c r="G90" t="n">
-        <v>7.54856586456299</v>
+        <v>7.5485668182373</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G99" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H99" t="n">
         <v>12698</v>
@@ -3269,7 +3269,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G100" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>10.0575084686279</v>
       </c>
       <c r="G101" t="n">
-        <v>8.04868125915527</v>
+        <v>8.04868030548096</v>
       </c>
       <c r="H101" t="n">
         <v>2560</v>
@@ -3327,7 +3327,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G102" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H102" t="n">
         <v>512</v>
@@ -3356,7 +3356,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G105" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G106" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>9.43257522583008</v>
       </c>
       <c r="G108" t="n">
-        <v>7.54856586456299</v>
+        <v>7.5485668182373</v>
       </c>
       <c r="H108" t="n">
         <v>614</v>
@@ -3559,7 +3559,7 @@
         <v>9.44722175598145</v>
       </c>
       <c r="G110" t="n">
-        <v>7.5602879524231</v>
+        <v>7.56028890609741</v>
       </c>
       <c r="H110" t="n">
         <v>102</v>
@@ -3588,7 +3588,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G111" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H111" t="n">
         <v>307</v>
@@ -3617,7 +3617,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G112" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>9.43257522583008</v>
       </c>
       <c r="G123" t="n">
-        <v>7.54856586456299</v>
+        <v>7.5485668182373</v>
       </c>
       <c r="H123" t="n">
         <v>614</v>
@@ -4400,7 +4400,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G139" t="n">
-        <v>7.56419324874878</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H139" t="n">
         <v>30723</v>
@@ -4429,7 +4429,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G140" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H140" t="n">
         <v>102</v>
@@ -4458,7 +4458,7 @@
         <v>9.61322021484375</v>
       </c>
       <c r="G141" t="n">
-        <v>7.69313049316406</v>
+        <v>7.69313144683838</v>
       </c>
       <c r="H141" t="n">
         <v>614</v>
@@ -4487,7 +4487,7 @@
         <v>9.61322021484375</v>
       </c>
       <c r="G142" t="n">
-        <v>7.69313049316406</v>
+        <v>7.69313144683838</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>9.50092697143555</v>
       </c>
       <c r="G143" t="n">
-        <v>7.60326719284058</v>
+        <v>7.60326623916626</v>
       </c>
       <c r="H143" t="n">
         <v>6144</v>
@@ -4545,7 +4545,7 @@
         <v>9.50092697143555</v>
       </c>
       <c r="G144" t="n">
-        <v>7.60326719284058</v>
+        <v>7.60326623916626</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.64251327514648</v>
       </c>
       <c r="G149" t="n">
-        <v>7.71657180786133</v>
+        <v>7.71657276153564</v>
       </c>
       <c r="H149" t="n">
         <v>5018</v>
@@ -4719,7 +4719,7 @@
         <v>9.64251327514648</v>
       </c>
       <c r="G150" t="n">
-        <v>7.71657180786133</v>
+        <v>7.71657276153564</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>9.64251327514648</v>
       </c>
       <c r="G151" t="n">
-        <v>7.71657180786133</v>
+        <v>7.71657276153564</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>9.64251327514648</v>
       </c>
       <c r="G152" t="n">
-        <v>7.71657180786133</v>
+        <v>7.71657276153564</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G153" t="n">
-        <v>7.56419324874878</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H153" t="n">
         <v>26217</v>
@@ -4835,7 +4835,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G154" t="n">
-        <v>7.56419324874878</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>9.45210361480713</v>
       </c>
       <c r="G155" t="n">
-        <v>7.56419324874878</v>
+        <v>7.5641942024231</v>
       </c>
       <c r="H155" t="n">
         <v>14952</v>
@@ -5357,7 +5357,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G172" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H172" t="n">
         <v>1740</v>
@@ -5386,7 +5386,7 @@
         <v>9.60833740234375</v>
       </c>
       <c r="G173" t="n">
-        <v>7.68922328948975</v>
+        <v>7.68922424316406</v>
       </c>
       <c r="H173" t="n">
         <v>2150</v>
@@ -5415,7 +5415,7 @@
         <v>9.60833740234375</v>
       </c>
       <c r="G174" t="n">
-        <v>7.68922328948975</v>
+        <v>7.68922424316406</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>9.60833740234375</v>
       </c>
       <c r="G175" t="n">
-        <v>7.68922328948975</v>
+        <v>7.68922424316406</v>
       </c>
       <c r="H175" t="n">
         <v>1024</v>
@@ -5473,7 +5473,7 @@
         <v>9.61322021484375</v>
       </c>
       <c r="G176" t="n">
-        <v>7.69313049316406</v>
+        <v>7.69313144683838</v>
       </c>
       <c r="H176" t="n">
         <v>6144</v>
@@ -5502,7 +5502,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G177" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H177" t="n">
         <v>4096</v>
@@ -5531,7 +5531,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G178" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G179" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G180" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>9.65715980529785</v>
       </c>
       <c r="G181" t="n">
-        <v>7.72829341888428</v>
+        <v>7.72829532623291</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G182" t="n">
-        <v>7.73220062255859</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H182" t="n">
         <v>1126</v>
@@ -5676,7 +5676,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G183" t="n">
-        <v>7.73220062255859</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G184" t="n">
-        <v>7.63452243804932</v>
+        <v>7.63452339172363</v>
       </c>
       <c r="H184" t="n">
         <v>512</v>
@@ -5734,7 +5734,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G185" t="n">
-        <v>7.63452243804932</v>
+        <v>7.63452339172363</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G186" t="n">
-        <v>7.63452243804932</v>
+        <v>7.63452339172363</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>9.53998470306396</v>
       </c>
       <c r="G187" t="n">
-        <v>7.63452243804932</v>
+        <v>7.63452339172363</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G189" t="n">
-        <v>7.73220062255859</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H189" t="n">
         <v>1843</v>
@@ -5879,7 +5879,7 @@
         <v>9.66204166412354</v>
       </c>
       <c r="G190" t="n">
-        <v>7.73220062255859</v>
+        <v>7.73220157623291</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G192" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H192" t="n">
         <v>1126</v>
@@ -6024,7 +6024,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G195" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H195" t="n">
         <v>102</v>
@@ -6053,7 +6053,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G196" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H196" t="n">
         <v>204</v>
@@ -6082,7 +6082,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G197" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G201" t="n">
-        <v>7.81034183502197</v>
+        <v>7.81034374237061</v>
       </c>
       <c r="H201" t="n">
         <v>1945</v>
@@ -6227,7 +6227,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G202" t="n">
-        <v>7.81034183502197</v>
+        <v>7.81034374237061</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G204" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H204" t="n">
         <v>2560</v>
@@ -6314,7 +6314,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G205" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H205" t="n">
         <v>2048</v>
@@ -6343,7 +6343,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G206" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H206" t="n">
         <v>1126</v>
@@ -6372,7 +6372,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G207" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H207" t="n">
         <v>1024</v>
@@ -6401,7 +6401,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G208" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H208" t="n">
         <v>6349</v>
@@ -6430,7 +6430,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G209" t="n">
-        <v>7.79862213134766</v>
+        <v>7.79862117767334</v>
       </c>
       <c r="H209" t="n">
         <v>5530</v>
@@ -6459,7 +6459,7 @@
         <v>9.74504089355469</v>
       </c>
       <c r="G210" t="n">
-        <v>7.79862213134766</v>
+        <v>7.79862117767334</v>
       </c>
       <c r="H210" t="n">
         <v>1433</v>
@@ -6488,7 +6488,7 @@
         <v>9.75968837738037</v>
       </c>
       <c r="G211" t="n">
-        <v>7.81034183502197</v>
+        <v>7.81034374237061</v>
       </c>
       <c r="H211" t="n">
         <v>43115</v>
@@ -7184,7 +7184,7 @@
         <v>9.56927871704102</v>
       </c>
       <c r="G235" t="n">
-        <v>7.65796518325806</v>
+        <v>7.65796709060669</v>
       </c>
       <c r="H235" t="n">
         <v>14337</v>
@@ -7213,7 +7213,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G236" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H236" t="n">
         <v>409</v>
@@ -7271,7 +7271,7 @@
         <v>9.66692543029785</v>
       </c>
       <c r="G238" t="n">
-        <v>7.7361102104187</v>
+        <v>7.73610877990723</v>
       </c>
       <c r="H238" t="n">
         <v>1433</v>
@@ -7358,7 +7358,7 @@
         <v>9.70598316192627</v>
       </c>
       <c r="G241" t="n">
-        <v>7.76736688613892</v>
+        <v>7.7673659324646</v>
       </c>
       <c r="H241" t="n">
         <v>8602</v>
@@ -7387,7 +7387,7 @@
         <v>9.70598316192627</v>
       </c>
       <c r="G242" t="n">
-        <v>7.76736688613892</v>
+        <v>7.7673659324646</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>9.95009708404541</v>
       </c>
       <c r="G250" t="n">
-        <v>7.96272134780884</v>
+        <v>7.96272039413452</v>
       </c>
       <c r="H250" t="n">
         <v>2662</v>
@@ -7648,7 +7648,7 @@
         <v>10.0575084686279</v>
       </c>
       <c r="G251" t="n">
-        <v>8.04868125915527</v>
+        <v>8.04868030548096</v>
       </c>
       <c r="H251" t="n">
         <v>2560</v>
@@ -7677,7 +7677,7 @@
         <v>10.1453886032104</v>
       </c>
       <c r="G252" t="n">
-        <v>8.11900806427002</v>
+        <v>8.11900901794434</v>
       </c>
       <c r="H252" t="n">
         <v>5325</v>
@@ -7706,7 +7706,7 @@
         <v>10.4480895996094</v>
       </c>
       <c r="G253" t="n">
-        <v>8.36124992370605</v>
+        <v>8.36124801635742</v>
       </c>
       <c r="H253" t="n">
         <v>19355</v>
@@ -7764,7 +7764,7 @@
         <v>10.1551532745361</v>
       </c>
       <c r="G255" t="n">
-        <v>8.12682247161865</v>
+        <v>8.12682056427002</v>
       </c>
       <c r="H255" t="n">
         <v>22940</v>
@@ -7822,7 +7822,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G257" t="n">
-        <v>8.15644454956055</v>
+        <v>8.15644359588623</v>
       </c>
       <c r="H257" t="n">
         <v>5101</v>
@@ -7880,7 +7880,7 @@
         <v>10.3685722351074</v>
       </c>
       <c r="G259" t="n">
-        <v>8.2976131439209</v>
+        <v>8.29761409759521</v>
       </c>
       <c r="H259" t="n">
         <v>1326</v>
@@ -7909,7 +7909,7 @@
         <v>10.280369758606</v>
       </c>
       <c r="G260" t="n">
-        <v>8.22702789306641</v>
+        <v>8.22702884674072</v>
       </c>
       <c r="H260" t="n">
         <v>11326</v>
@@ -7967,7 +7967,7 @@
         <v>10.3783721923828</v>
       </c>
       <c r="G262" t="n">
-        <v>8.30545616149902</v>
+        <v>8.30545711517334</v>
       </c>
       <c r="H262" t="n">
         <v>4591</v>
@@ -7996,7 +7996,7 @@
         <v>10.280369758606</v>
       </c>
       <c r="G263" t="n">
-        <v>8.22702789306641</v>
+        <v>8.22702884674072</v>
       </c>
       <c r="H263" t="n">
         <v>816</v>
@@ -8025,7 +8025,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G264" t="n">
-        <v>8.15644454956055</v>
+        <v>8.15644359588623</v>
       </c>
       <c r="H264" t="n">
         <v>17652</v>
@@ -8054,7 +8054,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G265" t="n">
-        <v>8.15644454956055</v>
+        <v>8.15644359588623</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>10.3783721923828</v>
       </c>
       <c r="G266" t="n">
-        <v>8.30545616149902</v>
+        <v>8.30545711517334</v>
       </c>
       <c r="H266" t="n">
         <v>24693</v>
@@ -8141,7 +8141,7 @@
         <v>10.6919765472412</v>
       </c>
       <c r="G268" t="n">
-        <v>8.55642318725586</v>
+        <v>8.55642127990723</v>
       </c>
       <c r="H268" t="n">
         <v>26122</v>
@@ -8170,7 +8170,7 @@
         <v>10.5939750671387</v>
       </c>
       <c r="G269" t="n">
-        <v>8.47799682617188</v>
+        <v>8.47799491882324</v>
       </c>
       <c r="H269" t="n">
         <v>5306</v>
@@ -8228,7 +8228,7 @@
         <v>10.6821765899658</v>
       </c>
       <c r="G271" t="n">
-        <v>8.54858016967773</v>
+        <v>8.54858112335205</v>
       </c>
       <c r="H271" t="n">
         <v>8877</v>
@@ -8257,7 +8257,7 @@
         <v>10.7801790237427</v>
       </c>
       <c r="G272" t="n">
-        <v>8.62700748443604</v>
+        <v>8.62700843811035</v>
       </c>
       <c r="H272" t="n">
         <v>23366</v>
@@ -8286,7 +8286,7 @@
         <v>10.6919765472412</v>
       </c>
       <c r="G273" t="n">
-        <v>8.55642318725586</v>
+        <v>8.55642127990723</v>
       </c>
       <c r="H273" t="n">
         <v>24081</v>
@@ -8315,7 +8315,7 @@
         <v>10.770378112793</v>
       </c>
       <c r="G274" t="n">
-        <v>8.61916351318359</v>
+        <v>8.61916542053223</v>
       </c>
       <c r="H274" t="n">
         <v>15714</v>
@@ -8344,7 +8344,7 @@
         <v>10.6821765899658</v>
       </c>
       <c r="G275" t="n">
-        <v>8.54858016967773</v>
+        <v>8.54858112335205</v>
       </c>
       <c r="H275" t="n">
         <v>8979</v>
@@ -8460,7 +8460,7 @@
         <v>10.7507781982422</v>
       </c>
       <c r="G279" t="n">
-        <v>8.60348033905029</v>
+        <v>8.60347938537598</v>
       </c>
       <c r="H279" t="n">
         <v>3673</v>
@@ -8489,7 +8489,7 @@
         <v>10.9761819839478</v>
       </c>
       <c r="G280" t="n">
-        <v>8.78386211395264</v>
+        <v>8.78386306762695</v>
       </c>
       <c r="H280" t="n">
         <v>26224</v>
@@ -8518,7 +8518,7 @@
         <v>10.9761819839478</v>
       </c>
       <c r="G281" t="n">
-        <v>8.78386211395264</v>
+        <v>8.78386306762695</v>
       </c>
       <c r="H281" t="n">
         <v>13673</v>
@@ -8547,7 +8547,7 @@
         <v>10.9369812011719</v>
       </c>
       <c r="G282" t="n">
-        <v>8.75249195098877</v>
+        <v>8.75249099731445</v>
       </c>
       <c r="H282" t="n">
         <v>30305</v>
@@ -8605,7 +8605,7 @@
         <v>11.0055818557739</v>
       </c>
       <c r="G284" t="n">
-        <v>8.8073902130127</v>
+        <v>8.80739116668701</v>
       </c>
       <c r="H284" t="n">
         <v>11020</v>
@@ -8634,7 +8634,7 @@
         <v>11.025182723999</v>
       </c>
       <c r="G285" t="n">
-        <v>8.82307624816895</v>
+        <v>8.82307529449463</v>
       </c>
       <c r="H285" t="n">
         <v>5203</v>
@@ -8663,7 +8663,7 @@
         <v>11.0349826812744</v>
       </c>
       <c r="G286" t="n">
-        <v>8.83091926574707</v>
+        <v>8.83091831207275</v>
       </c>
       <c r="H286" t="n">
         <v>9081</v>
@@ -8692,7 +8692,7 @@
         <v>11.025182723999</v>
       </c>
       <c r="G287" t="n">
-        <v>8.82307624816895</v>
+        <v>8.82307529449463</v>
       </c>
       <c r="H287" t="n">
         <v>35611</v>
@@ -8808,7 +8808,7 @@
         <v>10.6723766326904</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54073619842529</v>
+        <v>8.54073715209961</v>
       </c>
       <c r="H291" t="n">
         <v>45611</v>
@@ -8837,7 +8837,7 @@
         <v>10.5155744552612</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41525363922119</v>
+        <v>8.41525459289551</v>
       </c>
       <c r="H292" t="n">
         <v>20918</v>
@@ -8895,7 +8895,7 @@
         <v>10.4371728897095</v>
       </c>
       <c r="G294" t="n">
-        <v>8.35251331329346</v>
+        <v>8.35251235961914</v>
       </c>
       <c r="H294" t="n">
         <v>6836</v>
@@ -9098,7 +9098,7 @@
         <v>10.5743751525879</v>
       </c>
       <c r="G301" t="n">
-        <v>8.46230888366699</v>
+        <v>8.46230983734131</v>
       </c>
       <c r="H301" t="n">
         <v>9489</v>
@@ -9243,7 +9243,7 @@
         <v>10.3391714096069</v>
       </c>
       <c r="G306" t="n">
-        <v>8.27408409118652</v>
+        <v>8.27408504486084</v>
       </c>
       <c r="H306" t="n">
         <v>20305</v>
@@ -9272,7 +9272,7 @@
         <v>10.280369758606</v>
       </c>
       <c r="G307" t="n">
-        <v>8.22702789306641</v>
+        <v>8.22702884674072</v>
       </c>
       <c r="H307" t="n">
         <v>7857</v>
@@ -9330,7 +9330,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G309" t="n">
-        <v>8.21134281158447</v>
+        <v>8.21134090423584</v>
       </c>
       <c r="H309" t="n">
         <v>67549</v>
@@ -9417,7 +9417,7 @@
         <v>10.2411699295044</v>
       </c>
       <c r="G312" t="n">
-        <v>8.19565677642822</v>
+        <v>8.19565773010254</v>
       </c>
       <c r="H312" t="n">
         <v>12652</v>
@@ -9446,7 +9446,7 @@
         <v>10.2411699295044</v>
       </c>
       <c r="G313" t="n">
-        <v>8.19565677642822</v>
+        <v>8.19565773010254</v>
       </c>
       <c r="H313" t="n">
         <v>14081</v>
@@ -9504,7 +9504,7 @@
         <v>10.1823692321777</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14860057830811</v>
+        <v>8.14860153198242</v>
       </c>
       <c r="H315" t="n">
         <v>166323</v>
@@ -9533,7 +9533,7 @@
         <v>10.3979721069336</v>
       </c>
       <c r="G316" t="n">
-        <v>8.32114124298096</v>
+        <v>8.32114028930664</v>
       </c>
       <c r="H316" t="n">
         <v>34489</v>
@@ -9620,7 +9620,7 @@
         <v>10.7605781555176</v>
       </c>
       <c r="G319" t="n">
-        <v>8.61132144927979</v>
+        <v>8.6113224029541</v>
       </c>
       <c r="H319" t="n">
         <v>75917</v>
@@ -9649,7 +9649,7 @@
         <v>10.7997789382935</v>
       </c>
       <c r="G320" t="n">
-        <v>8.64269351959229</v>
+        <v>8.64269256591797</v>
       </c>
       <c r="H320" t="n">
         <v>37754</v>
@@ -9678,7 +9678,7 @@
         <v>10.9761819839478</v>
       </c>
       <c r="G321" t="n">
-        <v>8.78386211395264</v>
+        <v>8.78386306762695</v>
       </c>
       <c r="H321" t="n">
         <v>130814</v>
@@ -9707,7 +9707,7 @@
         <v>10.9075813293457</v>
       </c>
       <c r="G322" t="n">
-        <v>8.72896480560303</v>
+        <v>8.72896575927734</v>
       </c>
       <c r="H322" t="n">
         <v>24999</v>
@@ -9794,7 +9794,7 @@
         <v>11.0741834640503</v>
       </c>
       <c r="G325" t="n">
-        <v>8.86229038238525</v>
+        <v>8.86229133605957</v>
       </c>
       <c r="H325" t="n">
         <v>46019</v>
@@ -9823,7 +9823,7 @@
         <v>11.2701873779297</v>
       </c>
       <c r="G326" t="n">
-        <v>9.01914501190186</v>
+        <v>9.01914405822754</v>
       </c>
       <c r="H326" t="n">
         <v>53570</v>
@@ -9852,7 +9852,7 @@
         <v>11.4171886444092</v>
       </c>
       <c r="G327" t="n">
-        <v>9.13678550720215</v>
+        <v>9.13678455352783</v>
       </c>
       <c r="H327" t="n">
         <v>72345</v>
@@ -9910,7 +9910,7 @@
         <v>11.5543909072876</v>
       </c>
       <c r="G329" t="n">
-        <v>9.24658298492432</v>
+        <v>9.24658393859863</v>
       </c>
       <c r="H329" t="n">
         <v>34795</v>
@@ -9968,7 +9968,7 @@
         <v>11.7111940383911</v>
       </c>
       <c r="G331" t="n">
-        <v>9.37206745147705</v>
+        <v>9.37206840515137</v>
       </c>
       <c r="H331" t="n">
         <v>192445</v>
@@ -9997,7 +9997,7 @@
         <v>11.87779712677</v>
       </c>
       <c r="G332" t="n">
-        <v>9.50539493560791</v>
+        <v>9.50539398193359</v>
       </c>
       <c r="H332" t="n">
         <v>43570</v>
@@ -10026,7 +10026,7 @@
         <v>12.0542001724243</v>
       </c>
       <c r="G333" t="n">
-        <v>9.64656257629395</v>
+        <v>9.64656352996826</v>
       </c>
       <c r="H333" t="n">
         <v>79794</v>
@@ -10084,7 +10084,7 @@
         <v>12.3482046127319</v>
       </c>
       <c r="G335" t="n">
-        <v>9.88184547424316</v>
+        <v>9.88184452056885</v>
       </c>
       <c r="H335" t="n">
         <v>161629</v>
@@ -10142,7 +10142,7 @@
         <v>12.7696123123169</v>
       </c>
       <c r="G337" t="n">
-        <v>10.2190847396851</v>
+        <v>10.2190837860107</v>
       </c>
       <c r="H337" t="n">
         <v>73468</v>
@@ -10171,7 +10171,7 @@
         <v>12.7696123123169</v>
       </c>
       <c r="G338" t="n">
-        <v>10.2190847396851</v>
+        <v>10.2190837860107</v>
       </c>
       <c r="H338" t="n">
         <v>133773</v>
@@ -10229,7 +10229,7 @@
         <v>12.5344076156616</v>
       </c>
       <c r="G340" t="n">
-        <v>10.0308570861816</v>
+        <v>10.030858039856</v>
       </c>
       <c r="H340" t="n">
         <v>28979</v>
@@ -10258,7 +10258,7 @@
         <v>12.6814098358154</v>
       </c>
       <c r="G341" t="n">
-        <v>10.1484985351562</v>
+        <v>10.1484975814819</v>
       </c>
       <c r="H341" t="n">
         <v>47346</v>
@@ -10287,7 +10287,7 @@
         <v>12.603009223938</v>
       </c>
       <c r="G342" t="n">
-        <v>10.0857563018799</v>
+        <v>10.0857572555542</v>
       </c>
       <c r="H342" t="n">
         <v>8979</v>
@@ -10316,7 +10316,7 @@
         <v>12.7304105758667</v>
       </c>
       <c r="G343" t="n">
-        <v>10.1877117156982</v>
+        <v>10.1877107620239</v>
       </c>
       <c r="H343" t="n">
         <v>37958</v>
@@ -10345,7 +10345,7 @@
         <v>12.7500114440918</v>
       </c>
       <c r="G344" t="n">
-        <v>10.2033967971802</v>
+        <v>10.2033977508545</v>
       </c>
       <c r="H344" t="n">
         <v>61529</v>
@@ -10403,7 +10403,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H346" t="n">
         <v>117549</v>
@@ -10432,7 +10432,7 @@
         <v>13.1028165817261</v>
       </c>
       <c r="G347" t="n">
-        <v>10.4857339859009</v>
+        <v>10.4857349395752</v>
       </c>
       <c r="H347" t="n">
         <v>112957</v>
@@ -10490,7 +10490,7 @@
         <v>12.8676128387451</v>
       </c>
       <c r="G349" t="n">
-        <v>10.297511100769</v>
+        <v>10.2975101470947</v>
       </c>
       <c r="H349" t="n">
         <v>66223</v>
@@ -10577,7 +10577,7 @@
         <v>12.7402105331421</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1955547332764</v>
+        <v>10.1955537796021</v>
       </c>
       <c r="H352" t="n">
         <v>70917</v>
@@ -10606,7 +10606,7 @@
         <v>12.67160987854</v>
       </c>
       <c r="G353" t="n">
-        <v>10.1406555175781</v>
+        <v>10.1406545639038</v>
       </c>
       <c r="H353" t="n">
         <v>58060</v>
@@ -10722,7 +10722,7 @@
         <v>12.6618099212646</v>
       </c>
       <c r="G357" t="n">
-        <v>10.1328115463257</v>
+        <v>10.1328134536743</v>
       </c>
       <c r="H357" t="n">
         <v>38570</v>
@@ -10751,7 +10751,7 @@
         <v>12.603009223938</v>
       </c>
       <c r="G358" t="n">
-        <v>10.0857563018799</v>
+        <v>10.0857572555542</v>
       </c>
       <c r="H358" t="n">
         <v>75610</v>
@@ -10780,7 +10780,7 @@
         <v>12.7402105331421</v>
       </c>
       <c r="G359" t="n">
-        <v>10.1955547332764</v>
+        <v>10.1955537796021</v>
       </c>
       <c r="H359" t="n">
         <v>88059</v>
@@ -10809,7 +10809,7 @@
         <v>13.034215927124</v>
       </c>
       <c r="G360" t="n">
-        <v>10.430835723877</v>
+        <v>10.4308366775513</v>
       </c>
       <c r="H360" t="n">
         <v>156119</v>
@@ -10867,7 +10867,7 @@
         <v>12.965615272522</v>
       </c>
       <c r="G362" t="n">
-        <v>10.3759384155273</v>
+        <v>10.3759393692017</v>
       </c>
       <c r="H362" t="n">
         <v>25509</v>
@@ -10925,7 +10925,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H364" t="n">
         <v>75917</v>
@@ -10954,7 +10954,7 @@
         <v>13.1126165390015</v>
       </c>
       <c r="G365" t="n">
-        <v>10.4935779571533</v>
+        <v>10.493577003479</v>
       </c>
       <c r="H365" t="n">
         <v>53366</v>
@@ -10983,7 +10983,7 @@
         <v>12.8578128814697</v>
       </c>
       <c r="G366" t="n">
-        <v>10.2896680831909</v>
+        <v>10.2896671295166</v>
       </c>
       <c r="H366" t="n">
         <v>31428</v>
@@ -11012,7 +11012,7 @@
         <v>12.7696123123169</v>
       </c>
       <c r="G367" t="n">
-        <v>10.2190847396851</v>
+        <v>10.2190837860107</v>
       </c>
       <c r="H367" t="n">
         <v>14897</v>
@@ -11041,7 +11041,7 @@
         <v>12.9362144470215</v>
       </c>
       <c r="G368" t="n">
-        <v>10.3524084091187</v>
+        <v>10.352409362793</v>
       </c>
       <c r="H368" t="n">
         <v>38774</v>
@@ -11070,7 +11070,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G369" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H369" t="n">
         <v>128977</v>
@@ -11099,7 +11099,7 @@
         <v>13.1126165390015</v>
       </c>
       <c r="G370" t="n">
-        <v>10.4935779571533</v>
+        <v>10.493577003479</v>
       </c>
       <c r="H370" t="n">
         <v>107753</v>
@@ -11244,7 +11244,7 @@
         <v>13.7300281524658</v>
       </c>
       <c r="G375" t="n">
-        <v>10.9876699447632</v>
+        <v>10.9876718521118</v>
       </c>
       <c r="H375" t="n">
         <v>105916</v>
@@ -11273,7 +11273,7 @@
         <v>13.6614255905151</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9327716827393</v>
+        <v>10.9327707290649</v>
       </c>
       <c r="H376" t="n">
         <v>129181</v>
@@ -11302,7 +11302,7 @@
         <v>13.6418256759644</v>
       </c>
       <c r="G377" t="n">
-        <v>10.917085647583</v>
+        <v>10.9170866012573</v>
       </c>
       <c r="H377" t="n">
         <v>13367</v>
@@ -11331,7 +11331,7 @@
         <v>13.6516256332397</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9249296188354</v>
+        <v>10.9249277114868</v>
       </c>
       <c r="H378" t="n">
         <v>11020</v>
@@ -11447,7 +11447,7 @@
         <v>13.1028165817261</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4857339859009</v>
+        <v>10.4857349395752</v>
       </c>
       <c r="H382" t="n">
         <v>20611</v>
@@ -11650,7 +11650,7 @@
         <v>12.2992038726807</v>
       </c>
       <c r="G389" t="n">
-        <v>9.84263229370117</v>
+        <v>9.84263038635254</v>
       </c>
       <c r="H389" t="n">
         <v>59590</v>
@@ -11679,7 +11679,7 @@
         <v>12.3482046127319</v>
       </c>
       <c r="G390" t="n">
-        <v>9.88184547424316</v>
+        <v>9.88184452056885</v>
       </c>
       <c r="H390" t="n">
         <v>43978</v>
@@ -11737,7 +11737,7 @@
         <v>12.3286037445068</v>
       </c>
       <c r="G392" t="n">
-        <v>9.86615943908691</v>
+        <v>9.86616039276123</v>
       </c>
       <c r="H392" t="n">
         <v>31121</v>
@@ -11795,7 +11795,7 @@
         <v>12.603009223938</v>
       </c>
       <c r="G394" t="n">
-        <v>10.0857563018799</v>
+        <v>10.0857572555542</v>
       </c>
       <c r="H394" t="n">
         <v>8775</v>
@@ -11853,7 +11853,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G396" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H396" t="n">
         <v>26734</v>
@@ -11882,7 +11882,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G397" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H397" t="n">
         <v>1530</v>
@@ -11911,7 +11911,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G398" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H398" t="n">
         <v>14693</v>
@@ -11940,7 +11940,7 @@
         <v>12.4168062210083</v>
       </c>
       <c r="G399" t="n">
-        <v>9.93674468994141</v>
+        <v>9.93674373626709</v>
       </c>
       <c r="H399" t="n">
         <v>2653</v>
@@ -11998,7 +11998,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G401" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H401" t="n">
         <v>2550</v>
@@ -12027,7 +12027,7 @@
         <v>12.2992038726807</v>
       </c>
       <c r="G402" t="n">
-        <v>9.84263229370117</v>
+        <v>9.84263038635254</v>
       </c>
       <c r="H402" t="n">
         <v>40917</v>
@@ -12056,7 +12056,7 @@
         <v>12.2698030471802</v>
       </c>
       <c r="G403" t="n">
-        <v>9.81910419464111</v>
+        <v>9.8191032409668</v>
       </c>
       <c r="H403" t="n">
         <v>29795</v>
@@ -12143,7 +12143,7 @@
         <v>12.603009223938</v>
       </c>
       <c r="G406" t="n">
-        <v>10.0857563018799</v>
+        <v>10.0857572555542</v>
       </c>
       <c r="H406" t="n">
         <v>11734</v>
@@ -12230,7 +12230,7 @@
         <v>12.4462060928345</v>
       </c>
       <c r="G409" t="n">
-        <v>9.96027278900146</v>
+        <v>9.96027183532715</v>
       </c>
       <c r="H409" t="n">
         <v>14999</v>
@@ -12259,7 +12259,7 @@
         <v>12.4168062210083</v>
       </c>
       <c r="G410" t="n">
-        <v>9.93674468994141</v>
+        <v>9.93674373626709</v>
       </c>
       <c r="H410" t="n">
         <v>13367</v>
@@ -12346,7 +12346,7 @@
         <v>12.4854068756104</v>
       </c>
       <c r="G413" t="n">
-        <v>9.99164390563965</v>
+        <v>9.99164295196533</v>
       </c>
       <c r="H413" t="n">
         <v>126426</v>
@@ -12375,7 +12375,7 @@
         <v>12.5834093093872</v>
       </c>
       <c r="G414" t="n">
-        <v>10.0700721740723</v>
+        <v>10.0700712203979</v>
       </c>
       <c r="H414" t="n">
         <v>103773</v>
@@ -12433,7 +12433,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G416" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H416" t="n">
         <v>59386</v>
@@ -12491,7 +12491,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G418" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H418" t="n">
         <v>18265</v>
@@ -12520,7 +12520,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G419" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H419" t="n">
         <v>29285</v>
@@ -12549,7 +12549,7 @@
         <v>13.1616182327271</v>
       </c>
       <c r="G420" t="n">
-        <v>10.5327930450439</v>
+        <v>10.5327920913696</v>
       </c>
       <c r="H420" t="n">
         <v>54590</v>
@@ -12665,7 +12665,7 @@
         <v>13.2302188873291</v>
       </c>
       <c r="G424" t="n">
-        <v>10.5876903533936</v>
+        <v>10.5876913070679</v>
       </c>
       <c r="H424" t="n">
         <v>26428</v>
@@ -12694,7 +12694,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G425" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H425" t="n">
         <v>29693</v>
@@ -12723,7 +12723,7 @@
         <v>13.328221321106</v>
       </c>
       <c r="G426" t="n">
-        <v>10.6661195755005</v>
+        <v>10.6661186218262</v>
       </c>
       <c r="H426" t="n">
         <v>23366</v>
@@ -12781,7 +12781,7 @@
         <v>13.4262218475342</v>
       </c>
       <c r="G428" t="n">
-        <v>10.7445440292358</v>
+        <v>10.7445449829102</v>
       </c>
       <c r="H428" t="n">
         <v>24081</v>
@@ -12810,7 +12810,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G429" t="n">
-        <v>10.7759170532227</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H429" t="n">
         <v>18877</v>
@@ -12897,7 +12897,7 @@
         <v>13.396821975708</v>
       </c>
       <c r="G432" t="n">
-        <v>10.7210178375244</v>
+        <v>10.7210168838501</v>
       </c>
       <c r="H432" t="n">
         <v>6836</v>
@@ -12926,7 +12926,7 @@
         <v>13.4360227584839</v>
       </c>
       <c r="G433" t="n">
-        <v>10.7523889541626</v>
+        <v>10.7523899078369</v>
       </c>
       <c r="H433" t="n">
         <v>25203</v>
@@ -12955,7 +12955,7 @@
         <v>13.4262218475342</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7445440292358</v>
+        <v>10.7445449829102</v>
       </c>
       <c r="H434" t="n">
         <v>11836</v>
@@ -12984,7 +12984,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G435" t="n">
-        <v>10.7759170532227</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H435" t="n">
         <v>41325</v>
@@ -13013,7 +13013,7 @@
         <v>13.4654226303101</v>
       </c>
       <c r="G436" t="n">
-        <v>10.7759170532227</v>
+        <v>10.7759160995483</v>
       </c>
       <c r="H436" t="n">
         <v>18162</v>
@@ -13042,7 +13042,7 @@
         <v>13.524224281311</v>
       </c>
       <c r="G437" t="n">
-        <v>10.8229732513428</v>
+        <v>10.8229742050171</v>
       </c>
       <c r="H437" t="n">
         <v>59182</v>
@@ -13071,7 +13071,7 @@
         <v>13.396821975708</v>
       </c>
       <c r="G438" t="n">
-        <v>10.7210178375244</v>
+        <v>10.7210168838501</v>
       </c>
       <c r="H438" t="n">
         <v>62345</v>
@@ -13158,7 +13158,7 @@
         <v>13.1322183609009</v>
       </c>
       <c r="G441" t="n">
-        <v>10.5092639923096</v>
+        <v>10.5092668533325</v>
       </c>
       <c r="H441" t="n">
         <v>68876</v>
@@ -13187,7 +13187,7 @@
         <v>12.9362144470215</v>
       </c>
       <c r="G442" t="n">
-        <v>10.3524084091187</v>
+        <v>10.352409362793</v>
       </c>
       <c r="H442" t="n">
         <v>58468</v>
@@ -13245,7 +13245,7 @@
         <v>12.5834093093872</v>
       </c>
       <c r="G444" t="n">
-        <v>10.0700721740723</v>
+        <v>10.0700712203979</v>
       </c>
       <c r="H444" t="n">
         <v>50509</v>
@@ -13274,7 +13274,7 @@
         <v>12.2110023498535</v>
       </c>
       <c r="G445" t="n">
-        <v>9.77204608917236</v>
+        <v>9.77204704284668</v>
       </c>
       <c r="H445" t="n">
         <v>81733</v>
@@ -13448,7 +13448,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G451" t="n">
-        <v>7.92116260528564</v>
+        <v>7.92116355895996</v>
       </c>
       <c r="H451" t="n">
         <v>146936</v>
@@ -13506,7 +13506,7 @@
         <v>10.0157661437988</v>
       </c>
       <c r="G453" t="n">
-        <v>8.0152759552002</v>
+        <v>8.01527500152588</v>
       </c>
       <c r="H453" t="n">
         <v>54284</v>
@@ -13535,7 +13535,7 @@
         <v>9.85896301269531</v>
       </c>
       <c r="G454" t="n">
-        <v>7.88978958129883</v>
+        <v>7.88979053497314</v>
       </c>
       <c r="H454" t="n">
         <v>102345</v>
@@ -13564,7 +13564,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G455" t="n">
-        <v>8.15644454956055</v>
+        <v>8.15644359588623</v>
       </c>
       <c r="H455" t="n">
         <v>116630</v>
@@ -13622,7 +13622,7 @@
         <v>10.0549669265747</v>
       </c>
       <c r="G457" t="n">
-        <v>8.04664516448975</v>
+        <v>8.04664421081543</v>
       </c>
       <c r="H457" t="n">
         <v>39897</v>
@@ -13709,7 +13709,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G460" t="n">
-        <v>8.21134281158447</v>
+        <v>8.21134090423584</v>
       </c>
       <c r="H460" t="n">
         <v>111018</v>
@@ -13738,7 +13738,7 @@
         <v>10.2313690185547</v>
       </c>
       <c r="G461" t="n">
-        <v>8.1878137588501</v>
+        <v>8.18781471252441</v>
       </c>
       <c r="H461" t="n">
         <v>56937</v>
@@ -13767,7 +13767,7 @@
         <v>10.1921691894531</v>
       </c>
       <c r="G462" t="n">
-        <v>8.15644454956055</v>
+        <v>8.15644359588623</v>
       </c>
       <c r="H462" t="n">
         <v>45713</v>
@@ -13796,7 +13796,7 @@
         <v>10.3391714096069</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27408409118652</v>
+        <v>8.27408504486084</v>
       </c>
       <c r="H463" t="n">
         <v>55713</v>
@@ -13970,7 +13970,7 @@
         <v>10.280369758606</v>
       </c>
       <c r="G469" t="n">
-        <v>8.22702789306641</v>
+        <v>8.22702884674072</v>
       </c>
       <c r="H469" t="n">
         <v>41938</v>
@@ -14028,7 +14028,7 @@
         <v>10.2607698440552</v>
       </c>
       <c r="G471" t="n">
-        <v>8.21134281158447</v>
+        <v>8.21134090423584</v>
       </c>
       <c r="H471" t="n">
         <v>9489</v>
@@ -14086,7 +14086,7 @@
         <v>10.4371728897095</v>
       </c>
       <c r="G473" t="n">
-        <v>8.35251331329346</v>
+        <v>8.35251235961914</v>
       </c>
       <c r="H473" t="n">
         <v>14693</v>
@@ -14144,7 +14144,7 @@
         <v>10.5547752380371</v>
       </c>
       <c r="G475" t="n">
-        <v>8.44662570953369</v>
+        <v>8.44662666320801</v>
       </c>
       <c r="H475" t="n">
         <v>21530</v>
@@ -14231,7 +14231,7 @@
         <v>10.0157661437988</v>
       </c>
       <c r="G478" t="n">
-        <v>8.0152759552002</v>
+        <v>8.01527500152588</v>
       </c>
       <c r="H478" t="n">
         <v>22244</v>
@@ -14260,7 +14260,7 @@
         <v>9.99616622924805</v>
       </c>
       <c r="G479" t="n">
-        <v>7.9995903968811</v>
+        <v>7.99958944320679</v>
       </c>
       <c r="H479" t="n">
         <v>14183</v>
@@ -14318,7 +14318,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G481" t="n">
-        <v>7.92116260528564</v>
+        <v>7.92116355895996</v>
       </c>
       <c r="H481" t="n">
         <v>38570</v>
@@ -14347,7 +14347,7 @@
         <v>9.94716453552246</v>
       </c>
       <c r="G482" t="n">
-        <v>7.960373878479</v>
+        <v>7.96037483215332</v>
       </c>
       <c r="H482" t="n">
         <v>6938</v>
@@ -14376,7 +14376,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G483" t="n">
-        <v>7.92116260528564</v>
+        <v>7.92116355895996</v>
       </c>
       <c r="H483" t="n">
         <v>9489</v>
@@ -14405,7 +14405,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G484" t="n">
-        <v>7.88194704055786</v>
+        <v>7.88194799423218</v>
       </c>
       <c r="H484" t="n">
         <v>39285</v>
@@ -14434,7 +14434,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G485" t="n">
-        <v>7.88194704055786</v>
+        <v>7.88194799423218</v>
       </c>
       <c r="H485" t="n">
         <v>10305</v>
@@ -14463,7 +14463,7 @@
         <v>9.84916305541992</v>
       </c>
       <c r="G486" t="n">
-        <v>7.88194704055786</v>
+        <v>7.88194799423218</v>
       </c>
       <c r="H486" t="n">
         <v>24387</v>
@@ -14492,7 +14492,7 @@
         <v>9.8687629699707</v>
       </c>
       <c r="G487" t="n">
-        <v>7.89763355255127</v>
+        <v>7.89763259887695</v>
       </c>
       <c r="H487" t="n">
         <v>4999</v>
@@ -14521,7 +14521,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G488" t="n">
-        <v>7.92116260528564</v>
+        <v>7.92116355895996</v>
       </c>
       <c r="H488" t="n">
         <v>25611</v>
@@ -14608,7 +14608,7 @@
         <v>9.89816379547119</v>
       </c>
       <c r="G491" t="n">
-        <v>7.92116260528564</v>
+        <v>7.92116355895996</v>
       </c>
       <c r="H491" t="n">
         <v>12550</v>
@@ -14666,7 +14666,7 @@
         <v>9.82956314086914</v>
       </c>
       <c r="G493" t="n">
-        <v>7.86626386642456</v>
+        <v>7.86626291275024</v>
       </c>
       <c r="H493" t="n">
         <v>13571</v>
@@ -14695,7 +14695,7 @@
         <v>9.83936309814453</v>
       </c>
       <c r="G494" t="n">
-        <v>7.87410593032837</v>
+        <v>7.87410688400269</v>
       </c>
       <c r="H494" t="n">
         <v>25407</v>
@@ -14724,7 +14724,7 @@
         <v>9.78546237945557</v>
       </c>
       <c r="G495" t="n">
-        <v>7.830970287323</v>
+        <v>7.83096933364868</v>
       </c>
       <c r="H495" t="n">
         <v>20509</v>
@@ -14782,7 +14782,7 @@
         <v>9.51595783233643</v>
       </c>
       <c r="G497" t="n">
-        <v>7.61529588699341</v>
+        <v>7.61529493331909</v>
       </c>
       <c r="H497" t="n">
         <v>36632</v>
@@ -14898,7 +14898,7 @@
         <v>9.56495761871338</v>
       </c>
       <c r="G501" t="n">
-        <v>7.65450763702393</v>
+        <v>7.65450859069824</v>
       </c>
       <c r="H501" t="n">
         <v>6122</v>
@@ -14927,7 +14927,7 @@
         <v>9.45715713500977</v>
       </c>
       <c r="G502" t="n">
-        <v>7.56823921203613</v>
+        <v>7.56824016571045</v>
       </c>
       <c r="H502" t="n">
         <v>36325</v>
@@ -14985,7 +14985,7 @@
         <v>9.192551612854</v>
       </c>
       <c r="G504" t="n">
-        <v>7.35648441314697</v>
+        <v>7.35648488998413</v>
       </c>
       <c r="H504" t="n">
         <v>38570</v>
@@ -15014,7 +15014,7 @@
         <v>9.12395095825195</v>
       </c>
       <c r="G505" t="n">
-        <v>7.30158472061157</v>
+        <v>7.30158615112305</v>
       </c>
       <c r="H505" t="n">
         <v>75508</v>
@@ -15043,7 +15043,7 @@
         <v>9.01614856719971</v>
       </c>
       <c r="G506" t="n">
-        <v>7.21531534194946</v>
+        <v>7.21531581878662</v>
       </c>
       <c r="H506" t="n">
         <v>55509</v>
@@ -15101,7 +15101,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G508" t="n">
-        <v>7.33295583724976</v>
+        <v>7.33295631408691</v>
       </c>
       <c r="H508" t="n">
         <v>7857</v>
@@ -15130,7 +15130,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G509" t="n">
-        <v>7.33295583724976</v>
+        <v>7.33295631408691</v>
       </c>
       <c r="H509" t="n">
         <v>5714</v>
@@ -15159,7 +15159,7 @@
         <v>9.08475017547607</v>
       </c>
       <c r="G510" t="n">
-        <v>7.27021503448486</v>
+        <v>7.27021408081055</v>
       </c>
       <c r="H510" t="n">
         <v>8265</v>
@@ -15275,7 +15275,7 @@
         <v>9.16315174102783</v>
       </c>
       <c r="G514" t="n">
-        <v>7.33295583724976</v>
+        <v>7.33295631408691</v>
       </c>
       <c r="H514" t="n">
         <v>8163</v>
@@ -15362,7 +15362,7 @@
         <v>9.11415100097656</v>
       </c>
       <c r="G517" t="n">
-        <v>7.29374265670776</v>
+        <v>7.29374170303345</v>
       </c>
       <c r="H517" t="n">
         <v>22958</v>
@@ -15391,7 +15391,7 @@
         <v>9.04555034637451</v>
       </c>
       <c r="G518" t="n">
-        <v>7.23884391784668</v>
+        <v>7.23884439468384</v>
       </c>
       <c r="H518" t="n">
         <v>17856</v>
@@ -15449,7 +15449,7 @@
         <v>9.0259485244751</v>
       </c>
       <c r="G520" t="n">
-        <v>7.22315740585327</v>
+        <v>7.22315692901611</v>
       </c>
       <c r="H520" t="n">
         <v>13163</v>
@@ -15478,7 +15478,7 @@
         <v>9.11415100097656</v>
       </c>
       <c r="G521" t="n">
-        <v>7.29374265670776</v>
+        <v>7.29374170303345</v>
       </c>
       <c r="H521" t="n">
         <v>10510</v>
@@ -15565,7 +15565,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G524" t="n">
-        <v>7.01924705505371</v>
+        <v>7.01924657821655</v>
       </c>
       <c r="H524" t="n">
         <v>13775</v>
@@ -15623,7 +15623,7 @@
         <v>8.89854717254639</v>
       </c>
       <c r="G526" t="n">
-        <v>7.12120246887207</v>
+        <v>7.12120151519775</v>
       </c>
       <c r="H526" t="n">
         <v>45815</v>
@@ -15652,7 +15652,7 @@
         <v>8.87894725799561</v>
       </c>
       <c r="G527" t="n">
-        <v>7.10551691055298</v>
+        <v>7.10551738739014</v>
       </c>
       <c r="H527" t="n">
         <v>45713</v>
@@ -15681,7 +15681,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H528" t="n">
         <v>26938</v>
@@ -15710,7 +15710,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G529" t="n">
-        <v>7.08198881149292</v>
+        <v>7.08198833465576</v>
       </c>
       <c r="H529" t="n">
         <v>16122</v>
@@ -15739,7 +15739,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G530" t="n">
-        <v>7.01924705505371</v>
+        <v>7.01924657821655</v>
       </c>
       <c r="H530" t="n">
         <v>30509</v>
@@ -15768,7 +15768,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G531" t="n">
-        <v>7.02708864212036</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H531" t="n">
         <v>13775</v>
@@ -15797,7 +15797,7 @@
         <v>8.48694038391113</v>
       </c>
       <c r="G532" t="n">
-        <v>6.79180669784546</v>
+        <v>6.79180765151978</v>
       </c>
       <c r="H532" t="n">
         <v>67345</v>
@@ -15826,7 +15826,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G533" t="n">
-        <v>6.9016056060791</v>
+        <v>6.90160608291626</v>
       </c>
       <c r="H533" t="n">
         <v>49693</v>
@@ -15855,7 +15855,7 @@
         <v>8.90834712982178</v>
       </c>
       <c r="G534" t="n">
-        <v>7.12904500961304</v>
+        <v>7.12904596328735</v>
       </c>
       <c r="H534" t="n">
         <v>75202</v>
@@ -15884,7 +15884,7 @@
         <v>8.94754791259766</v>
       </c>
       <c r="G535" t="n">
-        <v>7.16041660308838</v>
+        <v>7.16041612625122</v>
       </c>
       <c r="H535" t="n">
         <v>95304</v>
@@ -15913,7 +15913,7 @@
         <v>8.94754791259766</v>
       </c>
       <c r="G536" t="n">
-        <v>7.16041660308838</v>
+        <v>7.16041612625122</v>
       </c>
       <c r="H536" t="n">
         <v>23775</v>
@@ -15942,7 +15942,7 @@
         <v>8.91814804077148</v>
       </c>
       <c r="G537" t="n">
-        <v>7.13688898086548</v>
+        <v>7.13688945770264</v>
       </c>
       <c r="H537" t="n">
         <v>47346</v>
@@ -15971,7 +15971,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G538" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H538" t="n">
         <v>17754</v>
@@ -16000,7 +16000,7 @@
         <v>8.86914730072021</v>
       </c>
       <c r="G539" t="n">
-        <v>7.09767580032349</v>
+        <v>7.09767484664917</v>
       </c>
       <c r="H539" t="n">
         <v>23468</v>
@@ -16029,7 +16029,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G540" t="n">
-        <v>7.01924705505371</v>
+        <v>7.01924657821655</v>
       </c>
       <c r="H540" t="n">
         <v>36734</v>
@@ -16087,7 +16087,7 @@
         <v>8.85934734344482</v>
       </c>
       <c r="G542" t="n">
-        <v>7.08983278274536</v>
+        <v>7.08983325958252</v>
       </c>
       <c r="H542" t="n">
         <v>14387</v>
@@ -16116,7 +16116,7 @@
         <v>8.87894725799561</v>
       </c>
       <c r="G543" t="n">
-        <v>7.10551691055298</v>
+        <v>7.10551738739014</v>
       </c>
       <c r="H543" t="n">
         <v>32550</v>
@@ -16145,7 +16145,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G544" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H544" t="n">
         <v>2244</v>
@@ -16203,7 +16203,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.08198881149292</v>
+        <v>7.08198833465576</v>
       </c>
       <c r="H546" t="n">
         <v>4999</v>
@@ -16232,7 +16232,7 @@
         <v>8.83974647521973</v>
       </c>
       <c r="G547" t="n">
-        <v>7.07414531707764</v>
+        <v>7.07414627075195</v>
       </c>
       <c r="H547" t="n">
         <v>4795</v>
@@ -16261,7 +16261,7 @@
         <v>8.76134490966797</v>
       </c>
       <c r="G548" t="n">
-        <v>7.01140451431274</v>
+        <v>7.01140403747559</v>
       </c>
       <c r="H548" t="n">
         <v>3061</v>
@@ -16319,7 +16319,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G550" t="n">
-        <v>7.06630325317383</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H550" t="n">
         <v>32856</v>
@@ -16348,7 +16348,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G551" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H551" t="n">
         <v>6122</v>
@@ -16406,7 +16406,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G553" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H553" t="n">
         <v>13265</v>
@@ -16435,7 +16435,7 @@
         <v>8.72214412689209</v>
       </c>
       <c r="G554" t="n">
-        <v>6.98003339767456</v>
+        <v>6.98003387451172</v>
       </c>
       <c r="H554" t="n">
         <v>38468</v>
@@ -16464,7 +16464,7 @@
         <v>8.70254421234131</v>
       </c>
       <c r="G555" t="n">
-        <v>6.96434831619263</v>
+        <v>6.96434783935547</v>
       </c>
       <c r="H555" t="n">
         <v>37958</v>
@@ -16493,7 +16493,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G556" t="n">
-        <v>7.02708864212036</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H556" t="n">
         <v>4489</v>
@@ -16522,7 +16522,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G557" t="n">
-        <v>6.9016056060791</v>
+        <v>6.90160608291626</v>
       </c>
       <c r="H557" t="n">
         <v>6122</v>
@@ -16580,7 +16580,7 @@
         <v>8.72214412689209</v>
       </c>
       <c r="G559" t="n">
-        <v>6.98003339767456</v>
+        <v>6.98003387451172</v>
       </c>
       <c r="H559" t="n">
         <v>1938</v>
@@ -16609,7 +16609,7 @@
         <v>8.70254421234131</v>
       </c>
       <c r="G560" t="n">
-        <v>6.96434831619263</v>
+        <v>6.96434783935547</v>
       </c>
       <c r="H560" t="n">
         <v>6734</v>
@@ -16638,7 +16638,7 @@
         <v>8.83974647521973</v>
       </c>
       <c r="G561" t="n">
-        <v>7.07414531707764</v>
+        <v>7.07414627075195</v>
       </c>
       <c r="H561" t="n">
         <v>25917</v>
@@ -16725,7 +16725,7 @@
         <v>8.85934734344482</v>
       </c>
       <c r="G564" t="n">
-        <v>7.08983278274536</v>
+        <v>7.08983325958252</v>
       </c>
       <c r="H564" t="n">
         <v>6428</v>
@@ -16754,7 +16754,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G565" t="n">
-        <v>7.02708864212036</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H565" t="n">
         <v>22346</v>
@@ -16783,7 +16783,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G566" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H566" t="n">
         <v>20713</v>
@@ -16812,7 +16812,7 @@
         <v>8.86914730072021</v>
       </c>
       <c r="G567" t="n">
-        <v>7.09767580032349</v>
+        <v>7.09767484664917</v>
       </c>
       <c r="H567" t="n">
         <v>77447</v>
@@ -16870,7 +16870,7 @@
         <v>8.91814804077148</v>
       </c>
       <c r="G569" t="n">
-        <v>7.13688898086548</v>
+        <v>7.13688945770264</v>
       </c>
       <c r="H569" t="n">
         <v>32346</v>
@@ -16899,7 +16899,7 @@
         <v>8.86914730072021</v>
       </c>
       <c r="G570" t="n">
-        <v>7.09767580032349</v>
+        <v>7.09767484664917</v>
       </c>
       <c r="H570" t="n">
         <v>4999</v>
@@ -16928,7 +16928,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G571" t="n">
-        <v>7.06630325317383</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H571" t="n">
         <v>17142</v>
@@ -16957,7 +16957,7 @@
         <v>8.85934734344482</v>
       </c>
       <c r="G572" t="n">
-        <v>7.08983278274536</v>
+        <v>7.08983325958252</v>
       </c>
       <c r="H572" t="n">
         <v>6836</v>
@@ -16986,7 +16986,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G573" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H573" t="n">
         <v>57345</v>
@@ -17015,7 +17015,7 @@
         <v>8.82994556427002</v>
       </c>
       <c r="G574" t="n">
-        <v>7.06630325317383</v>
+        <v>7.06630277633667</v>
       </c>
       <c r="H574" t="n">
         <v>4897</v>
@@ -17044,7 +17044,7 @@
         <v>8.84954643249512</v>
       </c>
       <c r="G575" t="n">
-        <v>7.08198881149292</v>
+        <v>7.08198833465576</v>
       </c>
       <c r="H575" t="n">
         <v>14183</v>
@@ -17073,7 +17073,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G576" t="n">
-        <v>7.01924705505371</v>
+        <v>7.01924657821655</v>
       </c>
       <c r="H576" t="n">
         <v>7959</v>
@@ -17102,7 +17102,7 @@
         <v>8.74174499511719</v>
       </c>
       <c r="G577" t="n">
-        <v>6.99571895599365</v>
+        <v>6.99571990966797</v>
       </c>
       <c r="H577" t="n">
         <v>9693</v>
@@ -17189,7 +17189,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G580" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H580" t="n">
         <v>3673</v>
@@ -17247,7 +17247,7 @@
         <v>8.80054569244385</v>
       </c>
       <c r="G582" t="n">
-        <v>7.04277515411377</v>
+        <v>7.04277563095093</v>
       </c>
       <c r="H582" t="n">
         <v>8367</v>
@@ -17276,7 +17276,7 @@
         <v>8.77114486694336</v>
       </c>
       <c r="G583" t="n">
-        <v>7.01924705505371</v>
+        <v>7.01924657821655</v>
       </c>
       <c r="H583" t="n">
         <v>4183</v>
@@ -17305,7 +17305,7 @@
         <v>8.78094482421875</v>
       </c>
       <c r="G584" t="n">
-        <v>7.02708864212036</v>
+        <v>7.02708911895752</v>
       </c>
       <c r="H584" t="n">
         <v>5203</v>
@@ -17363,7 +17363,7 @@
         <v>8.82014560699463</v>
       </c>
       <c r="G586" t="n">
-        <v>7.05846071243286</v>
+        <v>7.0584602355957</v>
       </c>
       <c r="H586" t="n">
         <v>52448</v>
@@ -17392,7 +17392,7 @@
         <v>8.70254421234131</v>
       </c>
       <c r="G587" t="n">
-        <v>6.96434831619263</v>
+        <v>6.96434783935547</v>
       </c>
       <c r="H587" t="n">
         <v>6224</v>
@@ -17450,7 +17450,7 @@
         <v>8.63394260406494</v>
       </c>
       <c r="G589" t="n">
-        <v>6.90944862365723</v>
+        <v>6.90944910049438</v>
       </c>
       <c r="H589" t="n">
         <v>5101</v>
@@ -17508,7 +17508,7 @@
         <v>8.60454177856445</v>
       </c>
       <c r="G591" t="n">
-        <v>6.88592004776001</v>
+        <v>6.88592052459717</v>
       </c>
       <c r="H591" t="n">
         <v>9183</v>
@@ -17537,7 +17537,7 @@
         <v>8.49674129486084</v>
       </c>
       <c r="G592" t="n">
-        <v>6.79965209960938</v>
+        <v>6.7996506690979</v>
       </c>
       <c r="H592" t="n">
         <v>24591</v>
@@ -17566,7 +17566,7 @@
         <v>8.52614116668701</v>
       </c>
       <c r="G593" t="n">
-        <v>6.82317876815796</v>
+        <v>6.82317924499512</v>
       </c>
       <c r="H593" t="n">
         <v>8571</v>
@@ -17595,7 +17595,7 @@
         <v>8.47714042663574</v>
       </c>
       <c r="G594" t="n">
-        <v>6.78396511077881</v>
+        <v>6.78396558761597</v>
       </c>
       <c r="H594" t="n">
         <v>5714</v>
@@ -17624,7 +17624,7 @@
         <v>8.45753955841064</v>
       </c>
       <c r="G595" t="n">
-        <v>6.7682785987854</v>
+        <v>6.76827955245972</v>
       </c>
       <c r="H595" t="n">
         <v>15714</v>
@@ -17653,7 +17653,7 @@
         <v>8.28113746643066</v>
       </c>
       <c r="G596" t="n">
-        <v>6.62711095809937</v>
+        <v>6.62711000442505</v>
       </c>
       <c r="H596" t="n">
         <v>82243</v>
@@ -17682,7 +17682,7 @@
         <v>8.04593276977539</v>
       </c>
       <c r="G597" t="n">
-        <v>6.43888378143311</v>
+        <v>6.43888425827026</v>
       </c>
       <c r="H597" t="n">
         <v>122548</v>
@@ -17711,7 +17711,7 @@
         <v>8.13413524627686</v>
       </c>
       <c r="G598" t="n">
-        <v>6.60602521896362</v>
+        <v>6.60602569580078</v>
       </c>
       <c r="H598" t="n">
         <v>41223</v>
@@ -17769,7 +17769,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G600" t="n">
-        <v>7.00397825241089</v>
+        <v>7.00397872924805</v>
       </c>
       <c r="H600" t="n">
         <v>72651</v>
@@ -17798,7 +17798,7 @@
         <v>8.48694038391113</v>
       </c>
       <c r="G601" t="n">
-        <v>6.89255142211914</v>
+        <v>6.89255237579346</v>
       </c>
       <c r="H601" t="n">
         <v>23877</v>
@@ -17827,7 +17827,7 @@
         <v>8.42813873291016</v>
       </c>
       <c r="G602" t="n">
-        <v>6.8447961807251</v>
+        <v>6.84479570388794</v>
       </c>
       <c r="H602" t="n">
         <v>12856</v>
@@ -17856,7 +17856,7 @@
         <v>8.62414264678955</v>
       </c>
       <c r="G603" t="n">
-        <v>7.00397825241089</v>
+        <v>7.00397872924805</v>
       </c>
       <c r="H603" t="n">
         <v>19183</v>
@@ -18030,7 +18030,7 @@
         <v>8.56534194946289</v>
       </c>
       <c r="G609" t="n">
-        <v>6.95622396469116</v>
+        <v>6.95622444152832</v>
       </c>
       <c r="H609" t="n">
         <v>11122</v>
@@ -18059,7 +18059,7 @@
         <v>8.51634120941162</v>
       </c>
       <c r="G610" t="n">
-        <v>6.91642951965332</v>
+        <v>6.91642904281616</v>
       </c>
       <c r="H610" t="n">
         <v>7857</v>
@@ -18146,7 +18146,7 @@
         <v>8.28113746643066</v>
       </c>
       <c r="G613" t="n">
-        <v>6.72541189193726</v>
+        <v>6.7254114151001</v>
       </c>
       <c r="H613" t="n">
         <v>11020</v>
@@ -18175,7 +18175,7 @@
         <v>8.12433433532715</v>
       </c>
       <c r="G614" t="n">
-        <v>6.5980658531189</v>
+        <v>6.59806632995605</v>
       </c>
       <c r="H614" t="n">
         <v>42856</v>
@@ -18204,7 +18204,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G615" t="n">
-        <v>6.36725378036499</v>
+        <v>6.36725330352783</v>
       </c>
       <c r="H615" t="n">
         <v>45203</v>
@@ -18233,7 +18233,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G616" t="n">
-        <v>6.36725378036499</v>
+        <v>6.36725330352783</v>
       </c>
       <c r="H616" t="n">
         <v>27244</v>
@@ -18262,7 +18262,7 @@
         <v>7.8597297668457</v>
       </c>
       <c r="G617" t="n">
-        <v>6.38317060470581</v>
+        <v>6.38317108154297</v>
       </c>
       <c r="H617" t="n">
         <v>11428</v>
@@ -18291,7 +18291,7 @@
         <v>7.92833089828491</v>
       </c>
       <c r="G618" t="n">
-        <v>6.43888425827026</v>
+        <v>6.43888473510742</v>
       </c>
       <c r="H618" t="n">
         <v>13367</v>
@@ -18349,7 +18349,7 @@
         <v>7.77152919769287</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31154012680054</v>
+        <v>6.31153964996338</v>
       </c>
       <c r="H620" t="n">
         <v>81427</v>
@@ -18378,7 +18378,7 @@
         <v>7.77152919769287</v>
       </c>
       <c r="G621" t="n">
-        <v>6.31154012680054</v>
+        <v>6.31153964996338</v>
       </c>
       <c r="H621" t="n">
         <v>10407</v>
@@ -18407,7 +18407,7 @@
         <v>7.49712419509888</v>
       </c>
       <c r="G622" t="n">
-        <v>6.08868598937988</v>
+        <v>6.08868551254272</v>
       </c>
       <c r="H622" t="n">
         <v>25509</v>
@@ -18465,7 +18465,7 @@
         <v>7.53632497787476</v>
       </c>
       <c r="G624" t="n">
-        <v>6.12052249908447</v>
+        <v>6.12052202224731</v>
       </c>
       <c r="H624" t="n">
         <v>7550</v>
@@ -18581,7 +18581,7 @@
         <v>7.68332719802856</v>
       </c>
       <c r="G628" t="n">
-        <v>6.23990774154663</v>
+        <v>6.23990821838379</v>
       </c>
       <c r="H628" t="n">
         <v>4489</v>
@@ -18639,7 +18639,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G630" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684900283813</v>
       </c>
       <c r="H630" t="n">
         <v>11734</v>
@@ -18668,7 +18668,7 @@
         <v>7.38932180404663</v>
       </c>
       <c r="G631" t="n">
-        <v>6.00113582611084</v>
+        <v>6.00113534927368</v>
       </c>
       <c r="H631" t="n">
         <v>9795</v>
@@ -18755,7 +18755,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G634" t="n">
-        <v>5.74644565582275</v>
+        <v>5.74644613265991</v>
       </c>
       <c r="H634" t="n">
         <v>16530</v>
@@ -18900,7 +18900,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G639" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H639" t="n">
         <v>71019</v>
@@ -18958,7 +18958,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G641" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H641" t="n">
         <v>25101</v>
@@ -19132,7 +19132,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G647" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H647" t="n">
         <v>15714</v>
@@ -19248,7 +19248,7 @@
         <v>7.28151988983154</v>
       </c>
       <c r="G651" t="n">
-        <v>5.91358518600464</v>
+        <v>5.9135856628418</v>
       </c>
       <c r="H651" t="n">
         <v>9183</v>
@@ -19277,7 +19277,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G652" t="n">
-        <v>6.04889011383057</v>
+        <v>6.04889059066772</v>
       </c>
       <c r="H652" t="n">
         <v>10816</v>
@@ -19364,7 +19364,7 @@
         <v>7.73232793807983</v>
       </c>
       <c r="G655" t="n">
-        <v>6.27970314025879</v>
+        <v>6.27970266342163</v>
       </c>
       <c r="H655" t="n">
         <v>18673</v>
@@ -19393,7 +19393,7 @@
         <v>7.55592489242554</v>
       </c>
       <c r="G656" t="n">
-        <v>6.13643980026245</v>
+        <v>6.13644027709961</v>
       </c>
       <c r="H656" t="n">
         <v>32142</v>
@@ -19538,7 +19538,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G661" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H661" t="n">
         <v>9387</v>
@@ -19567,7 +19567,7 @@
         <v>7.37952184677124</v>
       </c>
       <c r="G662" t="n">
-        <v>5.99317693710327</v>
+        <v>5.99317741394043</v>
       </c>
       <c r="H662" t="n">
         <v>4897</v>
@@ -19596,7 +19596,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G663" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684900283813</v>
       </c>
       <c r="H663" t="n">
         <v>12244</v>
@@ -19654,7 +19654,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G665" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684900283813</v>
       </c>
       <c r="H665" t="n">
         <v>2448</v>
@@ -19683,7 +19683,7 @@
         <v>7.45792293548584</v>
       </c>
       <c r="G666" t="n">
-        <v>6.05684947967529</v>
+        <v>6.05684900283813</v>
       </c>
       <c r="H666" t="n">
         <v>2244</v>
@@ -19712,7 +19712,7 @@
         <v>7.41872310638428</v>
       </c>
       <c r="G667" t="n">
-        <v>6.02501344680786</v>
+        <v>6.02501392364502</v>
       </c>
       <c r="H667" t="n">
         <v>4489</v>
@@ -19770,7 +19770,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G669" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H669" t="n">
         <v>8265</v>
@@ -19857,7 +19857,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G672" t="n">
-        <v>5.74644565582275</v>
+        <v>5.74644613265991</v>
       </c>
       <c r="H672" t="n">
         <v>11020</v>
@@ -20002,7 +20002,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G677" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H677" t="n">
         <v>25917</v>
@@ -20031,7 +20031,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G678" t="n">
-        <v>5.49175548553467</v>
+        <v>5.49175596237183</v>
       </c>
       <c r="H678" t="n">
         <v>244485</v>
@@ -20060,7 +20060,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G679" t="n">
-        <v>5.58726453781128</v>
+        <v>5.58726501464844</v>
       </c>
       <c r="H679" t="n">
         <v>40101</v>
@@ -20089,7 +20089,7 @@
         <v>6.88951396942139</v>
       </c>
       <c r="G680" t="n">
-        <v>5.59522390365601</v>
+        <v>5.59522294998169</v>
       </c>
       <c r="H680" t="n">
         <v>27346</v>
@@ -20118,7 +20118,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G681" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H681" t="n">
         <v>7550</v>
@@ -20147,7 +20147,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G682" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H682" t="n">
         <v>31428</v>
@@ -20176,7 +20176,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G683" t="n">
-        <v>5.58726453781128</v>
+        <v>5.58726501464844</v>
       </c>
       <c r="H683" t="n">
         <v>18162</v>
@@ -20205,7 +20205,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G684" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H684" t="n">
         <v>1530</v>
@@ -20234,7 +20234,7 @@
         <v>6.86991405487061</v>
       </c>
       <c r="G685" t="n">
-        <v>5.57930660247803</v>
+        <v>5.57930612564087</v>
       </c>
       <c r="H685" t="n">
         <v>8571</v>
@@ -20263,7 +20263,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G686" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H686" t="n">
         <v>3469</v>
@@ -20292,7 +20292,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G687" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H687" t="n">
         <v>22958</v>
@@ -20350,7 +20350,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G689" t="n">
-        <v>5.58726453781128</v>
+        <v>5.58726501464844</v>
       </c>
       <c r="H689" t="n">
         <v>17448</v>
@@ -20379,7 +20379,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G690" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H690" t="n">
         <v>16632</v>
@@ -20408,7 +20408,7 @@
         <v>6.88951396942139</v>
       </c>
       <c r="G691" t="n">
-        <v>5.59522390365601</v>
+        <v>5.59522294998169</v>
       </c>
       <c r="H691" t="n">
         <v>11530</v>
@@ -20437,7 +20437,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G692" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H692" t="n">
         <v>8877</v>
@@ -20495,7 +20495,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G694" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H694" t="n">
         <v>17652</v>
@@ -20582,7 +20582,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G697" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H697" t="n">
         <v>11122</v>
@@ -20611,7 +20611,7 @@
         <v>7.47752380371094</v>
       </c>
       <c r="G698" t="n">
-        <v>6.07276725769043</v>
+        <v>6.07276773452759</v>
       </c>
       <c r="H698" t="n">
         <v>9183</v>
@@ -20640,7 +20640,7 @@
         <v>7.49712419509888</v>
       </c>
       <c r="G699" t="n">
-        <v>6.08868598937988</v>
+        <v>6.08868551254272</v>
       </c>
       <c r="H699" t="n">
         <v>24999</v>
@@ -20727,7 +20727,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G702" t="n">
-        <v>6.04889011383057</v>
+        <v>6.04889059066772</v>
       </c>
       <c r="H702" t="n">
         <v>2857</v>
@@ -20756,7 +20756,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G703" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H703" t="n">
         <v>3367</v>
@@ -20814,7 +20814,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G705" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H705" t="n">
         <v>4795</v>
@@ -21017,7 +21017,7 @@
         <v>7.0267162322998</v>
       </c>
       <c r="G712" t="n">
-        <v>5.7066502571106</v>
+        <v>5.70665073394775</v>
       </c>
       <c r="H712" t="n">
         <v>7346</v>
@@ -21046,7 +21046,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G713" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H713" t="n">
         <v>30917</v>
@@ -21075,7 +21075,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G714" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H714" t="n">
         <v>5816</v>
@@ -21104,7 +21104,7 @@
         <v>6.879714012146</v>
       </c>
       <c r="G715" t="n">
-        <v>5.58726453781128</v>
+        <v>5.58726501464844</v>
       </c>
       <c r="H715" t="n">
         <v>4795</v>
@@ -21162,7 +21162,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G717" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H717" t="n">
         <v>11530</v>
@@ -21336,7 +21336,7 @@
         <v>6.82091283798218</v>
       </c>
       <c r="G723" t="n">
-        <v>5.53950977325439</v>
+        <v>5.53950929641724</v>
       </c>
       <c r="H723" t="n">
         <v>11632</v>
@@ -21394,7 +21394,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G725" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H725" t="n">
         <v>28570</v>
@@ -21481,7 +21481,7 @@
         <v>6.82091283798218</v>
       </c>
       <c r="G728" t="n">
-        <v>5.53950977325439</v>
+        <v>5.53950929641724</v>
       </c>
       <c r="H728" t="n">
         <v>59386</v>
@@ -21539,7 +21539,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G730" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H730" t="n">
         <v>1428</v>
@@ -21568,7 +21568,7 @@
         <v>6.91891384124756</v>
       </c>
       <c r="G731" t="n">
-        <v>5.61910104751587</v>
+        <v>5.61910057067871</v>
       </c>
       <c r="H731" t="n">
         <v>29591</v>
@@ -21597,7 +21597,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G732" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H732" t="n">
         <v>8061</v>
@@ -21713,7 +21713,7 @@
         <v>6.7817120552063</v>
       </c>
       <c r="G736" t="n">
-        <v>5.50767374038696</v>
+        <v>5.50767421722412</v>
       </c>
       <c r="H736" t="n">
         <v>11632</v>
@@ -21771,7 +21771,7 @@
         <v>6.7817120552063</v>
       </c>
       <c r="G738" t="n">
-        <v>5.50767374038696</v>
+        <v>5.50767421722412</v>
       </c>
       <c r="H738" t="n">
         <v>6734</v>
@@ -21800,7 +21800,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G739" t="n">
-        <v>5.49175548553467</v>
+        <v>5.49175596237183</v>
       </c>
       <c r="H739" t="n">
         <v>5306</v>
@@ -21829,7 +21829,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G740" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H740" t="n">
         <v>5816</v>
@@ -21858,7 +21858,7 @@
         <v>6.8601131439209</v>
       </c>
       <c r="G741" t="n">
-        <v>5.57134675979614</v>
+        <v>5.57134628295898</v>
       </c>
       <c r="H741" t="n">
         <v>6428</v>
@@ -21916,7 +21916,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G743" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H743" t="n">
         <v>10918</v>
@@ -22032,7 +22032,7 @@
         <v>7.05611705780029</v>
       </c>
       <c r="G747" t="n">
-        <v>5.73052835464478</v>
+        <v>5.73052787780762</v>
       </c>
       <c r="H747" t="n">
         <v>22142</v>
@@ -22061,7 +22061,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G748" t="n">
-        <v>5.74644565582275</v>
+        <v>5.74644613265991</v>
       </c>
       <c r="H748" t="n">
         <v>1938</v>
@@ -22090,7 +22090,7 @@
         <v>7.08551692962646</v>
       </c>
       <c r="G749" t="n">
-        <v>5.75440502166748</v>
+        <v>5.75440454483032</v>
       </c>
       <c r="H749" t="n">
         <v>24183</v>
@@ -22119,7 +22119,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G750" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H750" t="n">
         <v>9081</v>
@@ -22148,7 +22148,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G751" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H751" t="n">
         <v>1530</v>
@@ -22177,7 +22177,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G752" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H752" t="n">
         <v>13265</v>
@@ -22206,7 +22206,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G753" t="n">
-        <v>5.66685438156128</v>
+        <v>5.66685485839844</v>
       </c>
       <c r="H753" t="n">
         <v>56325</v>
@@ -22235,7 +22235,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G754" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H754" t="n">
         <v>21632</v>
@@ -22264,7 +22264,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G755" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H755" t="n">
         <v>41427</v>
@@ -22293,7 +22293,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G756" t="n">
-        <v>5.66685438156128</v>
+        <v>5.66685485839844</v>
       </c>
       <c r="H756" t="n">
         <v>39489</v>
@@ -22322,7 +22322,7 @@
         <v>6.9581151008606</v>
       </c>
       <c r="G757" t="n">
-        <v>5.6509370803833</v>
+        <v>5.65093755722046</v>
       </c>
       <c r="H757" t="n">
         <v>1632</v>
@@ -22351,7 +22351,7 @@
         <v>6.93851518630981</v>
       </c>
       <c r="G758" t="n">
-        <v>5.63501977920532</v>
+        <v>5.63501930236816</v>
       </c>
       <c r="H758" t="n">
         <v>29285</v>
@@ -22438,7 +22438,7 @@
         <v>7.0267162322998</v>
       </c>
       <c r="G761" t="n">
-        <v>5.7066502571106</v>
+        <v>5.70665073394775</v>
       </c>
       <c r="H761" t="n">
         <v>306</v>
@@ -22467,7 +22467,7 @@
         <v>7.07571697235107</v>
       </c>
       <c r="G762" t="n">
-        <v>5.74644565582275</v>
+        <v>5.74644613265991</v>
       </c>
       <c r="H762" t="n">
         <v>10918</v>
@@ -22496,7 +22496,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G763" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H763" t="n">
         <v>16734</v>
@@ -22612,7 +22612,7 @@
         <v>7.0463171005249</v>
       </c>
       <c r="G767" t="n">
-        <v>5.72256851196289</v>
+        <v>5.72256898880005</v>
       </c>
       <c r="H767" t="n">
         <v>4693</v>
@@ -22670,7 +22670,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G769" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H769" t="n">
         <v>38774</v>
@@ -22728,7 +22728,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81011867523193</v>
+        <v>5.81011819839478</v>
       </c>
       <c r="H771" t="n">
         <v>160915</v>
@@ -22757,7 +22757,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G772" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H772" t="n">
         <v>12448</v>
@@ -22786,7 +22786,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G773" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H773" t="n">
         <v>17448</v>
@@ -22815,7 +22815,7 @@
         <v>7.20311880111694</v>
       </c>
       <c r="G774" t="n">
-        <v>5.84991312026978</v>
+        <v>5.84991359710693</v>
       </c>
       <c r="H774" t="n">
         <v>9489</v>
@@ -22844,7 +22844,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G775" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H775" t="n">
         <v>12550</v>
@@ -22902,7 +22902,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G777" t="n">
-        <v>6.04889011383057</v>
+        <v>6.04889059066772</v>
       </c>
       <c r="H777" t="n">
         <v>6224</v>
@@ -22960,7 +22960,7 @@
         <v>7.37952184677124</v>
       </c>
       <c r="G779" t="n">
-        <v>5.99317693710327</v>
+        <v>5.99317741394043</v>
       </c>
       <c r="H779" t="n">
         <v>408</v>
@@ -22989,7 +22989,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G780" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H780" t="n">
         <v>714</v>
@@ -23018,7 +23018,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G781" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H781" t="n">
         <v>3163</v>
@@ -23047,7 +23047,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G782" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H782" t="n">
         <v>714</v>
@@ -23076,7 +23076,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G783" t="n">
-        <v>5.97725963592529</v>
+        <v>5.97725915908813</v>
       </c>
       <c r="H783" t="n">
         <v>2857</v>
@@ -23105,7 +23105,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G784" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H784" t="n">
         <v>1224</v>
@@ -23163,7 +23163,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G786" t="n">
-        <v>5.97725963592529</v>
+        <v>5.97725915908813</v>
       </c>
       <c r="H786" t="n">
         <v>2448</v>
@@ -23192,7 +23192,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G787" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H787" t="n">
         <v>816</v>
@@ -23221,7 +23221,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G788" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H788" t="n">
         <v>2346</v>
@@ -23250,7 +23250,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G789" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H789" t="n">
         <v>8571</v>
@@ -23337,7 +23337,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G792" t="n">
-        <v>6.04889011383057</v>
+        <v>6.04889059066772</v>
       </c>
       <c r="H792" t="n">
         <v>22958</v>
@@ -23424,7 +23424,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G795" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H795" t="n">
         <v>1020</v>
@@ -23453,7 +23453,7 @@
         <v>7.20311880111694</v>
       </c>
       <c r="G796" t="n">
-        <v>5.84991312026978</v>
+        <v>5.84991359710693</v>
       </c>
       <c r="H796" t="n">
         <v>816</v>
@@ -23511,7 +23511,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G798" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H798" t="n">
         <v>2142</v>
@@ -23569,7 +23569,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G800" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H800" t="n">
         <v>918</v>
@@ -23627,7 +23627,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G802" t="n">
-        <v>5.81011867523193</v>
+        <v>5.81011819839478</v>
       </c>
       <c r="H802" t="n">
         <v>7142</v>
@@ -23656,7 +23656,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G803" t="n">
-        <v>5.81011867523193</v>
+        <v>5.81011819839478</v>
       </c>
       <c r="H803" t="n">
         <v>816</v>
@@ -23685,7 +23685,7 @@
         <v>7.17371892929077</v>
       </c>
       <c r="G804" t="n">
-        <v>5.82603645324707</v>
+        <v>5.82603693008423</v>
       </c>
       <c r="H804" t="n">
         <v>8163</v>
@@ -23714,7 +23714,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G805" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H805" t="n">
         <v>3979</v>
@@ -23743,7 +23743,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G806" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H806" t="n">
         <v>2040</v>
@@ -23772,7 +23772,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G807" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H807" t="n">
         <v>11224</v>
@@ -23801,7 +23801,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G808" t="n">
-        <v>5.81011867523193</v>
+        <v>5.81011819839478</v>
       </c>
       <c r="H808" t="n">
         <v>16224</v>
@@ -23830,7 +23830,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G809" t="n">
-        <v>5.81011867523193</v>
+        <v>5.81011819839478</v>
       </c>
       <c r="H809" t="n">
         <v>107243</v>
@@ -23917,7 +23917,7 @@
         <v>7.05611705780029</v>
       </c>
       <c r="G812" t="n">
-        <v>5.73052835464478</v>
+        <v>5.73052787780762</v>
       </c>
       <c r="H812" t="n">
         <v>5612</v>
@@ -23946,7 +23946,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G813" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H813" t="n">
         <v>7550</v>
@@ -24004,7 +24004,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G815" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H815" t="n">
         <v>3673</v>
@@ -24033,7 +24033,7 @@
         <v>7.06591701507568</v>
       </c>
       <c r="G816" t="n">
-        <v>5.73848676681519</v>
+        <v>5.73848628997803</v>
       </c>
       <c r="H816" t="n">
         <v>12550</v>
@@ -24062,7 +24062,7 @@
         <v>7.10511779785156</v>
       </c>
       <c r="G817" t="n">
-        <v>5.77032375335693</v>
+        <v>5.77032327651978</v>
       </c>
       <c r="H817" t="n">
         <v>8979</v>
@@ -24149,7 +24149,7 @@
         <v>7.49712419509888</v>
       </c>
       <c r="G820" t="n">
-        <v>6.08868598937988</v>
+        <v>6.08868551254272</v>
       </c>
       <c r="H820" t="n">
         <v>23264</v>
@@ -24265,7 +24265,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G824" t="n">
-        <v>5.97725963592529</v>
+        <v>5.97725915908813</v>
       </c>
       <c r="H824" t="n">
         <v>6632</v>
@@ -24294,7 +24294,7 @@
         <v>7.35992193222046</v>
       </c>
       <c r="G825" t="n">
-        <v>5.97725963592529</v>
+        <v>5.97725915908813</v>
       </c>
       <c r="H825" t="n">
         <v>1734</v>
@@ -24323,7 +24323,7 @@
         <v>7.3011212348938</v>
       </c>
       <c r="G826" t="n">
-        <v>5.92950487136841</v>
+        <v>5.92950439453125</v>
       </c>
       <c r="H826" t="n">
         <v>1734</v>
@@ -24381,7 +24381,7 @@
         <v>7.25212001800537</v>
       </c>
       <c r="G828" t="n">
-        <v>5.88970851898193</v>
+        <v>5.88970947265625</v>
       </c>
       <c r="H828" t="n">
         <v>4693</v>
@@ -24410,7 +24410,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G829" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H829" t="n">
         <v>5408</v>
@@ -24584,7 +24584,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G835" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H835" t="n">
         <v>11326</v>
@@ -24613,7 +24613,7 @@
         <v>7.35012197494507</v>
       </c>
       <c r="G836" t="n">
-        <v>5.96930074691772</v>
+        <v>5.96930027008057</v>
       </c>
       <c r="H836" t="n">
         <v>8877</v>
@@ -24700,7 +24700,7 @@
         <v>7.38932180404663</v>
       </c>
       <c r="G839" t="n">
-        <v>6.00113582611084</v>
+        <v>6.00113534927368</v>
       </c>
       <c r="H839" t="n">
         <v>9938</v>
@@ -24758,7 +24758,7 @@
         <v>7.38932180404663</v>
       </c>
       <c r="G841" t="n">
-        <v>6.00113582611084</v>
+        <v>6.00113534927368</v>
       </c>
       <c r="H841" t="n">
         <v>2244</v>
@@ -24816,7 +24816,7 @@
         <v>7.38932180404663</v>
       </c>
       <c r="G843" t="n">
-        <v>6.00113582611084</v>
+        <v>6.00113534927368</v>
       </c>
       <c r="H843" t="n">
         <v>1023</v>
@@ -24845,7 +24845,7 @@
         <v>7.44812297821045</v>
       </c>
       <c r="G844" t="n">
-        <v>6.04889011383057</v>
+        <v>6.04889059066772</v>
       </c>
       <c r="H844" t="n">
         <v>755</v>
@@ -24961,7 +24961,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G848" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H848" t="n">
         <v>12347</v>
@@ -25048,7 +25048,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G851" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H851" t="n">
         <v>1631</v>
@@ -25222,7 +25222,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G857" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H857" t="n">
         <v>1352</v>
@@ -25309,7 +25309,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G860" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H860" t="n">
         <v>530</v>
@@ -25396,7 +25396,7 @@
         <v>7.0365161895752</v>
       </c>
       <c r="G863" t="n">
-        <v>5.80932712554932</v>
+        <v>5.809326171875</v>
       </c>
       <c r="H863" t="n">
         <v>18597</v>
@@ -25425,7 +25425,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G864" t="n">
-        <v>5.76078081130981</v>
+        <v>5.76078033447266</v>
       </c>
       <c r="H864" t="n">
         <v>1530</v>
@@ -25454,7 +25454,7 @@
         <v>6.97771501541138</v>
       </c>
       <c r="G865" t="n">
-        <v>5.76078081130981</v>
+        <v>5.76078033447266</v>
       </c>
       <c r="H865" t="n">
         <v>11040</v>
@@ -25686,7 +25686,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G873" t="n">
-        <v>5.906418800354</v>
+        <v>5.90641832351685</v>
       </c>
       <c r="H873" t="n">
         <v>3023</v>
@@ -25773,7 +25773,7 @@
         <v>7.21291923522949</v>
       </c>
       <c r="G876" t="n">
-        <v>5.95496511459351</v>
+        <v>5.95496463775635</v>
       </c>
       <c r="H876" t="n">
         <v>1209</v>
@@ -25831,7 +25831,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G878" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H878" t="n">
         <v>27956</v>
@@ -25889,7 +25889,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G880" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H880" t="n">
         <v>10627</v>
@@ -25976,7 +25976,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G883" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H883" t="n">
         <v>8222</v>
@@ -26063,7 +26063,7 @@
         <v>7.8597297668457</v>
       </c>
       <c r="G886" t="n">
-        <v>6.48896980285645</v>
+        <v>6.48896932601929</v>
       </c>
       <c r="H886" t="n">
         <v>9380</v>
@@ -26121,7 +26121,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G888" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H888" t="n">
         <v>4731</v>
@@ -26150,7 +26150,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G889" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H889" t="n">
         <v>1959</v>
@@ -26179,7 +26179,7 @@
         <v>7.74212789535522</v>
       </c>
       <c r="G890" t="n">
-        <v>6.39187812805176</v>
+        <v>6.3918776512146</v>
       </c>
       <c r="H890" t="n">
         <v>9052</v>
@@ -26237,7 +26237,7 @@
         <v>7.66372680664062</v>
       </c>
       <c r="G892" t="n">
-        <v>6.32715082168579</v>
+        <v>6.32715034484863</v>
       </c>
       <c r="H892" t="n">
         <v>2086</v>
@@ -26266,7 +26266,7 @@
         <v>7.64412593841553</v>
       </c>
       <c r="G893" t="n">
-        <v>6.31096744537354</v>
+        <v>6.31096792221069</v>
       </c>
       <c r="H893" t="n">
         <v>2775</v>
@@ -26353,7 +26353,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G896" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H896" t="n">
         <v>6512</v>
@@ -26382,7 +26382,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G897" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H897" t="n">
         <v>2538</v>
@@ -26527,7 +26527,7 @@
         <v>7.80092906951904</v>
       </c>
       <c r="G902" t="n">
-        <v>6.4404239654541</v>
+        <v>6.44042444229126</v>
       </c>
       <c r="H902" t="n">
         <v>632</v>
@@ -26556,7 +26556,7 @@
         <v>7.80092906951904</v>
       </c>
       <c r="G903" t="n">
-        <v>6.4404239654541</v>
+        <v>6.44042444229126</v>
       </c>
       <c r="H903" t="n">
         <v>204</v>
@@ -26643,7 +26643,7 @@
         <v>7.74212789535522</v>
       </c>
       <c r="G906" t="n">
-        <v>6.39187812805176</v>
+        <v>6.3918776512146</v>
       </c>
       <c r="H906" t="n">
         <v>1142</v>
@@ -26672,7 +26672,7 @@
         <v>7.64412593841553</v>
       </c>
       <c r="G907" t="n">
-        <v>6.31096744537354</v>
+        <v>6.31096792221069</v>
       </c>
       <c r="H907" t="n">
         <v>6781</v>
@@ -26701,7 +26701,7 @@
         <v>7.84012985229492</v>
       </c>
       <c r="G908" t="n">
-        <v>6.47278833389282</v>
+        <v>6.47278785705566</v>
       </c>
       <c r="H908" t="n">
         <v>11734</v>
@@ -26846,7 +26846,7 @@
         <v>7.27171993255615</v>
       </c>
       <c r="G913" t="n">
-        <v>6.00351047515869</v>
+        <v>6.00351095199585</v>
       </c>
       <c r="H913" t="n">
         <v>1296</v>
@@ -27107,7 +27107,7 @@
         <v>7.27171993255615</v>
       </c>
       <c r="G922" t="n">
-        <v>6.00351047515869</v>
+        <v>6.00351095199585</v>
       </c>
       <c r="H922" t="n">
         <v>10202</v>
@@ -27194,7 +27194,7 @@
         <v>7.0365161895752</v>
       </c>
       <c r="G925" t="n">
-        <v>5.80932712554932</v>
+        <v>5.809326171875</v>
       </c>
       <c r="H925" t="n">
         <v>205</v>
@@ -27223,7 +27223,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G926" t="n">
-        <v>5.906418800354</v>
+        <v>5.90641832351685</v>
       </c>
       <c r="H926" t="n">
         <v>13129</v>
@@ -27252,7 +27252,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G927" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H927" t="n">
         <v>1667</v>
@@ -27281,7 +27281,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G928" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H928" t="n">
         <v>158</v>
@@ -27310,7 +27310,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G929" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H929" t="n">
         <v>1427</v>
@@ -27339,7 +27339,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G930" t="n">
-        <v>5.906418800354</v>
+        <v>5.90641832351685</v>
       </c>
       <c r="H930" t="n">
         <v>2759</v>
@@ -27368,7 +27368,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G931" t="n">
-        <v>5.906418800354</v>
+        <v>5.90641832351685</v>
       </c>
       <c r="H931" t="n">
         <v>1760</v>
@@ -27397,7 +27397,7 @@
         <v>7.15411806106567</v>
       </c>
       <c r="G932" t="n">
-        <v>5.906418800354</v>
+        <v>5.90641832351685</v>
       </c>
       <c r="H932" t="n">
         <v>2979</v>
@@ -27571,7 +27571,7 @@
         <v>7.13451814651489</v>
       </c>
       <c r="G938" t="n">
-        <v>5.89023733139038</v>
+        <v>5.89023685455322</v>
       </c>
       <c r="H938" t="n">
         <v>3351</v>
@@ -27658,7 +27658,7 @@
         <v>6.64450979232788</v>
       </c>
       <c r="G941" t="n">
-        <v>5.48568677902222</v>
+        <v>5.48568725585938</v>
       </c>
       <c r="H941" t="n">
         <v>9487</v>
@@ -27716,7 +27716,7 @@
         <v>6.64450979232788</v>
       </c>
       <c r="G943" t="n">
-        <v>5.48568677902222</v>
+        <v>5.48568725585938</v>
       </c>
       <c r="H943" t="n">
         <v>14773</v>
@@ -27745,7 +27745,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G944" t="n">
-        <v>5.34004974365234</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H944" t="n">
         <v>49947</v>
@@ -27890,7 +27890,7 @@
         <v>6.42890596389771</v>
       </c>
       <c r="G949" t="n">
-        <v>5.30768537521362</v>
+        <v>5.30768585205078</v>
       </c>
       <c r="H949" t="n">
         <v>1313</v>
@@ -27977,7 +27977,7 @@
         <v>6.40930604934692</v>
       </c>
       <c r="G952" t="n">
-        <v>5.29150390625</v>
+        <v>5.29150438308716</v>
       </c>
       <c r="H952" t="n">
         <v>2238</v>
@@ -28093,7 +28093,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G956" t="n">
-        <v>5.17823076248169</v>
+        <v>5.17823028564453</v>
       </c>
       <c r="H956" t="n">
         <v>8426</v>
@@ -28122,7 +28122,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G957" t="n">
-        <v>5.17823076248169</v>
+        <v>5.17823028564453</v>
       </c>
       <c r="H957" t="n">
         <v>9562</v>
@@ -28151,7 +28151,7 @@
         <v>6.33090496063232</v>
       </c>
       <c r="G958" t="n">
-        <v>5.22677659988403</v>
+        <v>5.22677612304688</v>
       </c>
       <c r="H958" t="n">
         <v>2367</v>
@@ -28180,7 +28180,7 @@
         <v>6.33090496063232</v>
       </c>
       <c r="G959" t="n">
-        <v>5.22677659988403</v>
+        <v>5.22677612304688</v>
       </c>
       <c r="H959" t="n">
         <v>4950</v>
@@ -28209,7 +28209,7 @@
         <v>6.17410182952881</v>
       </c>
       <c r="G960" t="n">
-        <v>5.09732055664062</v>
+        <v>5.09732007980347</v>
       </c>
       <c r="H960" t="n">
         <v>2133</v>
@@ -28238,7 +28238,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G961" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H961" t="n">
         <v>3112</v>
@@ -28325,7 +28325,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G964" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H964" t="n">
         <v>13827</v>
@@ -28354,7 +28354,7 @@
         <v>6.21330308914185</v>
       </c>
       <c r="G965" t="n">
-        <v>5.12968444824219</v>
+        <v>5.12968492507935</v>
       </c>
       <c r="H965" t="n">
         <v>12844</v>
@@ -28441,7 +28441,7 @@
         <v>6.40930604934692</v>
       </c>
       <c r="G968" t="n">
-        <v>5.29150390625</v>
+        <v>5.29150438308716</v>
       </c>
       <c r="H968" t="n">
         <v>13612</v>
@@ -28470,7 +28470,7 @@
         <v>6.605309009552</v>
       </c>
       <c r="G969" t="n">
-        <v>5.45332384109497</v>
+        <v>5.45332336425781</v>
       </c>
       <c r="H969" t="n">
         <v>12147</v>
@@ -28499,7 +28499,7 @@
         <v>6.64450979232788</v>
       </c>
       <c r="G970" t="n">
-        <v>5.48568677902222</v>
+        <v>5.48568725585938</v>
       </c>
       <c r="H970" t="n">
         <v>15234</v>
@@ -28586,7 +28586,7 @@
         <v>6.68371105194092</v>
       </c>
       <c r="G973" t="n">
-        <v>5.5180516242981</v>
+        <v>5.51805114746094</v>
       </c>
       <c r="H973" t="n">
         <v>9164</v>
@@ -28673,7 +28673,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G976" t="n">
-        <v>5.43714189529419</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H976" t="n">
         <v>2929</v>
@@ -28789,7 +28789,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G980" t="n">
-        <v>5.34004974365234</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H980" t="n">
         <v>4323</v>
@@ -28818,7 +28818,7 @@
         <v>6.42890596389771</v>
       </c>
       <c r="G981" t="n">
-        <v>5.30768537521362</v>
+        <v>5.30768585205078</v>
       </c>
       <c r="H981" t="n">
         <v>5244</v>
@@ -28847,7 +28847,7 @@
         <v>6.46810722351074</v>
       </c>
       <c r="G982" t="n">
-        <v>5.34004974365234</v>
+        <v>5.3400502204895</v>
       </c>
       <c r="H982" t="n">
         <v>4261</v>
@@ -28876,7 +28876,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G983" t="n">
-        <v>5.17823076248169</v>
+        <v>5.17823028564453</v>
       </c>
       <c r="H983" t="n">
         <v>19040</v>
@@ -28905,7 +28905,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G984" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H984" t="n">
         <v>10681</v>
@@ -28934,7 +28934,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G985" t="n">
-        <v>5.00022792816162</v>
+        <v>5.00022840499878</v>
       </c>
       <c r="H985" t="n">
         <v>9933</v>
@@ -28963,7 +28963,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G986" t="n">
-        <v>5.01641035079956</v>
+        <v>5.0164098739624</v>
       </c>
       <c r="H986" t="n">
         <v>13715</v>
@@ -28992,7 +28992,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G987" t="n">
-        <v>5.00022792816162</v>
+        <v>5.00022840499878</v>
       </c>
       <c r="H987" t="n">
         <v>2193</v>
@@ -29050,7 +29050,7 @@
         <v>6.03690004348755</v>
       </c>
       <c r="G989" t="n">
-        <v>4.984046459198</v>
+        <v>4.98404693603516</v>
       </c>
       <c r="H989" t="n">
         <v>11870</v>
@@ -29079,7 +29079,7 @@
         <v>5.99769878387451</v>
       </c>
       <c r="G990" t="n">
-        <v>4.95168161392212</v>
+        <v>4.95168256759644</v>
       </c>
       <c r="H990" t="n">
         <v>2840</v>
@@ -29108,7 +29108,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G991" t="n">
-        <v>5.01641035079956</v>
+        <v>5.0164098739624</v>
       </c>
       <c r="H991" t="n">
         <v>4674</v>
@@ -29224,7 +29224,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G995" t="n">
-        <v>5.00022792816162</v>
+        <v>5.00022840499878</v>
       </c>
       <c r="H995" t="n">
         <v>11815</v>
@@ -29253,7 +29253,7 @@
         <v>5.95849800109863</v>
       </c>
       <c r="G996" t="n">
-        <v>4.91931867599487</v>
+        <v>4.91931819915771</v>
       </c>
       <c r="H996" t="n">
         <v>1755</v>
@@ -29311,7 +29311,7 @@
         <v>5.88009691238403</v>
       </c>
       <c r="G998" t="n">
-        <v>4.85459041595459</v>
+        <v>4.85458993911743</v>
       </c>
       <c r="H998" t="n">
         <v>7056</v>
@@ -29340,7 +29340,7 @@
         <v>6.01729917526245</v>
       </c>
       <c r="G999" t="n">
-        <v>4.96786451339722</v>
+        <v>4.96786499023438</v>
       </c>
       <c r="H999" t="n">
         <v>8729</v>
@@ -29456,7 +29456,7 @@
         <v>5.95849800109863</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.91931867599487</v>
+        <v>4.91931819915771</v>
       </c>
       <c r="H1003" t="n">
         <v>7724</v>
@@ -29485,7 +29485,7 @@
         <v>5.91929817199707</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.88695526123047</v>
+        <v>4.88695478439331</v>
       </c>
       <c r="H1004" t="n">
         <v>6254</v>
@@ -29572,7 +29572,7 @@
         <v>5.99769878387451</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.95168161392212</v>
+        <v>4.95168256759644</v>
       </c>
       <c r="H1007" t="n">
         <v>5428</v>
@@ -29630,7 +29630,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.00022792816162</v>
+        <v>5.00022840499878</v>
       </c>
       <c r="H1009" t="n">
         <v>9231</v>
@@ -29746,7 +29746,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1013" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1013" t="n">
         <v>14081</v>
@@ -29775,7 +29775,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G1014" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H1014" t="n">
         <v>8061</v>
@@ -29891,7 +29891,7 @@
         <v>6.19370222091675</v>
       </c>
       <c r="G1018" t="n">
-        <v>5.11350202560425</v>
+        <v>5.11350250244141</v>
       </c>
       <c r="H1018" t="n">
         <v>4000</v>
@@ -29920,7 +29920,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.01641035079956</v>
+        <v>5.0164098739624</v>
       </c>
       <c r="H1019" t="n">
         <v>2097</v>
@@ -29949,7 +29949,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.01641035079956</v>
+        <v>5.0164098739624</v>
       </c>
       <c r="H1020" t="n">
         <v>7495</v>
@@ -30007,7 +30007,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1022" t="n">
         <v>13275</v>
@@ -30065,7 +30065,7 @@
         <v>6.05649995803833</v>
       </c>
       <c r="G1024" t="n">
-        <v>5.00022792816162</v>
+        <v>5.00022840499878</v>
       </c>
       <c r="H1024" t="n">
         <v>28920</v>
@@ -30123,7 +30123,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1026" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1026" t="n">
         <v>22707</v>
@@ -30181,7 +30181,7 @@
         <v>6.17410182952881</v>
       </c>
       <c r="G1028" t="n">
-        <v>5.09732055664062</v>
+        <v>5.09732007980347</v>
       </c>
       <c r="H1028" t="n">
         <v>4715</v>
@@ -30210,7 +30210,7 @@
         <v>6.21330308914185</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.12968444824219</v>
+        <v>5.12968492507935</v>
       </c>
       <c r="H1029" t="n">
         <v>215</v>
@@ -30268,7 +30268,7 @@
         <v>6.42890596389771</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.30768537521362</v>
+        <v>5.30768585205078</v>
       </c>
       <c r="H1031" t="n">
         <v>17960</v>
@@ -30297,7 +30297,7 @@
         <v>6.33090496063232</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.22677659988403</v>
+        <v>5.22677612304688</v>
       </c>
       <c r="H1032" t="n">
         <v>27199</v>
@@ -30355,7 +30355,7 @@
         <v>6.33090496063232</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.22677659988403</v>
+        <v>5.22677612304688</v>
       </c>
       <c r="H1034" t="n">
         <v>1913</v>
@@ -30413,7 +30413,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G1036" t="n">
-        <v>5.17823076248169</v>
+        <v>5.17823028564453</v>
       </c>
       <c r="H1036" t="n">
         <v>8505</v>
@@ -30442,7 +30442,7 @@
         <v>6.27210378646851</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.17823076248169</v>
+        <v>5.17823028564453</v>
       </c>
       <c r="H1037" t="n">
         <v>5295</v>
@@ -30500,7 +30500,7 @@
         <v>6.40930604934692</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.29150390625</v>
+        <v>5.29150438308716</v>
       </c>
       <c r="H1039" t="n">
         <v>3005</v>
@@ -30529,7 +30529,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.43714189529419</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1040" t="n">
         <v>7004</v>
@@ -30587,7 +30587,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.43714189529419</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1042" t="n">
         <v>3674</v>
@@ -30616,7 +30616,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.58277988433838</v>
+        <v>5.58277940750122</v>
       </c>
       <c r="H1043" t="n">
         <v>25298</v>
@@ -30645,7 +30645,7 @@
         <v>6.76211214065552</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.58277988433838</v>
+        <v>5.58277940750122</v>
       </c>
       <c r="H1044" t="n">
         <v>5579</v>
@@ -30674,7 +30674,7 @@
         <v>6.64450979232788</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.48568677902222</v>
+        <v>5.48568725585938</v>
       </c>
       <c r="H1045" t="n">
         <v>28744</v>
@@ -30819,7 +30819,7 @@
         <v>6.58570909500122</v>
       </c>
       <c r="G1050" t="n">
-        <v>5.43714189529419</v>
+        <v>5.43714141845703</v>
       </c>
       <c r="H1050" t="n">
         <v>6900</v>
@@ -30877,7 +30877,7 @@
         <v>6.5269079208374</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.38859558105469</v>
+        <v>5.38859605789185</v>
       </c>
       <c r="H1052" t="n">
         <v>11451</v>
@@ -30906,7 +30906,7 @@
         <v>6.07609987258911</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.01641035079956</v>
+        <v>5.0164098739624</v>
       </c>
       <c r="H1053" t="n">
         <v>15993</v>
@@ -30935,7 +30935,7 @@
         <v>6.21330308914185</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.12968444824219</v>
+        <v>5.12968492507935</v>
       </c>
       <c r="H1054" t="n">
         <v>1186</v>
@@ -30964,7 +30964,7 @@
         <v>6.13490104675293</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.06495571136475</v>
+        <v>5.0649561882019</v>
       </c>
       <c r="H1055" t="n">
         <v>12008</v>
@@ -30993,7 +30993,7 @@
         <v>5.99769878387451</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.95168161392212</v>
+        <v>4.95168256759644</v>
       </c>
       <c r="H1056" t="n">
         <v>24168</v>
@@ -31051,7 +31051,7 @@
         <v>5.88009691238403</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.85459041595459</v>
+        <v>4.85458993911743</v>
       </c>
       <c r="H1058" t="n">
         <v>9075</v>
@@ -31109,7 +31109,7 @@
         <v>5.62529277801514</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.64422512054443</v>
+        <v>4.64422559738159</v>
       </c>
       <c r="H1060" t="n">
         <v>21098</v>
@@ -31138,7 +31138,7 @@
         <v>5.60569286346436</v>
       </c>
       <c r="G1061" t="n">
-        <v>4.62804317474365</v>
+        <v>4.62804412841797</v>
       </c>
       <c r="H1061" t="n">
         <v>20324</v>
@@ -31167,7 +31167,7 @@
         <v>5.3704891204834</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.43386030197144</v>
+        <v>4.43385982513428</v>
       </c>
       <c r="H1062" t="n">
         <v>42287</v>
@@ -31196,7 +31196,7 @@
         <v>5.0960841178894</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.20731163024902</v>
+        <v>4.20731115341187</v>
       </c>
       <c r="H1063" t="n">
         <v>27303</v>
@@ -31254,7 +31254,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1065" t="n">
         <v>28011</v>
@@ -31341,7 +31341,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1068" t="n">
         <v>130323</v>
@@ -31428,7 +31428,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.97267317771912</v>
+        <v>3.97267365455627</v>
       </c>
       <c r="H1071" t="n">
         <v>1988</v>
@@ -31486,7 +31486,7 @@
         <v>4.88048076629639</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.02931022644043</v>
+        <v>4.02931070327759</v>
       </c>
       <c r="H1073" t="n">
         <v>2247</v>
@@ -31515,7 +31515,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1074" t="n">
         <v>3436</v>
@@ -31544,7 +31544,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1075" t="n">
         <v>13708</v>
@@ -31602,7 +31602,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.97267317771912</v>
+        <v>3.97267365455627</v>
       </c>
       <c r="H1077" t="n">
         <v>7069</v>
@@ -31660,7 +31660,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1079" t="n">
         <v>8191</v>
@@ -31689,7 +31689,7 @@
         <v>4.72367811203003</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.89985466003418</v>
+        <v>3.89985513687134</v>
       </c>
       <c r="H1080" t="n">
         <v>1234</v>
@@ -31834,7 +31834,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.97267317771912</v>
+        <v>3.97267365455627</v>
       </c>
       <c r="H1085" t="n">
         <v>10553</v>
@@ -31863,7 +31863,7 @@
         <v>4.84127998352051</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.99694657325745</v>
+        <v>3.99694609642029</v>
       </c>
       <c r="H1086" t="n">
         <v>6489</v>
@@ -31921,7 +31921,7 @@
         <v>4.66487693786621</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.85130834579468</v>
+        <v>3.85130786895752</v>
       </c>
       <c r="H1088" t="n">
         <v>3306</v>
@@ -31979,7 +31979,7 @@
         <v>4.88048076629639</v>
       </c>
       <c r="G1090" t="n">
-        <v>4.02931022644043</v>
+        <v>4.02931070327759</v>
       </c>
       <c r="H1090" t="n">
         <v>11602</v>
@@ -32095,7 +32095,7 @@
         <v>4.66487693786621</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.85130834579468</v>
+        <v>3.85130786895752</v>
       </c>
       <c r="H1094" t="n">
         <v>4391</v>
@@ -32153,7 +32153,7 @@
         <v>4.72367811203003</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.89985466003418</v>
+        <v>3.89985513687134</v>
       </c>
       <c r="H1096" t="n">
         <v>7676</v>
@@ -32182,7 +32182,7 @@
         <v>4.90008115768433</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.04549217224121</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H1097" t="n">
         <v>18563</v>
@@ -32211,7 +32211,7 @@
         <v>4.99808311462402</v>
       </c>
       <c r="G1098" t="n">
-        <v>4.12640285491943</v>
+        <v>4.12640190124512</v>
       </c>
       <c r="H1098" t="n">
         <v>10310</v>
@@ -32356,7 +32356,7 @@
         <v>4.81187915802002</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.97267317771912</v>
+        <v>3.97267365455627</v>
       </c>
       <c r="H1103" t="n">
         <v>5764</v>
@@ -32385,7 +32385,7 @@
         <v>4.71387815475464</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.89176392555237</v>
+        <v>3.89176344871521</v>
       </c>
       <c r="H1104" t="n">
         <v>19200</v>
@@ -32443,7 +32443,7 @@
         <v>4.86173391342163</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.01383352279663</v>
+        <v>4.01383304595947</v>
       </c>
       <c r="H1106" t="n">
         <v>1366</v>
@@ -32501,7 +32501,7 @@
         <v>4.67283201217651</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.85787606239319</v>
+        <v>3.85787653923035</v>
       </c>
       <c r="H1108" t="n">
         <v>22337</v>
@@ -32646,7 +32646,7 @@
         <v>4.93132877349854</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.07129049301147</v>
+        <v>4.07129001617432</v>
       </c>
       <c r="H1113" t="n">
         <v>5493</v>
@@ -32704,7 +32704,7 @@
         <v>4.96115589141846</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.09591579437256</v>
+        <v>4.09591627120972</v>
       </c>
       <c r="H1115" t="n">
         <v>3129</v>
@@ -32849,7 +32849,7 @@
         <v>4.95121288299561</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.08770656585693</v>
+        <v>4.08770704269409</v>
       </c>
       <c r="H1120" t="n">
         <v>18325</v>
@@ -32936,7 +32936,7 @@
         <v>5.09040403366089</v>
       </c>
       <c r="G1123" t="n">
-        <v>4.20262241363525</v>
+        <v>4.2026219367981</v>
       </c>
       <c r="H1123" t="n">
         <v>2643</v>
@@ -32994,7 +32994,7 @@
         <v>5.26936388015747</v>
       </c>
       <c r="G1125" t="n">
-        <v>4.35037136077881</v>
+        <v>4.35037088394165</v>
       </c>
       <c r="H1125" t="n">
         <v>51412</v>
@@ -33023,7 +33023,7 @@
         <v>6.46242713928223</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.33536052703857</v>
+        <v>5.33536005020142</v>
       </c>
       <c r="H1126" t="n">
         <v>99604</v>
@@ -33226,7 +33226,7 @@
         <v>6.5220799446106</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.38461017608643</v>
+        <v>5.38460969924927</v>
       </c>
       <c r="H1133" t="n">
         <v>27860</v>
@@ -33255,7 +33255,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1134" t="n">
         <v>13957</v>
@@ -33284,7 +33284,7 @@
         <v>6.32323598861694</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.22044563293457</v>
+        <v>5.22044515609741</v>
       </c>
       <c r="H1135" t="n">
         <v>8859</v>
@@ -33342,7 +33342,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.28611087799072</v>
+        <v>5.28611135482788</v>
       </c>
       <c r="H1137" t="n">
         <v>27133</v>
@@ -33371,7 +33371,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1138" t="n">
         <v>11238</v>
@@ -33400,7 +33400,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1139" t="n">
         <v>17035</v>
@@ -33458,7 +33458,7 @@
         <v>6.62150192260742</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.46669244766235</v>
+        <v>5.4666919708252</v>
       </c>
       <c r="H1141" t="n">
         <v>8119</v>
@@ -33487,7 +33487,7 @@
         <v>6.5220799446106</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38461017608643</v>
+        <v>5.38460969924927</v>
       </c>
       <c r="H1142" t="n">
         <v>3588</v>
@@ -33516,7 +33516,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1143" t="n">
         <v>10342</v>
@@ -33545,7 +33545,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1144" t="n">
         <v>3812</v>
@@ -33661,7 +33661,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1148" t="n">
         <v>13678</v>
@@ -33719,7 +33719,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686170578003</v>
       </c>
       <c r="H1150" t="n">
         <v>11910</v>
@@ -33748,7 +33748,7 @@
         <v>6.20392990112305</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.12194633483887</v>
+        <v>5.12194681167603</v>
       </c>
       <c r="H1151" t="n">
         <v>20255</v>
@@ -33806,7 +33806,7 @@
         <v>5.8460111618042</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.82644987106323</v>
+        <v>4.82644939422607</v>
       </c>
       <c r="H1153" t="n">
         <v>101991</v>
@@ -33835,7 +33835,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.77719974517822</v>
+        <v>4.77720022201538</v>
       </c>
       <c r="H1154" t="n">
         <v>28422</v>
@@ -33951,7 +33951,7 @@
         <v>5.80624198913574</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.79361629486084</v>
+        <v>4.793616771698</v>
       </c>
       <c r="H1158" t="n">
         <v>8096</v>
@@ -34009,7 +34009,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1160" t="n">
-        <v>4.77719974517822</v>
+        <v>4.77720022201538</v>
       </c>
       <c r="H1160" t="n">
         <v>9876</v>
@@ -34038,7 +34038,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.84286546707153</v>
+        <v>4.84286499023438</v>
       </c>
       <c r="H1161" t="n">
         <v>6176</v>
@@ -34183,7 +34183,7 @@
         <v>5.66705179214478</v>
       </c>
       <c r="G1166" t="n">
-        <v>4.67870140075684</v>
+        <v>4.67870092391968</v>
       </c>
       <c r="H1166" t="n">
         <v>6093</v>
@@ -34241,7 +34241,7 @@
         <v>5.66705179214478</v>
       </c>
       <c r="G1168" t="n">
-        <v>4.67870140075684</v>
+        <v>4.67870092391968</v>
       </c>
       <c r="H1168" t="n">
         <v>5491</v>
@@ -34328,7 +34328,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1171" t="n">
         <v>24633</v>
@@ -34415,7 +34415,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1174" t="n">
         <v>11971</v>
@@ -34444,7 +34444,7 @@
         <v>6.2834677696228</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.18761253356934</v>
+        <v>5.18761205673218</v>
       </c>
       <c r="H1175" t="n">
         <v>6878</v>
@@ -34531,7 +34531,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1178" t="n">
-        <v>5.02344799041748</v>
+        <v>5.02344751358032</v>
       </c>
       <c r="H1178" t="n">
         <v>8607</v>
@@ -34560,7 +34560,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.02344799041748</v>
+        <v>5.02344751358032</v>
       </c>
       <c r="H1179" t="n">
         <v>3300</v>
@@ -34618,7 +34618,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1181" t="n">
         <v>11181</v>
@@ -34792,7 +34792,7 @@
         <v>5.82612705230713</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.81003284454346</v>
+        <v>4.81003332138062</v>
       </c>
       <c r="H1187" t="n">
         <v>3698</v>
@@ -34937,7 +34937,7 @@
         <v>5.8460111618042</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.82644987106323</v>
+        <v>4.82644939422607</v>
       </c>
       <c r="H1192" t="n">
         <v>9400</v>
@@ -34966,7 +34966,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1193" t="n">
         <v>47925</v>
@@ -35024,7 +35024,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1195" t="n">
         <v>30634</v>
@@ -35198,7 +35198,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.02344799041748</v>
+        <v>5.02344751358032</v>
       </c>
       <c r="H1201" t="n">
         <v>16211</v>
@@ -35227,7 +35227,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.00703048706055</v>
+        <v>5.00703001022339</v>
       </c>
       <c r="H1202" t="n">
         <v>4375</v>
@@ -35575,7 +35575,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.00703048706055</v>
+        <v>5.00703001022339</v>
       </c>
       <c r="H1214" t="n">
         <v>5416</v>
@@ -35604,7 +35604,7 @@
         <v>6.00508594512939</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.9577808380127</v>
+        <v>4.95778131484985</v>
       </c>
       <c r="H1215" t="n">
         <v>5804</v>
@@ -35691,7 +35691,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.84286546707153</v>
+        <v>4.84286499023438</v>
       </c>
       <c r="H1218" t="n">
         <v>6662</v>
@@ -35720,7 +35720,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.84286546707153</v>
+        <v>4.84286499023438</v>
       </c>
       <c r="H1219" t="n">
         <v>14968</v>
@@ -35807,7 +35807,7 @@
         <v>5.82612705230713</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.81003284454346</v>
+        <v>4.81003332138062</v>
       </c>
       <c r="H1222" t="n">
         <v>2725</v>
@@ -35865,7 +35865,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.77719974517822</v>
+        <v>4.77720022201538</v>
       </c>
       <c r="H1224" t="n">
         <v>3929</v>
@@ -35923,7 +35923,7 @@
         <v>5.46820783615112</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.51453638076782</v>
+        <v>4.51453590393066</v>
       </c>
       <c r="H1226" t="n">
         <v>18088</v>
@@ -35952,7 +35952,7 @@
         <v>5.30913209915161</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.38320398330688</v>
+        <v>4.38320350646973</v>
       </c>
       <c r="H1227" t="n">
         <v>13515</v>
@@ -36068,7 +36068,7 @@
         <v>5.66705179214478</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.67870140075684</v>
+        <v>4.67870092391968</v>
       </c>
       <c r="H1231" t="n">
         <v>9791</v>
@@ -36097,7 +36097,7 @@
         <v>5.78635787963867</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.77719974517822</v>
+        <v>4.77720022201538</v>
       </c>
       <c r="H1232" t="n">
         <v>4302</v>
@@ -36155,7 +36155,7 @@
         <v>5.56762981414795</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.59661912918091</v>
+        <v>4.59661865234375</v>
       </c>
       <c r="H1234" t="n">
         <v>3349</v>
@@ -36184,7 +36184,7 @@
         <v>5.62728309631348</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.64586782455444</v>
+        <v>4.64586877822876</v>
       </c>
       <c r="H1235" t="n">
         <v>26498</v>
@@ -36300,7 +36300,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.00703048706055</v>
+        <v>5.00703001022339</v>
       </c>
       <c r="H1239" t="n">
         <v>53203</v>
@@ -36387,7 +36387,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1242" t="n">
         <v>23329</v>
@@ -36416,7 +36416,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1243" t="n">
         <v>9853</v>
@@ -36445,7 +36445,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1244" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686170578003</v>
       </c>
       <c r="H1244" t="n">
         <v>3756</v>
@@ -36503,7 +36503,7 @@
         <v>6.62150192260742</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.46669244766235</v>
+        <v>5.4666919708252</v>
       </c>
       <c r="H1246" t="n">
         <v>21941</v>
@@ -36532,7 +36532,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1247" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1247" t="n">
         <v>21606</v>
@@ -36561,7 +36561,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1248" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1248" t="n">
         <v>6631</v>
@@ -36619,7 +36619,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1250" t="n">
         <v>23161</v>
@@ -36677,7 +36677,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1252" t="n">
         <v>18069</v>
@@ -36706,7 +36706,7 @@
         <v>6.20392990112305</v>
       </c>
       <c r="G1253" t="n">
-        <v>5.12194633483887</v>
+        <v>5.12194681167603</v>
       </c>
       <c r="H1253" t="n">
         <v>16764</v>
@@ -36735,7 +36735,7 @@
         <v>6.2834677696228</v>
       </c>
       <c r="G1254" t="n">
-        <v>5.18761253356934</v>
+        <v>5.18761205673218</v>
       </c>
       <c r="H1254" t="n">
         <v>9343</v>
@@ -36764,7 +36764,7 @@
         <v>6.32323598861694</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.22044563293457</v>
+        <v>5.22044515609741</v>
       </c>
       <c r="H1255" t="n">
         <v>7716</v>
@@ -36793,7 +36793,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1256" t="n">
         <v>4998</v>
@@ -36822,7 +36822,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1257" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1257" t="n">
         <v>6915</v>
@@ -36851,7 +36851,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1258" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1258" t="n">
         <v>3541</v>
@@ -36880,7 +36880,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1259" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1259" t="n">
         <v>1643</v>
@@ -36938,7 +36938,7 @@
         <v>6.2834677696228</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.18761253356934</v>
+        <v>5.18761205673218</v>
       </c>
       <c r="H1261" t="n">
         <v>17742</v>
@@ -36967,7 +36967,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1262" t="n">
         <v>6965</v>
@@ -36996,7 +36996,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1263" t="n">
         <v>5007</v>
@@ -37025,7 +37025,7 @@
         <v>6.32323598861694</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.22044563293457</v>
+        <v>5.22044515609741</v>
       </c>
       <c r="H1264" t="n">
         <v>22374</v>
@@ -37083,7 +37083,7 @@
         <v>6.20392990112305</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.12194633483887</v>
+        <v>5.12194681167603</v>
       </c>
       <c r="H1266" t="n">
         <v>2013</v>
@@ -37112,7 +37112,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1267" t="n">
         <v>2627</v>
@@ -37141,7 +37141,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1268" t="n">
         <v>18597</v>
@@ -37170,7 +37170,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1269" t="n">
         <v>7993</v>
@@ -37199,7 +37199,7 @@
         <v>6.22381496429443</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.13836336135864</v>
+        <v>5.13836288452148</v>
       </c>
       <c r="H1270" t="n">
         <v>1807</v>
@@ -37286,7 +37286,7 @@
         <v>6.5220799446106</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.38461017608643</v>
+        <v>5.38460969924927</v>
       </c>
       <c r="H1273" t="n">
         <v>17389</v>
@@ -37315,7 +37315,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1274" t="n">
         <v>7807</v>
@@ -37344,7 +37344,7 @@
         <v>6.46242713928223</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.33536052703857</v>
+        <v>5.33536005020142</v>
       </c>
       <c r="H1275" t="n">
         <v>5715</v>
@@ -37373,7 +37373,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.28611087799072</v>
+        <v>5.28611135482788</v>
       </c>
       <c r="H1276" t="n">
         <v>10654</v>
@@ -37402,7 +37402,7 @@
         <v>6.5220799446106</v>
       </c>
       <c r="G1277" t="n">
-        <v>5.38461017608643</v>
+        <v>5.38460969924927</v>
       </c>
       <c r="H1277" t="n">
         <v>35988</v>
@@ -37431,7 +37431,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1278" t="n">
         <v>8612</v>
@@ -37489,7 +37489,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1280" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686170578003</v>
       </c>
       <c r="H1280" t="n">
         <v>7560</v>
@@ -37518,7 +37518,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1281" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1281" t="n">
         <v>1617</v>
@@ -37547,7 +37547,7 @@
         <v>6.34312105178833</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.23686218261719</v>
+        <v>5.23686170578003</v>
       </c>
       <c r="H1282" t="n">
         <v>5586</v>
@@ -37576,7 +37576,7 @@
         <v>6.32323598861694</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.22044563293457</v>
+        <v>5.22044515609741</v>
       </c>
       <c r="H1283" t="n">
         <v>1181</v>
@@ -37605,7 +37605,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1284" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1284" t="n">
         <v>6482</v>
@@ -37663,7 +37663,7 @@
         <v>6.08462381362915</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.02344799041748</v>
+        <v>5.02344751358032</v>
       </c>
       <c r="H1286" t="n">
         <v>6769</v>
@@ -37692,7 +37692,7 @@
         <v>6.00508594512939</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.9577808380127</v>
+        <v>4.95778131484985</v>
       </c>
       <c r="H1287" t="n">
         <v>19459</v>
@@ -37721,7 +37721,7 @@
         <v>5.86589479446411</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.84286546707153</v>
+        <v>4.84286499023438</v>
       </c>
       <c r="H1288" t="n">
         <v>16874</v>
@@ -37750,7 +37750,7 @@
         <v>6.00508594512939</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.9577808380127</v>
+        <v>4.95778131484985</v>
       </c>
       <c r="H1289" t="n">
         <v>3590</v>
@@ -37808,7 +37808,7 @@
         <v>6.06473922729492</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.00703048706055</v>
+        <v>5.00703001022339</v>
       </c>
       <c r="H1291" t="n">
         <v>15979</v>
@@ -37837,7 +37837,7 @@
         <v>6.26358318328857</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.17119598388672</v>
+        <v>5.17119550704956</v>
       </c>
       <c r="H1292" t="n">
         <v>35714</v>
@@ -37866,7 +37866,7 @@
         <v>6.3630051612854</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.25327825546265</v>
+        <v>5.2532787322998</v>
       </c>
       <c r="H1293" t="n">
         <v>4015</v>
@@ -37895,7 +37895,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1294" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1294" t="n">
         <v>6839</v>
@@ -38156,7 +38156,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1303" t="n">
         <v>2994</v>
@@ -38185,7 +38185,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1304" t="n">
         <v>12058</v>
@@ -38214,7 +38214,7 @@
         <v>6.32323598861694</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.22044563293457</v>
+        <v>5.22044515609741</v>
       </c>
       <c r="H1305" t="n">
         <v>4299</v>
@@ -38243,7 +38243,7 @@
         <v>6.46242713928223</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.33536052703857</v>
+        <v>5.33536005020142</v>
       </c>
       <c r="H1306" t="n">
         <v>3053</v>
@@ -38330,7 +38330,7 @@
         <v>6.30335187911987</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.20402812957764</v>
+        <v>5.20402860641479</v>
       </c>
       <c r="H1309" t="n">
         <v>4689</v>
@@ -38359,7 +38359,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.28611087799072</v>
+        <v>5.28611135482788</v>
       </c>
       <c r="H1310" t="n">
         <v>3377</v>
@@ -38388,7 +38388,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.28611087799072</v>
+        <v>5.28611135482788</v>
       </c>
       <c r="H1311" t="n">
         <v>5832</v>
@@ -38417,7 +38417,7 @@
         <v>6.4027738571167</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.28611087799072</v>
+        <v>5.28611135482788</v>
       </c>
       <c r="H1312" t="n">
         <v>959</v>
@@ -38446,7 +38446,7 @@
         <v>6.46242713928223</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.33536052703857</v>
+        <v>5.33536005020142</v>
       </c>
       <c r="H1313" t="n">
         <v>19412</v>
@@ -38475,7 +38475,7 @@
         <v>6.46242713928223</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.33536052703857</v>
+        <v>5.33536005020142</v>
       </c>
       <c r="H1314" t="n">
         <v>10335</v>
@@ -38504,7 +38504,7 @@
         <v>6.44254302978516</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.31894445419312</v>
+        <v>5.31894397735596</v>
       </c>
       <c r="H1315" t="n">
         <v>17255</v>
@@ -38591,7 +38591,7 @@
         <v>6.62150192260742</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.46669244766235</v>
+        <v>5.4666919708252</v>
       </c>
       <c r="H1318" t="n">
         <v>9355</v>
@@ -38620,7 +38620,7 @@
         <v>6.50219583511353</v>
       </c>
       <c r="G1319" t="n">
-        <v>5.36819362640381</v>
+        <v>5.36819314956665</v>
       </c>
       <c r="H1319" t="n">
         <v>42896</v>
@@ -38707,7 +38707,7 @@
         <v>6.84023094177246</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.64727401733398</v>
+        <v>5.64727449417114</v>
       </c>
       <c r="H1322" t="n">
         <v>41211</v>
@@ -38765,7 +38765,7 @@
         <v>7.37710905075073</v>
       </c>
       <c r="G1324" t="n">
-        <v>6.09051990509033</v>
+        <v>6.09051895141602</v>
       </c>
       <c r="H1324" t="n">
         <v>187553</v>
@@ -38881,7 +38881,7 @@
         <v>7.41687822341919</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.12335300445557</v>
+        <v>6.12335252761841</v>
       </c>
       <c r="H1328" t="n">
         <v>35155</v>
@@ -38968,7 +38968,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.45168209075928</v>
+        <v>6.45168256759644</v>
       </c>
       <c r="H1331" t="n">
         <v>54741</v>
@@ -38997,7 +38997,7 @@
         <v>7.93387222290039</v>
       </c>
       <c r="G1332" t="n">
-        <v>6.55018091201782</v>
+        <v>6.55018138885498</v>
       </c>
       <c r="H1332" t="n">
         <v>51335</v>
@@ -39026,7 +39026,7 @@
         <v>8.35144519805908</v>
       </c>
       <c r="G1333" t="n">
-        <v>6.89492845535278</v>
+        <v>6.89492797851562</v>
       </c>
       <c r="H1333" t="n">
         <v>109110</v>
@@ -39055,7 +39055,7 @@
         <v>8.35144519805908</v>
       </c>
       <c r="G1334" t="n">
-        <v>6.89492845535278</v>
+        <v>6.89492797851562</v>
       </c>
       <c r="H1334" t="n">
         <v>52925</v>
@@ -39200,7 +39200,7 @@
         <v>7.93387222290039</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.55018091201782</v>
+        <v>6.55018138885498</v>
       </c>
       <c r="H1339" t="n">
         <v>12699</v>
@@ -39258,7 +39258,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1341" t="n">
-        <v>6.45168209075928</v>
+        <v>6.45168256759644</v>
       </c>
       <c r="H1341" t="n">
         <v>8588</v>
@@ -39287,7 +39287,7 @@
         <v>7.83444976806641</v>
       </c>
       <c r="G1342" t="n">
-        <v>6.46809816360474</v>
+        <v>6.46809864044189</v>
       </c>
       <c r="H1342" t="n">
         <v>15203</v>
@@ -39432,7 +39432,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1347" t="n">
-        <v>6.45168209075928</v>
+        <v>6.45168256759644</v>
       </c>
       <c r="H1347" t="n">
         <v>8135</v>
@@ -39461,7 +39461,7 @@
         <v>7.85433483123779</v>
       </c>
       <c r="G1348" t="n">
-        <v>6.48451519012451</v>
+        <v>6.48451566696167</v>
       </c>
       <c r="H1348" t="n">
         <v>20706</v>
@@ -39548,7 +39548,7 @@
         <v>7.93387222290039</v>
       </c>
       <c r="G1351" t="n">
-        <v>6.55018091201782</v>
+        <v>6.55018138885498</v>
       </c>
       <c r="H1351" t="n">
         <v>10894</v>
@@ -39577,7 +39577,7 @@
         <v>7.85433483123779</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.48451519012451</v>
+        <v>6.48451566696167</v>
       </c>
       <c r="H1352" t="n">
         <v>12512</v>
@@ -39606,7 +39606,7 @@
         <v>7.81456613540649</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.45168209075928</v>
+        <v>6.45168256759644</v>
       </c>
       <c r="H1353" t="n">
         <v>7236</v>
@@ -39722,7 +39722,7 @@
         <v>8.05317878723145</v>
       </c>
       <c r="G1357" t="n">
-        <v>6.64868021011353</v>
+        <v>6.64868068695068</v>
       </c>
       <c r="H1357" t="n">
         <v>26620</v>
@@ -39838,7 +39838,7 @@
         <v>8.11283206939697</v>
       </c>
       <c r="G1361" t="n">
-        <v>6.865797996521</v>
+        <v>6.86579847335815</v>
       </c>
       <c r="H1361" t="n">
         <v>8824</v>
@@ -39867,7 +39867,7 @@
         <v>8.62982559204102</v>
       </c>
       <c r="G1362" t="n">
-        <v>7.30332469940186</v>
+        <v>7.30332374572754</v>
       </c>
       <c r="H1362" t="n">
         <v>134832</v>
@@ -39896,7 +39896,7 @@
         <v>9.08716678619385</v>
       </c>
       <c r="G1363" t="n">
-        <v>7.69036722183228</v>
+        <v>7.69036626815796</v>
       </c>
       <c r="H1363" t="n">
         <v>159063</v>
@@ -39954,7 +39954,7 @@
         <v>9.18658924102783</v>
       </c>
       <c r="G1365" t="n">
-        <v>7.77450609207153</v>
+        <v>7.77450704574585</v>
       </c>
       <c r="H1365" t="n">
         <v>41909</v>
@@ -39983,7 +39983,7 @@
         <v>9.08716678619385</v>
       </c>
       <c r="G1366" t="n">
-        <v>7.69036722183228</v>
+        <v>7.69036626815796</v>
       </c>
       <c r="H1366" t="n">
         <v>58746</v>
@@ -40041,7 +40041,7 @@
         <v>9.1269359588623</v>
       </c>
       <c r="G1368" t="n">
-        <v>7.72402238845825</v>
+        <v>7.72402334213257</v>
       </c>
       <c r="H1368" t="n">
         <v>34306</v>
@@ -40070,7 +40070,7 @@
         <v>9.04739761352539</v>
       </c>
       <c r="G1369" t="n">
-        <v>7.65670919418335</v>
+        <v>7.65671014785767</v>
       </c>
       <c r="H1369" t="n">
         <v>11989</v>
@@ -40099,7 +40099,7 @@
         <v>9.26612663269043</v>
       </c>
       <c r="G1370" t="n">
-        <v>7.84181880950928</v>
+        <v>7.84181785583496</v>
       </c>
       <c r="H1370" t="n">
         <v>33398</v>
@@ -40128,7 +40128,7 @@
         <v>9.2860107421875</v>
       </c>
       <c r="G1371" t="n">
-        <v>7.85864639282227</v>
+        <v>7.85864543914795</v>
       </c>
       <c r="H1371" t="n">
         <v>24801</v>
@@ -40157,7 +40157,7 @@
         <v>9.30589485168457</v>
       </c>
       <c r="G1372" t="n">
-        <v>7.87547302246094</v>
+        <v>7.87547397613525</v>
       </c>
       <c r="H1372" t="n">
         <v>18542</v>
@@ -40186,7 +40186,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1373" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1373" t="n">
         <v>29230</v>
@@ -40273,7 +40273,7 @@
         <v>9.26612663269043</v>
       </c>
       <c r="G1376" t="n">
-        <v>7.84181880950928</v>
+        <v>7.84181785583496</v>
       </c>
       <c r="H1376" t="n">
         <v>12346</v>
@@ -40302,7 +40302,7 @@
         <v>9.26612663269043</v>
       </c>
       <c r="G1377" t="n">
-        <v>7.84181880950928</v>
+        <v>7.84181785583496</v>
       </c>
       <c r="H1377" t="n">
         <v>38278</v>
@@ -40389,7 +40389,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1380" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1380" t="n">
         <v>28609</v>
@@ -40447,7 +40447,7 @@
         <v>9.2064733505249</v>
       </c>
       <c r="G1382" t="n">
-        <v>7.79133462905884</v>
+        <v>7.79133415222168</v>
       </c>
       <c r="H1382" t="n">
         <v>15116</v>
@@ -40476,7 +40476,7 @@
         <v>9.30589485168457</v>
       </c>
       <c r="G1383" t="n">
-        <v>7.87547302246094</v>
+        <v>7.87547397613525</v>
       </c>
       <c r="H1383" t="n">
         <v>23273</v>
@@ -40505,7 +40505,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1384" t="n">
         <v>16087</v>
@@ -40534,7 +40534,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1385" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1385" t="n">
         <v>11464</v>
@@ -40563,7 +40563,7 @@
         <v>9.34566402435303</v>
       </c>
       <c r="G1386" t="n">
-        <v>7.90912914276123</v>
+        <v>7.90913009643555</v>
       </c>
       <c r="H1386" t="n">
         <v>15626</v>
@@ -40592,7 +40592,7 @@
         <v>9.1269359588623</v>
       </c>
       <c r="G1387" t="n">
-        <v>7.72402238845825</v>
+        <v>7.72402334213257</v>
       </c>
       <c r="H1387" t="n">
         <v>11091</v>
@@ -40621,7 +40621,7 @@
         <v>9.06728267669678</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.67353820800781</v>
+        <v>7.67353916168213</v>
       </c>
       <c r="H1388" t="n">
         <v>29048</v>
@@ -40650,7 +40650,7 @@
         <v>9.1269359588623</v>
       </c>
       <c r="G1389" t="n">
-        <v>7.72402238845825</v>
+        <v>7.72402334213257</v>
       </c>
       <c r="H1389" t="n">
         <v>7698</v>
@@ -40679,7 +40679,7 @@
         <v>9.1269359588623</v>
       </c>
       <c r="G1390" t="n">
-        <v>7.72402238845825</v>
+        <v>7.72402334213257</v>
       </c>
       <c r="H1390" t="n">
         <v>23975</v>
@@ -40708,7 +40708,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1391" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1391" t="n">
         <v>58200</v>
@@ -40766,7 +40766,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1393" t="n">
         <v>28494</v>
@@ -40795,7 +40795,7 @@
         <v>10.041618347168</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.49810886383057</v>
+        <v>8.49810791015625</v>
       </c>
       <c r="H1394" t="n">
         <v>84499</v>
@@ -40824,7 +40824,7 @@
         <v>9.78312110900879</v>
       </c>
       <c r="G1395" t="n">
-        <v>8.27934551239014</v>
+        <v>8.27934455871582</v>
       </c>
       <c r="H1395" t="n">
         <v>37697</v>
@@ -40853,7 +40853,7 @@
         <v>9.72346782684326</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.22886180877686</v>
+        <v>8.22886085510254</v>
       </c>
       <c r="H1396" t="n">
         <v>13759</v>
@@ -40882,7 +40882,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1397" t="n">
         <v>13805</v>
@@ -40911,7 +40911,7 @@
         <v>9.90242671966553</v>
       </c>
       <c r="G1398" t="n">
-        <v>8.38031101226807</v>
+        <v>8.38031196594238</v>
       </c>
       <c r="H1398" t="n">
         <v>21910</v>
@@ -40940,7 +40940,7 @@
         <v>9.80300521850586</v>
       </c>
       <c r="G1399" t="n">
-        <v>8.29617214202881</v>
+        <v>8.29617309570312</v>
       </c>
       <c r="H1399" t="n">
         <v>35283</v>
@@ -40969,7 +40969,7 @@
         <v>9.78312110900879</v>
       </c>
       <c r="G1400" t="n">
-        <v>8.27934551239014</v>
+        <v>8.27934455871582</v>
       </c>
       <c r="H1400" t="n">
         <v>7120</v>
@@ -41027,7 +41027,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1402" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1402" t="n">
         <v>11326</v>
@@ -41201,7 +41201,7 @@
         <v>9.16670513153076</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.75767850875854</v>
+        <v>7.75767946243286</v>
       </c>
       <c r="H1408" t="n">
         <v>8026</v>
@@ -41317,7 +41317,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1412" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1412" t="n">
         <v>4128</v>
@@ -41520,7 +41520,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1419" t="n">
         <v>8388</v>
@@ -41723,7 +41723,7 @@
         <v>9.62404632568359</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.14472103118896</v>
+        <v>8.14472198486328</v>
       </c>
       <c r="H1426" t="n">
         <v>12026</v>
@@ -41897,7 +41897,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1432" t="n">
         <v>7027</v>
@@ -41926,7 +41926,7 @@
         <v>9.2860107421875</v>
       </c>
       <c r="G1433" t="n">
-        <v>7.85864639282227</v>
+        <v>7.85864543914795</v>
       </c>
       <c r="H1433" t="n">
         <v>5077</v>
@@ -42129,7 +42129,7 @@
         <v>9.38543319702148</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.94278621673584</v>
+        <v>7.94278526306152</v>
       </c>
       <c r="H1440" t="n">
         <v>5511</v>
@@ -42216,7 +42216,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1443" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1443" t="n">
         <v>4227</v>
@@ -42245,7 +42245,7 @@
         <v>9.32577991485596</v>
       </c>
       <c r="G1444" t="n">
-        <v>7.89230251312256</v>
+        <v>7.89230155944824</v>
       </c>
       <c r="H1444" t="n">
         <v>3850</v>
@@ -42274,7 +42274,7 @@
         <v>9.30589485168457</v>
       </c>
       <c r="G1445" t="n">
-        <v>7.87547302246094</v>
+        <v>7.87547397613525</v>
       </c>
       <c r="H1445" t="n">
         <v>14435</v>
@@ -42303,7 +42303,7 @@
         <v>9.2860107421875</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.85864639282227</v>
+        <v>7.85864543914795</v>
       </c>
       <c r="H1446" t="n">
         <v>8211</v>
@@ -42419,7 +42419,7 @@
         <v>9.78312110900879</v>
       </c>
       <c r="G1450" t="n">
-        <v>8.27934551239014</v>
+        <v>8.27934455871582</v>
       </c>
       <c r="H1450" t="n">
         <v>76510</v>
@@ -42477,7 +42477,7 @@
         <v>9.86265754699707</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.34665584564209</v>
+        <v>8.34665489196777</v>
       </c>
       <c r="H1452" t="n">
         <v>67950</v>
@@ -42506,7 +42506,7 @@
         <v>9.90242671966553</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.38031101226807</v>
+        <v>8.38031196594238</v>
       </c>
       <c r="H1453" t="n">
         <v>56084</v>
@@ -42564,7 +42564,7 @@
         <v>9.70358276367188</v>
       </c>
       <c r="G1455" t="n">
-        <v>8.21203136444092</v>
+        <v>8.21203231811523</v>
       </c>
       <c r="H1455" t="n">
         <v>26678</v>
@@ -42651,7 +42651,7 @@
         <v>9.72346782684326</v>
       </c>
       <c r="G1458" t="n">
-        <v>8.22886180877686</v>
+        <v>8.22886085510254</v>
       </c>
       <c r="H1458" t="n">
         <v>18134</v>
@@ -42680,7 +42680,7 @@
         <v>9.62404632568359</v>
       </c>
       <c r="G1459" t="n">
-        <v>8.14472103118896</v>
+        <v>8.14472198486328</v>
       </c>
       <c r="H1459" t="n">
         <v>14289</v>
@@ -42709,7 +42709,7 @@
         <v>9.70358276367188</v>
       </c>
       <c r="G1460" t="n">
-        <v>8.21203136444092</v>
+        <v>8.21203231811523</v>
       </c>
       <c r="H1460" t="n">
         <v>15239</v>
@@ -42767,7 +42767,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1462" t="n">
         <v>12986</v>
@@ -42796,7 +42796,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1463" t="n">
         <v>14919</v>
@@ -42941,7 +42941,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1468" t="n">
         <v>14461</v>
@@ -42970,7 +42970,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1469" t="n">
         <v>9074</v>
@@ -42999,7 +42999,7 @@
         <v>9.58427715301514</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.11106491088867</v>
+        <v>8.11106586456299</v>
       </c>
       <c r="H1470" t="n">
         <v>7455</v>
@@ -43086,7 +43086,7 @@
         <v>9.34566402435303</v>
       </c>
       <c r="G1473" t="n">
-        <v>7.90912914276123</v>
+        <v>7.90913009643555</v>
       </c>
       <c r="H1473" t="n">
         <v>10085</v>
@@ -43144,7 +43144,7 @@
         <v>9.34566402435303</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.90912914276123</v>
+        <v>7.90913009643555</v>
       </c>
       <c r="H1475" t="n">
         <v>12322</v>
@@ -43173,7 +43173,7 @@
         <v>9.26612663269043</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.84181880950928</v>
+        <v>7.84181785583496</v>
       </c>
       <c r="H1476" t="n">
         <v>15275</v>
@@ -43289,7 +43289,7 @@
         <v>9.34566402435303</v>
       </c>
       <c r="G1480" t="n">
-        <v>7.90912914276123</v>
+        <v>7.90913009643555</v>
       </c>
       <c r="H1480" t="n">
         <v>13399</v>
@@ -43318,7 +43318,7 @@
         <v>9.38543319702148</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.94278621673584</v>
+        <v>7.94278526306152</v>
       </c>
       <c r="H1481" t="n">
         <v>15288</v>
@@ -43347,7 +43347,7 @@
         <v>9.38543319702148</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.94278621673584</v>
+        <v>7.94278526306152</v>
       </c>
       <c r="H1482" t="n">
         <v>16746</v>
@@ -43376,7 +43376,7 @@
         <v>9.38543319702148</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.94278621673584</v>
+        <v>7.94278526306152</v>
       </c>
       <c r="H1483" t="n">
         <v>28491</v>
@@ -43434,7 +43434,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1485" t="n">
         <v>32210</v>
@@ -43463,7 +43463,7 @@
         <v>9.54450798034668</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.07740879058838</v>
+        <v>8.0774097442627</v>
       </c>
       <c r="H1486" t="n">
         <v>33330</v>
@@ -43550,7 +43550,7 @@
         <v>9.70358276367188</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.21203136444092</v>
+        <v>8.21203231811523</v>
       </c>
       <c r="H1489" t="n">
         <v>48479</v>
@@ -43608,7 +43608,7 @@
         <v>9.80300521850586</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.29617214202881</v>
+        <v>8.29617309570312</v>
       </c>
       <c r="H1491" t="n">
         <v>43631</v>
@@ -43666,7 +43666,7 @@
         <v>11.3838148117065</v>
       </c>
       <c r="G1493" t="n">
-        <v>9.63399314880371</v>
+        <v>9.63399410247803</v>
       </c>
       <c r="H1493" t="n">
         <v>377988</v>
@@ -43695,7 +43695,7 @@
         <v>10.9364156723022</v>
       </c>
       <c r="G1494" t="n">
-        <v>9.25536441802979</v>
+        <v>9.25536346435547</v>
       </c>
       <c r="H1494" t="n">
         <v>268225</v>
@@ -43840,7 +43840,7 @@
         <v>10.8867053985596</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.21329593658447</v>
+        <v>9.21329689025879</v>
       </c>
       <c r="H1499" t="n">
         <v>31584</v>
@@ -43898,7 +43898,7 @@
         <v>10.9861268997192</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.29743480682373</v>
+        <v>9.29743576049805</v>
       </c>
       <c r="H1501" t="n">
         <v>40725</v>
@@ -43985,7 +43985,7 @@
         <v>10.6381502151489</v>
       </c>
       <c r="G1504" t="n">
-        <v>9.00294589996338</v>
+        <v>9.0029468536377</v>
       </c>
       <c r="H1504" t="n">
         <v>51526</v>
@@ -44014,7 +44014,7 @@
         <v>10.8867053985596</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.21329593658447</v>
+        <v>9.21329689025879</v>
       </c>
       <c r="H1505" t="n">
         <v>23109</v>
@@ -44043,7 +44043,7 @@
         <v>11.3341035842896</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.5919246673584</v>
+        <v>9.59192371368408</v>
       </c>
       <c r="H1506" t="n">
         <v>43225</v>
@@ -44072,7 +44072,7 @@
         <v>11.2346820831299</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.50778484344482</v>
+        <v>9.50778579711914</v>
       </c>
       <c r="H1507" t="n">
         <v>67189</v>
@@ -44507,7 +44507,7 @@
         <v>11.7317905426025</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.92848205566406</v>
+        <v>9.92848110198975</v>
       </c>
       <c r="H1522" t="n">
         <v>23655</v>
@@ -44536,7 +44536,7 @@
         <v>11.7317905426025</v>
       </c>
       <c r="G1523" t="n">
-        <v>9.92848205566406</v>
+        <v>9.92848110198975</v>
       </c>
       <c r="H1523" t="n">
         <v>14004</v>
@@ -44710,7 +44710,7 @@
         <v>11.6820802688599</v>
       </c>
       <c r="G1529" t="n">
-        <v>9.88641166687012</v>
+        <v>9.88641262054443</v>
       </c>
       <c r="H1529" t="n">
         <v>12954</v>
@@ -44739,7 +44739,7 @@
         <v>11.4832363128662</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.71813297271729</v>
+        <v>9.71813201904297</v>
       </c>
       <c r="H1530" t="n">
         <v>10624</v>
@@ -44768,7 +44768,7 @@
         <v>11.2346820831299</v>
       </c>
       <c r="G1531" t="n">
-        <v>9.50778484344482</v>
+        <v>9.50778579711914</v>
       </c>
       <c r="H1531" t="n">
         <v>15287</v>
@@ -44797,7 +44797,7 @@
         <v>11.3838148117065</v>
       </c>
       <c r="G1532" t="n">
-        <v>9.63399314880371</v>
+        <v>9.63399410247803</v>
       </c>
       <c r="H1532" t="n">
         <v>18150</v>
@@ -44884,7 +44884,7 @@
         <v>10.8867053985596</v>
       </c>
       <c r="G1535" t="n">
-        <v>9.21329593658447</v>
+        <v>9.21329689025879</v>
       </c>
       <c r="H1535" t="n">
         <v>39579</v>
@@ -44913,7 +44913,7 @@
         <v>10.9364156723022</v>
       </c>
       <c r="G1536" t="n">
-        <v>9.25536441802979</v>
+        <v>9.25536346435547</v>
       </c>
       <c r="H1536" t="n">
         <v>14029</v>
@@ -44942,7 +44942,7 @@
         <v>11.3341035842896</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.5919246673584</v>
+        <v>9.59192371368408</v>
       </c>
       <c r="H1537" t="n">
         <v>33588</v>
@@ -45000,7 +45000,7 @@
         <v>10.8867053985596</v>
       </c>
       <c r="G1539" t="n">
-        <v>9.21329593658447</v>
+        <v>9.21329689025879</v>
       </c>
       <c r="H1539" t="n">
         <v>22652</v>
@@ -45029,7 +45029,7 @@
         <v>11.0358381271362</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.33950519561768</v>
+        <v>9.33950424194336</v>
       </c>
       <c r="H1540" t="n">
         <v>11340</v>
@@ -45174,7 +45174,7 @@
         <v>11.0358381271362</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.33950519561768</v>
+        <v>9.33950424194336</v>
       </c>
       <c r="H1545" t="n">
         <v>14075</v>
@@ -45261,7 +45261,7 @@
         <v>11.3341035842896</v>
       </c>
       <c r="G1548" t="n">
-        <v>9.5919246673584</v>
+        <v>9.59192371368408</v>
       </c>
       <c r="H1548" t="n">
         <v>57972</v>
@@ -45348,7 +45348,7 @@
         <v>13.1734104156494</v>
       </c>
       <c r="G1551" t="n">
-        <v>11.1485090255737</v>
+        <v>11.1485080718994</v>
       </c>
       <c r="H1551" t="n">
         <v>93266</v>
@@ -45493,7 +45493,7 @@
         <v>13.3225431442261</v>
       </c>
       <c r="G1556" t="n">
-        <v>11.2747163772583</v>
+        <v>11.2747173309326</v>
       </c>
       <c r="H1556" t="n">
         <v>44511</v>
@@ -45551,7 +45551,7 @@
         <v>14.018497467041</v>
       </c>
       <c r="G1558" t="n">
-        <v>11.8636960983276</v>
+        <v>11.863697052002</v>
       </c>
       <c r="H1558" t="n">
         <v>41401</v>
@@ -45580,7 +45580,7 @@
         <v>13.968786239624</v>
       </c>
       <c r="G1559" t="n">
-        <v>11.8216257095337</v>
+        <v>11.8216247558594</v>
       </c>
       <c r="H1559" t="n">
         <v>36864</v>
@@ -45609,7 +45609,7 @@
         <v>13.919075012207</v>
       </c>
       <c r="G1560" t="n">
-        <v>11.7795562744141</v>
+        <v>11.7795572280884</v>
       </c>
       <c r="H1560" t="n">
         <v>13801</v>
@@ -45667,7 +45667,7 @@
         <v>13.3722543716431</v>
       </c>
       <c r="G1562" t="n">
-        <v>11.3167886734009</v>
+        <v>11.3167877197266</v>
       </c>
       <c r="H1562" t="n">
         <v>29173</v>
@@ -45754,7 +45754,7 @@
         <v>12.4774560928345</v>
       </c>
       <c r="G1565" t="n">
-        <v>10.5595302581787</v>
+        <v>10.559531211853</v>
       </c>
       <c r="H1565" t="n">
         <v>39027</v>
@@ -45841,7 +45841,7 @@
         <v>12.8751440048218</v>
       </c>
       <c r="G1568" t="n">
-        <v>10.8960876464844</v>
+        <v>10.896089553833</v>
       </c>
       <c r="H1568" t="n">
         <v>12722</v>
@@ -45870,7 +45870,7 @@
         <v>12.9248552322388</v>
       </c>
       <c r="G1569" t="n">
-        <v>10.9381589889526</v>
+        <v>10.9381580352783</v>
       </c>
       <c r="H1569" t="n">
         <v>16009</v>
@@ -45899,7 +45899,7 @@
         <v>12.5271673202515</v>
       </c>
       <c r="G1570" t="n">
-        <v>10.6015996932983</v>
+        <v>10.601598739624</v>
       </c>
       <c r="H1570" t="n">
         <v>29253</v>
@@ -46189,7 +46189,7 @@
         <v>13.0242767333984</v>
       </c>
       <c r="G1580" t="n">
-        <v>11.0222978591919</v>
+        <v>11.0222969055176</v>
       </c>
       <c r="H1580" t="n">
         <v>38716</v>
@@ -46276,7 +46276,7 @@
         <v>13.0242767333984</v>
       </c>
       <c r="G1583" t="n">
-        <v>11.0222978591919</v>
+        <v>11.0222969055176</v>
       </c>
       <c r="H1583" t="n">
         <v>16818</v>
@@ -46305,7 +46305,7 @@
         <v>12.9248552322388</v>
       </c>
       <c r="G1584" t="n">
-        <v>10.9381589889526</v>
+        <v>10.9381580352783</v>
       </c>
       <c r="H1584" t="n">
         <v>8174</v>
@@ -46334,7 +46334,7 @@
         <v>12.5768775939941</v>
       </c>
       <c r="G1585" t="n">
-        <v>10.643669128418</v>
+        <v>10.6436700820923</v>
       </c>
       <c r="H1585" t="n">
         <v>13169</v>
@@ -46479,7 +46479,7 @@
         <v>14.018497467041</v>
       </c>
       <c r="G1590" t="n">
-        <v>11.8636960983276</v>
+        <v>11.863697052002</v>
       </c>
       <c r="H1590" t="n">
         <v>38553</v>
@@ -46508,7 +46508,7 @@
         <v>13.6605777740479</v>
       </c>
       <c r="G1591" t="n">
-        <v>11.5607929229736</v>
+        <v>11.5607938766479</v>
       </c>
       <c r="H1591" t="n">
         <v>26769</v>
@@ -46566,7 +46566,7 @@
         <v>13.3225431442261</v>
       </c>
       <c r="G1593" t="n">
-        <v>11.2747163772583</v>
+        <v>11.2747173309326</v>
       </c>
       <c r="H1593" t="n">
         <v>31462</v>
@@ -46595,7 +46595,7 @@
         <v>13.1435832977295</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.1232662200928</v>
+        <v>11.1232652664185</v>
       </c>
       <c r="H1594" t="n">
         <v>34832</v>
@@ -46653,7 +46653,7 @@
         <v>13.2430047988892</v>
       </c>
       <c r="G1596" t="n">
-        <v>11.207405090332</v>
+        <v>11.2074041366577</v>
       </c>
       <c r="H1596" t="n">
         <v>24457</v>
@@ -46769,7 +46769,7 @@
         <v>13.0441608428955</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.0391263961792</v>
+        <v>11.0391254425049</v>
       </c>
       <c r="H1600" t="n">
         <v>9252</v>
@@ -46798,7 +46798,7 @@
         <v>13.6605777740479</v>
       </c>
       <c r="G1601" t="n">
-        <v>11.5607929229736</v>
+        <v>11.5607938766479</v>
       </c>
       <c r="H1601" t="n">
         <v>21170</v>
@@ -46827,7 +46827,7 @@
         <v>13.2628898620605</v>
       </c>
       <c r="G1602" t="n">
-        <v>11.224232673645</v>
+        <v>11.2242336273193</v>
       </c>
       <c r="H1602" t="n">
         <v>15471</v>
@@ -46914,7 +46914,7 @@
         <v>13.5810403823853</v>
       </c>
       <c r="G1605" t="n">
-        <v>11.4934816360474</v>
+        <v>11.493480682373</v>
       </c>
       <c r="H1605" t="n">
         <v>8664</v>
@@ -46972,7 +46972,7 @@
         <v>12.6464729309082</v>
       </c>
       <c r="G1607" t="n">
-        <v>10.7025671005249</v>
+        <v>10.7025661468506</v>
       </c>
       <c r="H1607" t="n">
         <v>20409</v>
@@ -47175,7 +47175,7 @@
         <v>11.5130634307861</v>
       </c>
       <c r="G1614" t="n">
-        <v>9.74337577819824</v>
+        <v>9.74337482452393</v>
       </c>
       <c r="H1614" t="n">
         <v>23572</v>
@@ -47262,7 +47262,7 @@
         <v>10.7773408889771</v>
       </c>
       <c r="G1617" t="n">
-        <v>9.36331462860107</v>
+        <v>9.36331367492676</v>
       </c>
       <c r="H1617" t="n">
         <v>20763</v>
@@ -47291,7 +47291,7 @@
         <v>11.254566192627</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.77792549133301</v>
+        <v>9.77792644500732</v>
       </c>
       <c r="H1618" t="n">
         <v>13859</v>
@@ -47320,7 +47320,7 @@
         <v>11.3937568664551</v>
       </c>
       <c r="G1619" t="n">
-        <v>9.8988561630249</v>
+        <v>9.89885520935059</v>
       </c>
       <c r="H1619" t="n">
         <v>62051</v>
@@ -47407,7 +47407,7 @@
         <v>11.274450302124</v>
       </c>
       <c r="G1622" t="n">
-        <v>9.79520225524902</v>
+        <v>9.79520130157471</v>
       </c>
       <c r="H1622" t="n">
         <v>22180</v>
@@ -47436,7 +47436,7 @@
         <v>11.17502784729</v>
       </c>
       <c r="G1623" t="n">
-        <v>9.70882320404053</v>
+        <v>9.70882415771484</v>
       </c>
       <c r="H1623" t="n">
         <v>9831</v>
@@ -47465,7 +47465,7 @@
         <v>11.1949129104614</v>
       </c>
       <c r="G1624" t="n">
-        <v>9.72609996795654</v>
+        <v>9.72609901428223</v>
       </c>
       <c r="H1624" t="n">
         <v>9100</v>
@@ -47523,7 +47523,7 @@
         <v>11.9704036712646</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.3998432159424</v>
+        <v>10.3998441696167</v>
       </c>
       <c r="H1626" t="n">
         <v>39619</v>
@@ -47610,7 +47610,7 @@
         <v>11.9306354522705</v>
       </c>
       <c r="G1629" t="n">
-        <v>10.3652935028076</v>
+        <v>10.3652925491333</v>
       </c>
       <c r="H1629" t="n">
         <v>20238</v>
@@ -47871,7 +47871,7 @@
         <v>11.8312129974365</v>
       </c>
       <c r="G1638" t="n">
-        <v>10.2789144515991</v>
+        <v>10.2789154052734</v>
       </c>
       <c r="H1638" t="n">
         <v>10534</v>
@@ -47900,7 +47900,7 @@
         <v>11.4335260391235</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.93340587615967</v>
+        <v>9.93340492248535</v>
       </c>
       <c r="H1639" t="n">
         <v>28716</v>
@@ -48045,7 +48045,7 @@
         <v>11.9704036712646</v>
       </c>
       <c r="G1644" t="n">
-        <v>10.3998432159424</v>
+        <v>10.3998441696167</v>
       </c>
       <c r="H1644" t="n">
         <v>15294</v>
@@ -48132,7 +48132,7 @@
         <v>11.6920232772827</v>
       </c>
       <c r="G1647" t="n">
-        <v>10.1579885482788</v>
+        <v>10.1579875946045</v>
       </c>
       <c r="H1647" t="n">
         <v>15244</v>
@@ -48364,7 +48364,7 @@
         <v>13.0242767333984</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.3154449462891</v>
+        <v>11.3154439926147</v>
       </c>
       <c r="H1655" t="n">
         <v>38295</v>
@@ -48451,7 +48451,7 @@
         <v>13.0242767333984</v>
       </c>
       <c r="G1658" t="n">
-        <v>11.3154449462891</v>
+        <v>11.3154439926147</v>
       </c>
       <c r="H1658" t="n">
         <v>20686</v>
@@ -48509,7 +48509,7 @@
         <v>13.3424272537231</v>
       </c>
       <c r="G1660" t="n">
-        <v>11.5918531417847</v>
+        <v>11.5918521881104</v>
       </c>
       <c r="H1660" t="n">
         <v>42956</v>
@@ -48538,7 +48538,7 @@
         <v>13.1833524703979</v>
       </c>
       <c r="G1661" t="n">
-        <v>11.4536485671997</v>
+        <v>11.453649520874</v>
       </c>
       <c r="H1661" t="n">
         <v>26004</v>
@@ -48596,7 +48596,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1663" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1663" t="n">
         <v>43335</v>
@@ -48625,7 +48625,7 @@
         <v>13.819652557373</v>
       </c>
       <c r="G1664" t="n">
-        <v>12.0064640045166</v>
+        <v>12.0064630508423</v>
       </c>
       <c r="H1664" t="n">
         <v>58628</v>
@@ -48654,7 +48654,7 @@
         <v>13.4219646453857</v>
       </c>
       <c r="G1665" t="n">
-        <v>11.6609535217285</v>
+        <v>11.6609544754028</v>
       </c>
       <c r="H1665" t="n">
         <v>34626</v>
@@ -48741,7 +48741,7 @@
         <v>13.3026580810547</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.557300567627</v>
+        <v>11.5573015213013</v>
       </c>
       <c r="H1668" t="n">
         <v>37250</v>
@@ -48770,7 +48770,7 @@
         <v>13.2032356262207</v>
       </c>
       <c r="G1669" t="n">
-        <v>11.4709234237671</v>
+        <v>11.4709243774414</v>
       </c>
       <c r="H1669" t="n">
         <v>32232</v>
@@ -48799,7 +48799,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1670" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1670" t="n">
         <v>22335</v>
@@ -48886,7 +48886,7 @@
         <v>14.2173414230347</v>
       </c>
       <c r="G1673" t="n">
-        <v>12.3519744873047</v>
+        <v>12.351975440979</v>
       </c>
       <c r="H1673" t="n">
         <v>87009</v>
@@ -48973,7 +48973,7 @@
         <v>14.8735256195068</v>
       </c>
       <c r="G1676" t="n">
-        <v>12.922064781189</v>
+        <v>12.9220657348633</v>
       </c>
       <c r="H1676" t="n">
         <v>50454</v>
@@ -49002,7 +49002,7 @@
         <v>14.913293838501</v>
       </c>
       <c r="G1677" t="n">
-        <v>12.956615447998</v>
+        <v>12.9566164016724</v>
       </c>
       <c r="H1677" t="n">
         <v>57916</v>
@@ -49089,7 +49089,7 @@
         <v>16.2654323577881</v>
       </c>
       <c r="G1680" t="n">
-        <v>14.13134765625</v>
+        <v>14.1313486099243</v>
       </c>
       <c r="H1680" t="n">
         <v>68408</v>
@@ -49118,7 +49118,7 @@
         <v>15.8080921173096</v>
       </c>
       <c r="G1681" t="n">
-        <v>13.7340126037598</v>
+        <v>13.7340135574341</v>
       </c>
       <c r="H1681" t="n">
         <v>67717</v>
@@ -49176,7 +49176,7 @@
         <v>16.56369972229</v>
       </c>
       <c r="G1683" t="n">
-        <v>14.3904819488525</v>
+        <v>14.3904829025269</v>
       </c>
       <c r="H1683" t="n">
         <v>43484</v>
@@ -49234,7 +49234,7 @@
         <v>16.1660118103027</v>
       </c>
       <c r="G1685" t="n">
-        <v>14.0449714660645</v>
+        <v>14.0449733734131</v>
       </c>
       <c r="H1685" t="n">
         <v>32214</v>
@@ -49263,7 +49263,7 @@
         <v>16.4245071411133</v>
       </c>
       <c r="G1686" t="n">
-        <v>14.2695531845093</v>
+        <v>14.269552230835</v>
       </c>
       <c r="H1686" t="n">
         <v>18351</v>
@@ -49292,7 +49292,7 @@
         <v>16.4245071411133</v>
       </c>
       <c r="G1687" t="n">
-        <v>14.2695531845093</v>
+        <v>14.269552230835</v>
       </c>
       <c r="H1687" t="n">
         <v>17494</v>
@@ -49495,7 +49495,7 @@
         <v>16.56369972229</v>
       </c>
       <c r="G1694" t="n">
-        <v>14.3904819488525</v>
+        <v>14.3904829025269</v>
       </c>
       <c r="H1694" t="n">
         <v>26265</v>
@@ -49524,7 +49524,7 @@
         <v>15.9671669006348</v>
       </c>
       <c r="G1695" t="n">
-        <v>13.8722162246704</v>
+        <v>13.8722171783447</v>
       </c>
       <c r="H1695" t="n">
         <v>36972</v>
@@ -49553,7 +49553,7 @@
         <v>16.3847389221191</v>
       </c>
       <c r="G1696" t="n">
-        <v>14.2350015640259</v>
+        <v>14.2350025177002</v>
       </c>
       <c r="H1696" t="n">
         <v>21220</v>
@@ -49669,7 +49669,7 @@
         <v>16.6830043792725</v>
       </c>
       <c r="G1700" t="n">
-        <v>14.4941329956055</v>
+        <v>14.4941339492798</v>
       </c>
       <c r="H1700" t="n">
         <v>80815</v>
@@ -49698,7 +49698,7 @@
         <v>16.3648548126221</v>
       </c>
       <c r="G1701" t="n">
-        <v>14.2177267074585</v>
+        <v>14.2177257537842</v>
       </c>
       <c r="H1701" t="n">
         <v>31639</v>
@@ -49727,7 +49727,7 @@
         <v>16.7028903961182</v>
       </c>
       <c r="G1702" t="n">
-        <v>14.5114107131958</v>
+        <v>14.5114097595215</v>
       </c>
       <c r="H1702" t="n">
         <v>31153</v>
@@ -49756,7 +49756,7 @@
         <v>16.7227745056152</v>
       </c>
       <c r="G1703" t="n">
-        <v>14.5286874771118</v>
+        <v>14.5286865234375</v>
       </c>
       <c r="H1703" t="n">
         <v>25895</v>
@@ -49785,7 +49785,7 @@
         <v>16.7625427246094</v>
       </c>
       <c r="G1704" t="n">
-        <v>14.5632362365723</v>
+        <v>14.5632371902466</v>
       </c>
       <c r="H1704" t="n">
         <v>22656</v>
@@ -49988,7 +49988,7 @@
         <v>14.9928321838379</v>
       </c>
       <c r="G1711" t="n">
-        <v>13.0257186889648</v>
+        <v>13.0257177352905</v>
       </c>
       <c r="H1711" t="n">
         <v>31339</v>
@@ -50017,7 +50017,7 @@
         <v>14.9928321838379</v>
       </c>
       <c r="G1712" t="n">
-        <v>13.0257186889648</v>
+        <v>13.0257177352905</v>
       </c>
       <c r="H1712" t="n">
         <v>26278</v>
@@ -50046,7 +50046,7 @@
         <v>14.4758377075195</v>
       </c>
       <c r="G1713" t="n">
-        <v>12.5765552520752</v>
+        <v>12.5765542984009</v>
       </c>
       <c r="H1713" t="n">
         <v>28098</v>
@@ -50075,7 +50075,7 @@
         <v>14.2173414230347</v>
       </c>
       <c r="G1714" t="n">
-        <v>12.3519744873047</v>
+        <v>12.351975440979</v>
       </c>
       <c r="H1714" t="n">
         <v>34347</v>
@@ -50133,7 +50133,7 @@
         <v>14.3963003158569</v>
       </c>
       <c r="G1716" t="n">
-        <v>12.507453918457</v>
+        <v>12.5074529647827</v>
       </c>
       <c r="H1716" t="n">
         <v>12762</v>
@@ -50162,7 +50162,7 @@
         <v>13.8395366668701</v>
       </c>
       <c r="G1717" t="n">
-        <v>12.023738861084</v>
+        <v>12.0237398147583</v>
       </c>
       <c r="H1717" t="n">
         <v>15506</v>
@@ -50220,7 +50220,7 @@
         <v>14.2173414230347</v>
       </c>
       <c r="G1719" t="n">
-        <v>12.3519744873047</v>
+        <v>12.351975440979</v>
       </c>
       <c r="H1719" t="n">
         <v>16186</v>
@@ -50249,7 +50249,7 @@
         <v>14.6945657730103</v>
       </c>
       <c r="G1720" t="n">
-        <v>12.7665863037109</v>
+        <v>12.7665853500366</v>
       </c>
       <c r="H1720" t="n">
         <v>10057</v>
@@ -50307,7 +50307,7 @@
         <v>15.0723686218262</v>
       </c>
       <c r="G1722" t="n">
-        <v>13.094820022583</v>
+        <v>13.0948190689087</v>
       </c>
       <c r="H1722" t="n">
         <v>17435</v>
@@ -50394,7 +50394,7 @@
         <v>14.6746816635132</v>
       </c>
       <c r="G1725" t="n">
-        <v>12.7493095397949</v>
+        <v>12.7493104934692</v>
       </c>
       <c r="H1725" t="n">
         <v>18304</v>
@@ -50742,7 +50742,7 @@
         <v>13.8395366668701</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.023738861084</v>
+        <v>12.0237398147583</v>
       </c>
       <c r="H1737" t="n">
         <v>12333</v>
@@ -50771,7 +50771,7 @@
         <v>14.3963003158569</v>
       </c>
       <c r="G1738" t="n">
-        <v>12.507453918457</v>
+        <v>12.5074529647827</v>
       </c>
       <c r="H1738" t="n">
         <v>11725</v>
@@ -50858,7 +50858,7 @@
         <v>14.1179189682007</v>
       </c>
       <c r="G1741" t="n">
-        <v>12.2655973434448</v>
+        <v>12.2655963897705</v>
       </c>
       <c r="H1741" t="n">
         <v>8175</v>
@@ -50916,7 +50916,7 @@
         <v>13.9389591217041</v>
       </c>
       <c r="G1743" t="n">
-        <v>12.1101179122925</v>
+        <v>12.1101169586182</v>
       </c>
       <c r="H1743" t="n">
         <v>9521</v>
@@ -50974,7 +50974,7 @@
         <v>14.5951442718506</v>
       </c>
       <c r="G1745" t="n">
-        <v>12.6802091598511</v>
+        <v>12.6802082061768</v>
       </c>
       <c r="H1745" t="n">
         <v>11631</v>
@@ -51003,7 +51003,7 @@
         <v>14.6746816635132</v>
       </c>
       <c r="G1746" t="n">
-        <v>12.7493095397949</v>
+        <v>12.7493104934692</v>
       </c>
       <c r="H1746" t="n">
         <v>9847</v>
@@ -51032,7 +51032,7 @@
         <v>15.012716293335</v>
       </c>
       <c r="G1747" t="n">
-        <v>13.0429935455322</v>
+        <v>13.0429944992065</v>
       </c>
       <c r="H1747" t="n">
         <v>24978</v>
@@ -51061,7 +51061,7 @@
         <v>14.8138723373413</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.8702392578125</v>
+        <v>12.8702383041382</v>
       </c>
       <c r="H1748" t="n">
         <v>42863</v>
@@ -51148,7 +51148,7 @@
         <v>14.1974563598633</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.334698677063</v>
+        <v>12.3346977233887</v>
       </c>
       <c r="H1751" t="n">
         <v>17843</v>
@@ -51293,7 +51293,7 @@
         <v>13.819652557373</v>
       </c>
       <c r="G1756" t="n">
-        <v>12.0064640045166</v>
+        <v>12.0064630508423</v>
       </c>
       <c r="H1756" t="n">
         <v>11347</v>
@@ -51380,7 +51380,7 @@
         <v>13.6605777740479</v>
       </c>
       <c r="G1759" t="n">
-        <v>11.868260383606</v>
+        <v>11.8682613372803</v>
       </c>
       <c r="H1759" t="n">
         <v>18395</v>
@@ -51496,7 +51496,7 @@
         <v>14.2372245788574</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.3692502975464</v>
+        <v>12.3692493438721</v>
       </c>
       <c r="H1763" t="n">
         <v>4875</v>
@@ -51554,7 +51554,7 @@
         <v>13.7401151657104</v>
       </c>
       <c r="G1765" t="n">
-        <v>11.9373626708984</v>
+        <v>11.9373617172241</v>
       </c>
       <c r="H1765" t="n">
         <v>7787</v>
@@ -51641,7 +51641,7 @@
         <v>14.4758377075195</v>
       </c>
       <c r="G1768" t="n">
-        <v>12.5765552520752</v>
+        <v>12.5765542984009</v>
       </c>
       <c r="H1768" t="n">
         <v>21675</v>
@@ -51728,7 +51728,7 @@
         <v>14.5951442718506</v>
       </c>
       <c r="G1771" t="n">
-        <v>12.6802091598511</v>
+        <v>12.6802082061768</v>
       </c>
       <c r="H1771" t="n">
         <v>4686</v>
@@ -51757,7 +51757,7 @@
         <v>14.0383806228638</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.1964950561523</v>
+        <v>12.196494102478</v>
       </c>
       <c r="H1772" t="n">
         <v>16185</v>
@@ -51786,7 +51786,7 @@
         <v>14.1775722503662</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.3174238204956</v>
+        <v>12.3174228668213</v>
       </c>
       <c r="H1773" t="n">
         <v>17980</v>
@@ -51815,7 +51815,7 @@
         <v>13.7401151657104</v>
       </c>
       <c r="G1774" t="n">
-        <v>11.9373626708984</v>
+        <v>11.9373617172241</v>
       </c>
       <c r="H1774" t="n">
         <v>7843</v>
@@ -51844,7 +51844,7 @@
         <v>13.799768447876</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.9891891479492</v>
+        <v>11.9891881942749</v>
       </c>
       <c r="H1775" t="n">
         <v>11900</v>
@@ -51873,7 +51873,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1776" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1776" t="n">
         <v>11577</v>
@@ -51902,7 +51902,7 @@
         <v>13.2628898620605</v>
       </c>
       <c r="G1777" t="n">
-        <v>11.5227499008179</v>
+        <v>11.5227508544922</v>
       </c>
       <c r="H1777" t="n">
         <v>16480</v>
@@ -51931,7 +51931,7 @@
         <v>13.5611562728882</v>
       </c>
       <c r="G1778" t="n">
-        <v>11.7818832397461</v>
+        <v>11.7818841934204</v>
       </c>
       <c r="H1778" t="n">
         <v>32206</v>
@@ -51960,7 +51960,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1779" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1779" t="n">
         <v>3599</v>
@@ -51989,7 +51989,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1780" t="n">
-        <v>11.4018220901489</v>
+        <v>11.4018230438232</v>
       </c>
       <c r="H1780" t="n">
         <v>13813</v>
@@ -52018,7 +52018,7 @@
         <v>13.1833524703979</v>
       </c>
       <c r="G1781" t="n">
-        <v>11.4536485671997</v>
+        <v>11.453649520874</v>
       </c>
       <c r="H1781" t="n">
         <v>17457</v>
@@ -52105,7 +52105,7 @@
         <v>13.2827739715576</v>
       </c>
       <c r="G1784" t="n">
-        <v>11.5400266647339</v>
+        <v>11.5400257110596</v>
       </c>
       <c r="H1784" t="n">
         <v>10973</v>
@@ -52134,7 +52134,7 @@
         <v>13.4219646453857</v>
       </c>
       <c r="G1785" t="n">
-        <v>11.6609535217285</v>
+        <v>11.6609544754028</v>
       </c>
       <c r="H1785" t="n">
         <v>4641</v>
@@ -52163,7 +52163,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1786" t="n">
-        <v>11.4018220901489</v>
+        <v>11.4018230438232</v>
       </c>
       <c r="H1786" t="n">
         <v>5719</v>
@@ -52192,7 +52192,7 @@
         <v>13.3424272537231</v>
       </c>
       <c r="G1787" t="n">
-        <v>11.5918531417847</v>
+        <v>11.5918521881104</v>
       </c>
       <c r="H1787" t="n">
         <v>5154</v>
@@ -52221,7 +52221,7 @@
         <v>13.2628898620605</v>
       </c>
       <c r="G1788" t="n">
-        <v>11.5227499008179</v>
+        <v>11.5227508544922</v>
       </c>
       <c r="H1788" t="n">
         <v>14800</v>
@@ -52308,7 +52308,7 @@
         <v>13.5611562728882</v>
       </c>
       <c r="G1791" t="n">
-        <v>11.7818832397461</v>
+        <v>11.7818841934204</v>
       </c>
       <c r="H1791" t="n">
         <v>31040</v>
@@ -52337,7 +52337,7 @@
         <v>13.600923538208</v>
       </c>
       <c r="G1792" t="n">
-        <v>11.8164339065552</v>
+        <v>11.8164329528809</v>
       </c>
       <c r="H1792" t="n">
         <v>30123</v>
@@ -52366,7 +52366,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1793" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1793" t="n">
         <v>37740</v>
@@ -52424,7 +52424,7 @@
         <v>15.0723686218262</v>
       </c>
       <c r="G1795" t="n">
-        <v>13.094820022583</v>
+        <v>13.0948190689087</v>
       </c>
       <c r="H1795" t="n">
         <v>65239</v>
@@ -52453,7 +52453,7 @@
         <v>15.2513294219971</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.2502994537354</v>
+        <v>13.2503004074097</v>
       </c>
       <c r="H1796" t="n">
         <v>57355</v>
@@ -52685,7 +52685,7 @@
         <v>15.132022857666</v>
       </c>
       <c r="G1804" t="n">
-        <v>13.1466455459595</v>
+        <v>13.1466464996338</v>
       </c>
       <c r="H1804" t="n">
         <v>28642</v>
@@ -52772,7 +52772,7 @@
         <v>15.847861289978</v>
       </c>
       <c r="G1807" t="n">
-        <v>13.7685651779175</v>
+        <v>13.7685642242432</v>
       </c>
       <c r="H1807" t="n">
         <v>110276</v>
@@ -52946,7 +52946,7 @@
         <v>15.3706350326538</v>
       </c>
       <c r="G1813" t="n">
-        <v>13.3539514541626</v>
+        <v>13.3539533615112</v>
       </c>
       <c r="H1813" t="n">
         <v>15590</v>
@@ -53004,7 +53004,7 @@
         <v>15.5098257064819</v>
       </c>
       <c r="G1815" t="n">
-        <v>13.4748792648315</v>
+        <v>13.4748802185059</v>
       </c>
       <c r="H1815" t="n">
         <v>7526</v>
@@ -53091,7 +53091,7 @@
         <v>15.012716293335</v>
       </c>
       <c r="G1818" t="n">
-        <v>13.0429935455322</v>
+        <v>13.0429944992065</v>
       </c>
       <c r="H1818" t="n">
         <v>27552</v>
@@ -53207,7 +53207,7 @@
         <v>14.8735256195068</v>
       </c>
       <c r="G1822" t="n">
-        <v>12.922064781189</v>
+        <v>12.9220657348633</v>
       </c>
       <c r="H1822" t="n">
         <v>12235</v>
@@ -53236,7 +53236,7 @@
         <v>14.8735256195068</v>
       </c>
       <c r="G1823" t="n">
-        <v>12.922064781189</v>
+        <v>12.9220657348633</v>
       </c>
       <c r="H1823" t="n">
         <v>18985</v>
@@ -53265,7 +53265,7 @@
         <v>14.8735256195068</v>
       </c>
       <c r="G1824" t="n">
-        <v>12.922064781189</v>
+        <v>12.9220657348633</v>
       </c>
       <c r="H1824" t="n">
         <v>8150</v>
@@ -53323,7 +53323,7 @@
         <v>14.634913444519</v>
       </c>
       <c r="G1826" t="n">
-        <v>12.7147607803345</v>
+        <v>12.7147598266602</v>
       </c>
       <c r="H1826" t="n">
         <v>4901</v>
@@ -53352,7 +53352,7 @@
         <v>14.9928321838379</v>
       </c>
       <c r="G1827" t="n">
-        <v>13.0257186889648</v>
+        <v>13.0257177352905</v>
       </c>
       <c r="H1827" t="n">
         <v>17563</v>
@@ -53439,7 +53439,7 @@
         <v>15.132022857666</v>
       </c>
       <c r="G1830" t="n">
-        <v>13.1466455459595</v>
+        <v>13.1466464996338</v>
       </c>
       <c r="H1830" t="n">
         <v>42690</v>
@@ -53497,7 +53497,7 @@
         <v>14.4758377075195</v>
       </c>
       <c r="G1832" t="n">
-        <v>12.5765552520752</v>
+        <v>12.5765542984009</v>
       </c>
       <c r="H1832" t="n">
         <v>26334</v>
@@ -53555,7 +53555,7 @@
         <v>14.913293838501</v>
       </c>
       <c r="G1834" t="n">
-        <v>12.956615447998</v>
+        <v>12.9566164016724</v>
       </c>
       <c r="H1834" t="n">
         <v>16568</v>
@@ -53584,7 +53584,7 @@
         <v>14.1974563598633</v>
       </c>
       <c r="G1835" t="n">
-        <v>12.334698677063</v>
+        <v>12.3346977233887</v>
       </c>
       <c r="H1835" t="n">
         <v>38923</v>
@@ -53642,7 +53642,7 @@
         <v>13.6804618835449</v>
       </c>
       <c r="G1837" t="n">
-        <v>11.8855361938477</v>
+        <v>11.8855352401733</v>
       </c>
       <c r="H1837" t="n">
         <v>26299</v>
@@ -53700,7 +53700,7 @@
         <v>13.7401151657104</v>
       </c>
       <c r="G1839" t="n">
-        <v>11.9373626708984</v>
+        <v>11.9373617172241</v>
       </c>
       <c r="H1839" t="n">
         <v>49659</v>
@@ -53758,7 +53758,7 @@
         <v>13.1435832977295</v>
       </c>
       <c r="G1841" t="n">
-        <v>11.4190979003906</v>
+        <v>11.4190969467163</v>
       </c>
       <c r="H1841" t="n">
         <v>24427</v>
@@ -53816,7 +53816,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1843" t="n">
-        <v>11.4018220901489</v>
+        <v>11.4018230438232</v>
       </c>
       <c r="H1843" t="n">
         <v>16924</v>
@@ -53874,7 +53874,7 @@
         <v>13.2628898620605</v>
       </c>
       <c r="G1845" t="n">
-        <v>11.5227499008179</v>
+        <v>11.5227508544922</v>
       </c>
       <c r="H1845" t="n">
         <v>14692</v>
@@ -53932,7 +53932,7 @@
         <v>13.3424272537231</v>
       </c>
       <c r="G1847" t="n">
-        <v>11.5918531417847</v>
+        <v>11.5918521881104</v>
       </c>
       <c r="H1847" t="n">
         <v>9142</v>
@@ -53990,7 +53990,7 @@
         <v>13.600923538208</v>
       </c>
       <c r="G1849" t="n">
-        <v>11.8164339065552</v>
+        <v>11.8164329528809</v>
       </c>
       <c r="H1849" t="n">
         <v>20667</v>
@@ -54048,7 +54048,7 @@
         <v>13.2628898620605</v>
       </c>
       <c r="G1851" t="n">
-        <v>11.5227499008179</v>
+        <v>11.5227508544922</v>
       </c>
       <c r="H1851" t="n">
         <v>8893</v>
@@ -54222,7 +54222,7 @@
         <v>13.0242767333984</v>
       </c>
       <c r="G1857" t="n">
-        <v>11.3154449462891</v>
+        <v>11.3154439926147</v>
       </c>
       <c r="H1857" t="n">
         <v>18708</v>
@@ -54251,7 +54251,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1858" t="n">
-        <v>11.4018220901489</v>
+        <v>11.4018230438232</v>
       </c>
       <c r="H1858" t="n">
         <v>4223</v>
@@ -54338,7 +54338,7 @@
         <v>12.4476299285889</v>
       </c>
       <c r="G1861" t="n">
-        <v>10.8144569396973</v>
+        <v>10.8144550323486</v>
       </c>
       <c r="H1861" t="n">
         <v>47673</v>
@@ -54396,7 +54396,7 @@
         <v>12.6067047119141</v>
       </c>
       <c r="G1863" t="n">
-        <v>10.9526586532593</v>
+        <v>10.9526596069336</v>
       </c>
       <c r="H1863" t="n">
         <v>20472</v>
@@ -54425,7 +54425,7 @@
         <v>12.6862421035767</v>
       </c>
       <c r="G1864" t="n">
-        <v>11.0217618942261</v>
+        <v>11.0217609405518</v>
       </c>
       <c r="H1864" t="n">
         <v>13685</v>
@@ -54512,7 +54512,7 @@
         <v>12.6067047119141</v>
       </c>
       <c r="G1867" t="n">
-        <v>10.9526586532593</v>
+        <v>10.9526596069336</v>
       </c>
       <c r="H1867" t="n">
         <v>14660</v>
@@ -54599,7 +54599,7 @@
         <v>12.6067047119141</v>
       </c>
       <c r="G1870" t="n">
-        <v>11.2655925750732</v>
+        <v>11.2655935287476</v>
       </c>
       <c r="H1870" t="n">
         <v>8283</v>
@@ -54628,7 +54628,7 @@
         <v>12.4277448654175</v>
       </c>
       <c r="G1871" t="n">
-        <v>11.1056709289551</v>
+        <v>11.1056718826294</v>
       </c>
       <c r="H1871" t="n">
         <v>10419</v>
@@ -54715,7 +54715,7 @@
         <v>11.9107513427734</v>
       </c>
       <c r="G1874" t="n">
-        <v>10.6436748504639</v>
+        <v>10.6436758041382</v>
       </c>
       <c r="H1874" t="n">
         <v>25819</v>
@@ -54744,7 +54744,7 @@
         <v>11.9505195617676</v>
       </c>
       <c r="G1875" t="n">
-        <v>10.6792125701904</v>
+        <v>10.6792135238647</v>
       </c>
       <c r="H1875" t="n">
         <v>15795</v>
@@ -54773,7 +54773,7 @@
         <v>12.9447393417358</v>
       </c>
       <c r="G1876" t="n">
-        <v>11.5676679611206</v>
+        <v>11.5676670074463</v>
       </c>
       <c r="H1876" t="n">
         <v>85308</v>
@@ -54802,7 +54802,7 @@
         <v>13.0043926239014</v>
       </c>
       <c r="G1877" t="n">
-        <v>11.6209735870361</v>
+        <v>11.6209745407104</v>
       </c>
       <c r="H1877" t="n">
         <v>56683</v>
@@ -54889,7 +54889,7 @@
         <v>13.3821964263916</v>
       </c>
       <c r="G1880" t="n">
-        <v>11.9585866928101</v>
+        <v>11.9585876464844</v>
       </c>
       <c r="H1880" t="n">
         <v>48235</v>
@@ -54918,7 +54918,7 @@
         <v>13.1435832977295</v>
       </c>
       <c r="G1881" t="n">
-        <v>11.7453584671021</v>
+        <v>11.7453575134277</v>
       </c>
       <c r="H1881" t="n">
         <v>20772</v>
@@ -54976,7 +54976,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1883" t="n">
-        <v>11.7275886535645</v>
+        <v>11.7275896072388</v>
       </c>
       <c r="H1883" t="n">
         <v>17735</v>
@@ -55034,7 +55034,7 @@
         <v>12.9447393417358</v>
       </c>
       <c r="G1885" t="n">
-        <v>11.5676679611206</v>
+        <v>11.5676670074463</v>
       </c>
       <c r="H1885" t="n">
         <v>25168</v>
@@ -55063,7 +55063,7 @@
         <v>12.8652019500732</v>
       </c>
       <c r="G1886" t="n">
-        <v>11.4965906143188</v>
+        <v>11.4965915679932</v>
       </c>
       <c r="H1886" t="n">
         <v>14610</v>
@@ -55266,7 +55266,7 @@
         <v>12.8055486679077</v>
       </c>
       <c r="G1893" t="n">
-        <v>11.4432830810547</v>
+        <v>11.443284034729</v>
       </c>
       <c r="H1893" t="n">
         <v>24953</v>
@@ -55440,7 +55440,7 @@
         <v>12.6067047119141</v>
       </c>
       <c r="G1899" t="n">
-        <v>11.2655925750732</v>
+        <v>11.2655935287476</v>
       </c>
       <c r="H1899" t="n">
         <v>9180</v>
@@ -55498,7 +55498,7 @@
         <v>12.3482084274292</v>
       </c>
       <c r="G1901" t="n">
-        <v>11.034595489502</v>
+        <v>11.0345964431763</v>
       </c>
       <c r="H1901" t="n">
         <v>7085</v>
@@ -55759,7 +55759,7 @@
         <v>12.6265888214111</v>
       </c>
       <c r="G1910" t="n">
-        <v>11.2833623886108</v>
+        <v>11.2833614349365</v>
       </c>
       <c r="H1910" t="n">
         <v>45729</v>
@@ -55904,7 +55904,7 @@
         <v>12.1891317367554</v>
       </c>
       <c r="G1915" t="n">
-        <v>10.8924417495728</v>
+        <v>10.8924407958984</v>
       </c>
       <c r="H1915" t="n">
         <v>7866</v>
@@ -55933,7 +55933,7 @@
         <v>12.2090167999268</v>
       </c>
       <c r="G1916" t="n">
-        <v>10.910210609436</v>
+        <v>10.9102115631104</v>
       </c>
       <c r="H1916" t="n">
         <v>12222</v>
@@ -56020,7 +56020,7 @@
         <v>12.4277448654175</v>
       </c>
       <c r="G1919" t="n">
-        <v>11.1056709289551</v>
+        <v>11.1056718826294</v>
       </c>
       <c r="H1919" t="n">
         <v>10498</v>
@@ -56136,7 +56136,7 @@
         <v>12.4277448654175</v>
       </c>
       <c r="G1923" t="n">
-        <v>11.1056709289551</v>
+        <v>11.1056718826294</v>
       </c>
       <c r="H1923" t="n">
         <v>8635</v>
@@ -56368,7 +56368,7 @@
         <v>12.6265888214111</v>
       </c>
       <c r="G1931" t="n">
-        <v>11.2833623886108</v>
+        <v>11.2833614349365</v>
       </c>
       <c r="H1931" t="n">
         <v>7398</v>
@@ -56397,7 +56397,7 @@
         <v>12.8652019500732</v>
       </c>
       <c r="G1932" t="n">
-        <v>11.4965906143188</v>
+        <v>11.4965915679932</v>
       </c>
       <c r="H1932" t="n">
         <v>19392</v>
@@ -56455,7 +56455,7 @@
         <v>13.0640459060669</v>
       </c>
       <c r="G1934" t="n">
-        <v>11.6742811203003</v>
+        <v>11.6742820739746</v>
       </c>
       <c r="H1934" t="n">
         <v>18292</v>
@@ -56513,7 +56513,7 @@
         <v>12.6265888214111</v>
       </c>
       <c r="G1936" t="n">
-        <v>11.2833623886108</v>
+        <v>11.2833614349365</v>
       </c>
       <c r="H1936" t="n">
         <v>13337</v>
@@ -56542,7 +56542,7 @@
         <v>12.4476299285889</v>
       </c>
       <c r="G1937" t="n">
-        <v>11.1234407424927</v>
+        <v>11.1234397888184</v>
       </c>
       <c r="H1937" t="n">
         <v>14017</v>
@@ -56571,7 +56571,7 @@
         <v>12.8055486679077</v>
       </c>
       <c r="G1938" t="n">
-        <v>11.4432830810547</v>
+        <v>11.443284034729</v>
       </c>
       <c r="H1938" t="n">
         <v>20379</v>
@@ -56716,7 +56716,7 @@
         <v>12.8652019500732</v>
       </c>
       <c r="G1943" t="n">
-        <v>11.4965906143188</v>
+        <v>11.4965915679932</v>
       </c>
       <c r="H1943" t="n">
         <v>13684</v>
@@ -56745,7 +56745,7 @@
         <v>12.6265888214111</v>
       </c>
       <c r="G1944" t="n">
-        <v>11.2833623886108</v>
+        <v>11.2833614349365</v>
       </c>
       <c r="H1944" t="n">
         <v>5996</v>
@@ -56832,7 +56832,7 @@
         <v>12.2090167999268</v>
       </c>
       <c r="G1947" t="n">
-        <v>10.910210609436</v>
+        <v>10.9102115631104</v>
       </c>
       <c r="H1947" t="n">
         <v>15680</v>
@@ -56919,7 +56919,7 @@
         <v>12.8055486679077</v>
       </c>
       <c r="G1950" t="n">
-        <v>11.4432830810547</v>
+        <v>11.443284034729</v>
       </c>
       <c r="H1950" t="n">
         <v>5716</v>
@@ -56977,7 +56977,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1952" t="n">
-        <v>11.7275886535645</v>
+        <v>11.7275896072388</v>
       </c>
       <c r="H1952" t="n">
         <v>21712</v>
@@ -57064,7 +57064,7 @@
         <v>12.8850860595703</v>
       </c>
       <c r="G1955" t="n">
-        <v>11.5143604278564</v>
+        <v>11.5143594741821</v>
       </c>
       <c r="H1955" t="n">
         <v>11394</v>
@@ -57122,7 +57122,7 @@
         <v>12.7856636047363</v>
       </c>
       <c r="G1957" t="n">
-        <v>11.4255142211914</v>
+        <v>11.4255132675171</v>
       </c>
       <c r="H1957" t="n">
         <v>25985</v>
@@ -57180,7 +57180,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1959" t="n">
-        <v>11.7275886535645</v>
+        <v>11.7275896072388</v>
       </c>
       <c r="H1959" t="n">
         <v>64914</v>
@@ -57209,7 +57209,7 @@
         <v>13.3821964263916</v>
       </c>
       <c r="G1960" t="n">
-        <v>11.9585866928101</v>
+        <v>11.9585876464844</v>
       </c>
       <c r="H1960" t="n">
         <v>46152</v>
@@ -57238,7 +57238,7 @@
         <v>13.1236991882324</v>
       </c>
       <c r="G1961" t="n">
-        <v>11.7275886535645</v>
+        <v>11.7275896072388</v>
       </c>
       <c r="H1961" t="n">
         <v>144736</v>
@@ -57325,7 +57325,7 @@
         <v>14.2968778610229</v>
       </c>
       <c r="G1964" t="n">
-        <v>12.7759637832642</v>
+        <v>12.7759628295898</v>
       </c>
       <c r="H1964" t="n">
         <v>95696</v>
@@ -57383,7 +57383,7 @@
         <v>14.2968778610229</v>
       </c>
       <c r="G1966" t="n">
-        <v>12.7759637832642</v>
+        <v>12.7759628295898</v>
       </c>
       <c r="H1966" t="n">
         <v>70352</v>
@@ -57412,7 +57412,7 @@
         <v>14.2968778610229</v>
       </c>
       <c r="G1967" t="n">
-        <v>12.7759637832642</v>
+        <v>12.7759628295898</v>
       </c>
       <c r="H1967" t="n">
         <v>52699</v>
@@ -57470,7 +57470,7 @@
         <v>13.9986124038696</v>
       </c>
       <c r="G1969" t="n">
-        <v>12.5094289779663</v>
+        <v>12.509428024292</v>
       </c>
       <c r="H1969" t="n">
         <v>57862</v>
@@ -57499,7 +57499,7 @@
         <v>13.6406927108765</v>
       </c>
       <c r="G1970" t="n">
-        <v>12.1895837783813</v>
+        <v>12.1895847320557</v>
       </c>
       <c r="H1970" t="n">
         <v>108251</v>
@@ -57673,7 +57673,7 @@
         <v>14.1576871871948</v>
       </c>
       <c r="G1976" t="n">
-        <v>12.6515798568726</v>
+        <v>12.6515808105469</v>
       </c>
       <c r="H1976" t="n">
         <v>16405</v>
@@ -57731,7 +57731,7 @@
         <v>13.9986124038696</v>
       </c>
       <c r="G1978" t="n">
-        <v>12.5094289779663</v>
+        <v>12.509428024292</v>
       </c>
       <c r="H1978" t="n">
         <v>46160</v>
@@ -57847,7 +57847,7 @@
         <v>14.3764162063599</v>
       </c>
       <c r="G1982" t="n">
-        <v>12.8470411300659</v>
+        <v>12.8470401763916</v>
       </c>
       <c r="H1982" t="n">
         <v>72229</v>
@@ -58108,7 +58108,7 @@
         <v>14.416184425354</v>
       </c>
       <c r="G1991" t="n">
-        <v>12.8825778961182</v>
+        <v>12.8825788497925</v>
       </c>
       <c r="H1991" t="n">
         <v>18798</v>
@@ -58195,7 +58195,7 @@
         <v>14.5951442718506</v>
       </c>
       <c r="G1994" t="n">
-        <v>13.042501449585</v>
+        <v>13.0425004959106</v>
       </c>
       <c r="H1994" t="n">
         <v>50727</v>
@@ -58427,7 +58427,7 @@
         <v>15.3905200958252</v>
       </c>
       <c r="G2002" t="n">
-        <v>13.7532644271851</v>
+        <v>13.7532634735107</v>
       </c>
       <c r="H2002" t="n">
         <v>45532</v>
@@ -58543,7 +58543,7 @@
         <v>16.5835838317871</v>
       </c>
       <c r="G2006" t="n">
-        <v>14.8194074630737</v>
+        <v>14.819408416748</v>
       </c>
       <c r="H2006" t="n">
         <v>277660</v>
@@ -58572,7 +58572,7 @@
         <v>16.7625427246094</v>
       </c>
       <c r="G2007" t="n">
-        <v>14.9793291091919</v>
+        <v>14.9793281555176</v>
       </c>
       <c r="H2007" t="n">
         <v>196629</v>
@@ -58630,7 +58630,7 @@
         <v>16.8023128509521</v>
       </c>
       <c r="G2009" t="n">
-        <v>15.0148687362671</v>
+        <v>15.0148677825928</v>
       </c>
       <c r="H2009" t="n">
         <v>49236</v>
@@ -58688,7 +58688,7 @@
         <v>16.7824268341064</v>
       </c>
       <c r="G2011" t="n">
-        <v>14.9970970153809</v>
+        <v>14.9970979690552</v>
       </c>
       <c r="H2011" t="n">
         <v>35329</v>
@@ -58862,7 +58862,7 @@
         <v>16.6631202697754</v>
       </c>
       <c r="G2017" t="n">
-        <v>14.8904838562012</v>
+        <v>14.8904829025269</v>
       </c>
       <c r="H2017" t="n">
         <v>11050</v>
@@ -58978,7 +58978,7 @@
         <v>16.8420791625977</v>
       </c>
       <c r="G2021" t="n">
-        <v>15.0504035949707</v>
+        <v>15.050404548645</v>
       </c>
       <c r="H2021" t="n">
         <v>15723</v>
@@ -59036,7 +59036,7 @@
         <v>16.543815612793</v>
       </c>
       <c r="G2023" t="n">
-        <v>14.7838706970215</v>
+        <v>14.7838697433472</v>
       </c>
       <c r="H2023" t="n">
         <v>8739</v>
@@ -59065,7 +59065,7 @@
         <v>16.4046249389648</v>
       </c>
       <c r="G2024" t="n">
-        <v>14.6594858169556</v>
+        <v>14.6594867706299</v>
       </c>
       <c r="H2024" t="n">
         <v>84128</v>
@@ -59123,7 +59123,7 @@
         <v>16.026819229126</v>
       </c>
       <c r="G2026" t="n">
-        <v>14.3218727111816</v>
+        <v>14.3218717575073</v>
       </c>
       <c r="H2026" t="n">
         <v>21037</v>
@@ -59181,7 +59181,7 @@
         <v>16.5835838317871</v>
       </c>
       <c r="G2028" t="n">
-        <v>14.8194074630737</v>
+        <v>14.819408416748</v>
       </c>
       <c r="H2028" t="n">
         <v>50508</v>
@@ -59239,7 +59239,7 @@
         <v>16.543815612793</v>
       </c>
       <c r="G2030" t="n">
-        <v>14.7838706970215</v>
+        <v>14.7838697433472</v>
       </c>
       <c r="H2030" t="n">
         <v>31065</v>
@@ -59355,7 +59355,7 @@
         <v>17.0608081817627</v>
       </c>
       <c r="G2034" t="n">
-        <v>15.2458648681641</v>
+        <v>15.2458639144897</v>
       </c>
       <c r="H2034" t="n">
         <v>27619</v>
@@ -59442,7 +59442,7 @@
         <v>16.9613876342773</v>
       </c>
       <c r="G2037" t="n">
-        <v>15.1570205688477</v>
+        <v>15.157021522522</v>
       </c>
       <c r="H2037" t="n">
         <v>26192</v>
@@ -59471,7 +59471,7 @@
         <v>16.6034679412842</v>
       </c>
       <c r="G2038" t="n">
-        <v>14.8371772766113</v>
+        <v>14.837176322937</v>
       </c>
       <c r="H2038" t="n">
         <v>19433</v>
@@ -59500,7 +59500,7 @@
         <v>16.8023128509521</v>
       </c>
       <c r="G2039" t="n">
-        <v>15.0148687362671</v>
+        <v>15.0148677825928</v>
       </c>
       <c r="H2039" t="n">
         <v>14397</v>
@@ -59558,7 +59558,7 @@
         <v>16.9216175079346</v>
       </c>
       <c r="G2041" t="n">
-        <v>15.1214818954468</v>
+        <v>15.1214799880981</v>
       </c>
       <c r="H2041" t="n">
         <v>26875</v>
@@ -59587,7 +59587,7 @@
         <v>17.0011558532715</v>
       </c>
       <c r="G2042" t="n">
-        <v>15.1925582885742</v>
+        <v>15.1925592422485</v>
       </c>
       <c r="H2042" t="n">
         <v>39984</v>
@@ -59645,7 +59645,7 @@
         <v>16.8023128509521</v>
       </c>
       <c r="G2044" t="n">
-        <v>15.0148687362671</v>
+        <v>15.0148677825928</v>
       </c>
       <c r="H2044" t="n">
         <v>21176</v>
@@ -59732,7 +59732,7 @@
         <v>16.344970703125</v>
       </c>
       <c r="G2047" t="n">
-        <v>14.6061792373657</v>
+        <v>14.6061782836914</v>
       </c>
       <c r="H2047" t="n">
         <v>48732</v>
@@ -59877,7 +59877,7 @@
         <v>16.7028903961182</v>
       </c>
       <c r="G2052" t="n">
-        <v>14.9260225296021</v>
+        <v>14.9260234832764</v>
       </c>
       <c r="H2052" t="n">
         <v>78506</v>
@@ -59906,7 +59906,7 @@
         <v>16.7824268341064</v>
       </c>
       <c r="G2053" t="n">
-        <v>14.9970970153809</v>
+        <v>14.9970979690552</v>
       </c>
       <c r="H2053" t="n">
         <v>68921</v>
@@ -59993,7 +59993,7 @@
         <v>16.9613876342773</v>
       </c>
       <c r="G2056" t="n">
-        <v>15.1570205688477</v>
+        <v>15.157021522522</v>
       </c>
       <c r="H2056" t="n">
         <v>32374</v>
@@ -60022,7 +60022,7 @@
         <v>17.1801147460938</v>
       </c>
       <c r="G2057" t="n">
-        <v>15.3524799346924</v>
+        <v>15.3524789810181</v>
       </c>
       <c r="H2057" t="n">
         <v>40133</v>
@@ -60080,7 +60080,7 @@
         <v>17.3590755462646</v>
       </c>
       <c r="G2059" t="n">
-        <v>15.5124015808105</v>
+        <v>15.5124034881592</v>
       </c>
       <c r="H2059" t="n">
         <v>35505</v>
@@ -60109,7 +60109,7 @@
         <v>17.0210399627686</v>
       </c>
       <c r="G2060" t="n">
-        <v>15.2103271484375</v>
+        <v>15.2103261947632</v>
       </c>
       <c r="H2060" t="n">
         <v>48582</v>
@@ -60138,7 +60138,7 @@
         <v>17.0608081817627</v>
       </c>
       <c r="G2061" t="n">
-        <v>15.2458648681641</v>
+        <v>15.2458639144897</v>
       </c>
       <c r="H2061" t="n">
         <v>50771</v>
@@ -60196,7 +60196,7 @@
         <v>14.5951442718506</v>
       </c>
       <c r="G2063" t="n">
-        <v>13.042501449585</v>
+        <v>13.0425004959106</v>
       </c>
       <c r="H2063" t="n">
         <v>346649</v>
@@ -60312,7 +60312,7 @@
         <v>14.7144498825073</v>
       </c>
       <c r="G2067" t="n">
-        <v>13.1491136550903</v>
+        <v>13.1491146087646</v>
       </c>
       <c r="H2067" t="n">
         <v>38761</v>
@@ -60341,7 +60341,7 @@
         <v>14.7144498825073</v>
       </c>
       <c r="G2068" t="n">
-        <v>13.1491136550903</v>
+        <v>13.1491146087646</v>
       </c>
       <c r="H2068" t="n">
         <v>23494</v>
@@ -60370,7 +60370,7 @@
         <v>15.2513294219971</v>
       </c>
       <c r="G2069" t="n">
-        <v>13.6288805007935</v>
+        <v>13.6288795471191</v>
       </c>
       <c r="H2069" t="n">
         <v>58922</v>
@@ -60399,7 +60399,7 @@
         <v>15.5893640518188</v>
       </c>
       <c r="G2070" t="n">
-        <v>13.9309549331665</v>
+        <v>13.9309539794922</v>
       </c>
       <c r="H2070" t="n">
         <v>65467</v>
@@ -60689,7 +60689,7 @@
         <v>14.9530630111694</v>
       </c>
       <c r="G2080" t="n">
-        <v>13.362343788147</v>
+        <v>13.3623428344727</v>
       </c>
       <c r="H2080" t="n">
         <v>36772</v>
@@ -60776,7 +60776,7 @@
         <v>14.6547966003418</v>
       </c>
       <c r="G2083" t="n">
-        <v>13.0958061218262</v>
+        <v>13.0958070755005</v>
       </c>
       <c r="H2083" t="n">
         <v>38919</v>
@@ -60805,7 +60805,7 @@
         <v>14.7144498825073</v>
       </c>
       <c r="G2084" t="n">
-        <v>13.1491136550903</v>
+        <v>13.1491146087646</v>
       </c>
       <c r="H2084" t="n">
         <v>75268</v>
@@ -60834,7 +60834,7 @@
         <v>14.4360685348511</v>
       </c>
       <c r="G2085" t="n">
-        <v>12.9003477096558</v>
+        <v>12.9003467559814</v>
       </c>
       <c r="H2085" t="n">
         <v>69431</v>
@@ -60892,7 +60892,7 @@
         <v>14.6547966003418</v>
       </c>
       <c r="G2087" t="n">
-        <v>13.0958061218262</v>
+        <v>13.0958070755005</v>
       </c>
       <c r="H2087" t="n">
         <v>26141</v>
@@ -60950,7 +60950,7 @@
         <v>14.6945657730103</v>
       </c>
       <c r="G2089" t="n">
-        <v>13.1313457489014</v>
+        <v>13.1313447952271</v>
       </c>
       <c r="H2089" t="n">
         <v>121452</v>
@@ -61414,7 +61414,7 @@
         <v>14.018497467041</v>
       </c>
       <c r="G2105" t="n">
-        <v>12.5271968841553</v>
+        <v>12.5271978378296</v>
       </c>
       <c r="H2105" t="n">
         <v>30237</v>
@@ -61820,7 +61820,7 @@
         <v>14.4559526443481</v>
       </c>
       <c r="G2119" t="n">
-        <v>12.9181156158447</v>
+        <v>12.918116569519</v>
       </c>
       <c r="H2119" t="n">
         <v>21290</v>
@@ -61907,7 +61907,7 @@
         <v>14.0383806228638</v>
       </c>
       <c r="G2122" t="n">
-        <v>12.5449657440186</v>
+        <v>12.5449647903442</v>
       </c>
       <c r="H2122" t="n">
         <v>54053</v>
@@ -61965,7 +61965,7 @@
         <v>13.5015020370483</v>
       </c>
       <c r="G2124" t="n">
-        <v>12.0651998519897</v>
+        <v>12.0652008056641</v>
       </c>
       <c r="H2124" t="n">
         <v>104013</v>
@@ -61994,7 +61994,7 @@
         <v>14.018497467041</v>
       </c>
       <c r="G2125" t="n">
-        <v>12.5271968841553</v>
+        <v>12.5271978378296</v>
       </c>
       <c r="H2125" t="n">
         <v>67875</v>
@@ -79951,6 +79951,64 @@
         <v>23957</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>14.3400001525879</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>25987</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>14.6800003051758</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>14.8800001144409</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>14.8800001144409</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>21170</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>
